--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -556,10 +556,10 @@
         <v>37</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27021.686746988</v>
       </c>
       <c r="O4" t="n">
-        <v>999000</v>
+        <v>999802.4096385561</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -1466,10 +1466,10 @@
         <v>62</v>
       </c>
       <c r="N27" t="n">
-        <v>14857.623272727</v>
+        <v>14857.623287671</v>
       </c>
       <c r="O27" t="n">
-        <v>921172.642909074</v>
+        <v>921172.643835602</v>
       </c>
       <c r="P27" t="n">
         <v>34900</v>
@@ -4068,10 +4068,10 @@
         <v>873</v>
       </c>
       <c r="N88" t="n">
-        <v>10600</v>
+        <v>10603.665283541</v>
       </c>
       <c r="O88" t="n">
-        <v>9253800</v>
+        <v>9256999.792531293</v>
       </c>
       <c r="P88" t="n">
         <v>17200</v>
@@ -5912,10 +5912,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1712612367</v>
+        <v>4371.766707533</v>
       </c>
       <c r="O129" t="n">
-        <v>4852000.099972737</v>
+        <v>4852661.04536163</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1943880809</v>
+        <v>1550.1943922358</v>
       </c>
       <c r="O162" t="n">
-        <v>55806.99797091239</v>
+        <v>55806.9981204888</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7623,10 +7623,10 @@
         <v>420</v>
       </c>
       <c r="N167" t="n">
-        <v>2069.4655430712</v>
+        <v>2069.4655178908</v>
       </c>
       <c r="O167" t="n">
-        <v>869175.528089904</v>
+        <v>869175.517514136</v>
       </c>
       <c r="P167" t="n">
         <v>6500</v>
@@ -15754,22 +15754,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M348" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="N348" t="n">
         <v>10219</v>
       </c>
       <c r="O348" t="n">
-        <v>858396</v>
+        <v>756206</v>
       </c>
       <c r="P348" t="n">
         <v>16900</v>
       </c>
       <c r="Q348" t="n">
-        <v>1419600</v>
+        <v>1250600</v>
       </c>
     </row>
     <row r="349">
@@ -16220,10 +16220,10 @@
         <v>839</v>
       </c>
       <c r="N358" t="n">
-        <v>1516.0387548048</v>
+        <v>1516.0387544268</v>
       </c>
       <c r="O358" t="n">
-        <v>1271956.515281227</v>
+        <v>1271956.514964085</v>
       </c>
       <c r="P358" t="n">
         <v>2300</v>
@@ -16444,22 +16444,22 @@
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M363" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N363" t="n">
         <v>2327.68</v>
       </c>
       <c r="O363" t="n">
-        <v>39570.56</v>
+        <v>34915.2</v>
       </c>
       <c r="P363" t="n">
         <v>3900</v>
       </c>
       <c r="Q363" t="n">
-        <v>66300</v>
+        <v>58500</v>
       </c>
     </row>
     <row r="364">
@@ -17825,10 +17825,10 @@
         <v>158</v>
       </c>
       <c r="N392" t="n">
-        <v>1690.8700092894</v>
+        <v>1690.870009298</v>
       </c>
       <c r="O392" t="n">
-        <v>267157.4614677252</v>
+        <v>267157.461469084</v>
       </c>
       <c r="P392" t="n">
         <v>3000</v>
@@ -18103,22 +18103,22 @@
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M398" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="N398" t="n">
-        <v>3907.5003375527</v>
+        <v>3907.5003418803</v>
       </c>
       <c r="O398" t="n">
-        <v>265710.0229535836</v>
+        <v>242265.0211965786</v>
       </c>
       <c r="P398" t="n">
         <v>3900</v>
       </c>
       <c r="Q398" t="n">
-        <v>265200</v>
+        <v>241800</v>
       </c>
     </row>
     <row r="399">

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>37</v>
       </c>
       <c r="N4" t="n">
-        <v>27021.686746988</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>999802.4096385561</v>
+        <v>999000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8550793651</v>
+        <v>6272.8550883392</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.552698419</v>
+        <v>1794036.555265011</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0630728186</v>
+        <v>1098.0632479443</v>
       </c>
       <c r="O70" t="n">
-        <v>129571.4425925948</v>
+        <v>129571.4632574274</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4068,10 +4068,10 @@
         <v>873</v>
       </c>
       <c r="N88" t="n">
-        <v>10603.665283541</v>
+        <v>10600</v>
       </c>
       <c r="O88" t="n">
-        <v>9256999.792531293</v>
+        <v>9253800</v>
       </c>
       <c r="P88" t="n">
         <v>17200</v>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>355</v>
+        <v>205</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4928,19 +4928,19 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>355</v>
+        <v>205</v>
       </c>
       <c r="N107" t="n">
         <v>3472</v>
       </c>
       <c r="O107" t="n">
-        <v>1232560</v>
+        <v>711760</v>
       </c>
       <c r="P107" t="n">
         <v>4800</v>
       </c>
       <c r="Q107" t="n">
-        <v>1704000</v>
+        <v>984000</v>
       </c>
     </row>
     <row r="108">
@@ -5601,10 +5601,10 @@
         <v>289</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.462931554</v>
+        <v>12422.462939145</v>
       </c>
       <c r="O122" t="n">
-        <v>3590091.787219106</v>
+        <v>3590091.789412905</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5732,10 +5732,10 @@
         <v>2520</v>
       </c>
       <c r="N125" t="n">
-        <v>3471.9020126478</v>
+        <v>3472.0232664284</v>
       </c>
       <c r="O125" t="n">
-        <v>8749193.071872456</v>
+        <v>8749498.631399568</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600138793</v>
+        <v>3041.6600139179</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.666953529</v>
+        <v>1523871.666972868</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5912,10 +5912,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.766707533</v>
+        <v>4371.1712622683</v>
       </c>
       <c r="O129" t="n">
-        <v>4852661.04536163</v>
+        <v>4852000.101117813</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9242252747</v>
+        <v>1630.9242345815</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.5270274677</v>
+        <v>311506.5288050665</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1943922358</v>
+        <v>1550.19440684</v>
       </c>
       <c r="O162" t="n">
-        <v>55806.9981204888</v>
+        <v>55806.99864624</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7456,10 +7456,10 @@
         <v>48</v>
       </c>
       <c r="N163" t="n">
-        <v>1579.3858102767</v>
+        <v>1579.3856972112</v>
       </c>
       <c r="O163" t="n">
-        <v>75810.51889328161</v>
+        <v>75810.51346613761</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -9309,10 +9309,10 @@
         <v>1200</v>
       </c>
       <c r="N206" t="n">
-        <v>6207.9815581169</v>
+        <v>6207.9842244133</v>
       </c>
       <c r="O206" t="n">
-        <v>7449577.869740279</v>
+        <v>7449581.06929596</v>
       </c>
       <c r="P206" t="n">
         <v>9900</v>
@@ -9696,10 +9696,10 @@
         <v>720</v>
       </c>
       <c r="N215" t="n">
-        <v>4814.2679275122</v>
+        <v>4814.2679274047</v>
       </c>
       <c r="O215" t="n">
-        <v>3466272.907808784</v>
+        <v>3466272.907731384</v>
       </c>
       <c r="P215" t="n">
         <v>9900</v>
@@ -11654,10 +11654,10 @@
         <v>952</v>
       </c>
       <c r="N259" t="n">
-        <v>1778.4727855775</v>
+        <v>1778.47280077</v>
       </c>
       <c r="O259" t="n">
-        <v>1693106.09186978</v>
+        <v>1693106.10633304</v>
       </c>
       <c r="P259" t="n">
         <v>4900</v>
@@ -14523,10 +14523,10 @@
         <v>100</v>
       </c>
       <c r="N321" t="n">
-        <v>4907.8225298805</v>
+        <v>4907.82254</v>
       </c>
       <c r="O321" t="n">
-        <v>490782.25298805</v>
+        <v>490782.254</v>
       </c>
       <c r="P321" t="n">
         <v>8200</v>
@@ -14753,10 +14753,10 @@
         <v>84</v>
       </c>
       <c r="N326" t="n">
-        <v>3903.7388113695</v>
+        <v>3903.7388764045</v>
       </c>
       <c r="O326" t="n">
-        <v>327914.060155038</v>
+        <v>327914.065617978</v>
       </c>
       <c r="P326" t="n">
         <v>7500</v>
@@ -15748,13 +15748,13 @@
         </is>
       </c>
       <c r="J348" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M348" t="n">
         <v>74</v>
@@ -16220,10 +16220,10 @@
         <v>839</v>
       </c>
       <c r="N358" t="n">
-        <v>1516.0387544268</v>
+        <v>1516.0387516479</v>
       </c>
       <c r="O358" t="n">
-        <v>1271956.514964085</v>
+        <v>1271956.512632588</v>
       </c>
       <c r="P358" t="n">
         <v>2300</v>
@@ -16438,13 +16438,13 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M363" t="n">
         <v>15</v>
@@ -18097,22 +18097,22 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="K398" t="n">
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M398" t="n">
         <v>62</v>
       </c>
       <c r="N398" t="n">
-        <v>3907.5003418803</v>
+        <v>3907.5003448276</v>
       </c>
       <c r="O398" t="n">
-        <v>242265.0211965786</v>
+        <v>242265.0213793112</v>
       </c>
       <c r="P398" t="n">
         <v>3900</v>
@@ -18854,10 +18854,10 @@
         <v>2</v>
       </c>
       <c r="N414" t="n">
-        <v>3110.8390217391</v>
+        <v>3110.8380493577</v>
       </c>
       <c r="O414" t="n">
-        <v>6221.6780434782</v>
+        <v>6221.6760987154</v>
       </c>
       <c r="P414" t="n">
         <v>4500</v>
@@ -20986,7 +20986,7 @@
         </is>
       </c>
       <c r="J459" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K459" t="n">
         <v>0</v>
@@ -20995,19 +20995,19 @@
         <v>0</v>
       </c>
       <c r="M459" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N459" t="n">
         <v>27577.72</v>
       </c>
       <c r="O459" t="n">
-        <v>55155.44</v>
+        <v>110310.88</v>
       </c>
       <c r="P459" t="n">
         <v>120900</v>
       </c>
       <c r="Q459" t="n">
-        <v>241800</v>
+        <v>483600</v>
       </c>
     </row>
     <row r="460">
@@ -21725,10 +21725,10 @@
         <v>152</v>
       </c>
       <c r="N474" t="n">
-        <v>7046.939827363</v>
+        <v>7046.9398272138</v>
       </c>
       <c r="O474" t="n">
-        <v>1071134.853759176</v>
+        <v>1071134.853736497</v>
       </c>
       <c r="P474" t="n">
         <v>9900</v>
@@ -23008,10 +23008,10 @@
         <v>60</v>
       </c>
       <c r="N501" t="n">
-        <v>1008.8134367542</v>
+        <v>1008.8130317848</v>
       </c>
       <c r="O501" t="n">
-        <v>60528.806205252</v>
+        <v>60528.781907088</v>
       </c>
       <c r="P501" t="n">
         <v>1500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -2074,10 +2074,10 @@
         <v>34</v>
       </c>
       <c r="N42" t="n">
-        <v>61666.874171271</v>
+        <v>62706.203511236</v>
       </c>
       <c r="O42" t="n">
-        <v>2096673.721823214</v>
+        <v>2132010.919382024</v>
       </c>
       <c r="P42" t="n">
         <v>98900</v>
@@ -4299,10 +4299,10 @@
         <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>8214</v>
+        <v>8701.9603960396</v>
       </c>
       <c r="O93" t="n">
-        <v>16428</v>
+        <v>17403.9207920792</v>
       </c>
       <c r="P93" t="n">
         <v>7900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9242345815</v>
+        <v>1630.9242415885</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.5288050665</v>
+        <v>311506.5301434035</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -9696,10 +9696,10 @@
         <v>720</v>
       </c>
       <c r="N215" t="n">
-        <v>4814.2679274047</v>
+        <v>4814.2679269747</v>
       </c>
       <c r="O215" t="n">
-        <v>3466272.907731384</v>
+        <v>3466272.907421784</v>
       </c>
       <c r="P215" t="n">
         <v>9900</v>
@@ -10962,10 +10962,10 @@
         <v>97</v>
       </c>
       <c r="N244" t="n">
-        <v>7700</v>
+        <v>7812.5456760049</v>
       </c>
       <c r="O244" t="n">
-        <v>746900</v>
+        <v>757816.9305724753</v>
       </c>
       <c r="P244" t="n">
         <v>13900</v>
@@ -16220,10 +16220,10 @@
         <v>839</v>
       </c>
       <c r="N358" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O358" t="n">
-        <v>1271956.512632588</v>
+        <v>1271956.512420153</v>
       </c>
       <c r="P358" t="n">
         <v>2300</v>
@@ -23093,10 +23093,10 @@
         <v>742</v>
       </c>
       <c r="N503" t="n">
-        <v>3181.9</v>
+        <v>3248.0517671518</v>
       </c>
       <c r="O503" t="n">
-        <v>2360969.8</v>
+        <v>2410054.411226636</v>
       </c>
       <c r="P503" t="n">
         <v>5100</v>
@@ -23751,10 +23751,10 @@
         <v>17</v>
       </c>
       <c r="N518" t="n">
-        <v>1952.66</v>
+        <v>1991.055</v>
       </c>
       <c r="O518" t="n">
-        <v>33195.22</v>
+        <v>33847.935</v>
       </c>
       <c r="P518" t="n">
         <v>3500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8550883392</v>
+        <v>6272.855106383</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.555265011</v>
+        <v>1794036.560425538</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -2074,10 +2074,10 @@
         <v>34</v>
       </c>
       <c r="N42" t="n">
-        <v>62706.203511236</v>
+        <v>61666.874241573</v>
       </c>
       <c r="O42" t="n">
-        <v>2132010.919382024</v>
+        <v>2096673.724213482</v>
       </c>
       <c r="P42" t="n">
         <v>98900</v>
@@ -2840,10 +2840,10 @@
         <v>148</v>
       </c>
       <c r="N60" t="n">
-        <v>1950.2144208289</v>
+        <v>1950.2140408627</v>
       </c>
       <c r="O60" t="n">
-        <v>288631.7342826772</v>
+        <v>288631.6780476796</v>
       </c>
       <c r="P60" t="n">
         <v>2900</v>
@@ -2927,10 +2927,10 @@
         <v>434</v>
       </c>
       <c r="N62" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.3101659125</v>
       </c>
       <c r="O62" t="n">
-        <v>2142792.611789459</v>
+        <v>2142792.612006025</v>
       </c>
       <c r="P62" t="n">
         <v>7500</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0632479443</v>
+        <v>1098.0633365079</v>
       </c>
       <c r="O70" t="n">
-        <v>129571.4632574274</v>
+        <v>129571.4737079322</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4299,10 +4299,10 @@
         <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>8701.9603960396</v>
+        <v>8214</v>
       </c>
       <c r="O93" t="n">
-        <v>17403.9207920792</v>
+        <v>16428</v>
       </c>
       <c r="P93" t="n">
         <v>7900</v>
@@ -4885,10 +4885,10 @@
         <v>435</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300509879</v>
+        <v>4890.9300510856</v>
       </c>
       <c r="O106" t="n">
-        <v>2127554.572179737</v>
+        <v>2127554.572222236</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
@@ -5333,10 +5333,10 @@
         <v>84</v>
       </c>
       <c r="N116" t="n">
-        <v>3240.8500492611</v>
+        <v>3240.8500493827</v>
       </c>
       <c r="O116" t="n">
-        <v>272231.4041379324</v>
+        <v>272231.4041481468</v>
       </c>
       <c r="P116" t="n">
         <v>5200</v>
@@ -5601,10 +5601,10 @@
         <v>289</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.462939145</v>
+        <v>12422.462940415</v>
       </c>
       <c r="O122" t="n">
-        <v>3590091.789412905</v>
+        <v>3590091.789779935</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5732,10 +5732,10 @@
         <v>2520</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.0232664284</v>
+        <v>3472.2761671707</v>
       </c>
       <c r="O125" t="n">
-        <v>8749498.631399568</v>
+        <v>8750135.941270163</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600139179</v>
+        <v>3041.660013947</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.666972868</v>
+        <v>1523871.666987447</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5912,10 +5912,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1712622683</v>
+        <v>4371.1712623543</v>
       </c>
       <c r="O129" t="n">
-        <v>4852000.101117813</v>
+        <v>4852000.101213273</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9242415885</v>
+        <v>1630.9242710358</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.5301434035</v>
+        <v>311506.5357678378</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.19440684</v>
+        <v>1550.1944427152</v>
       </c>
       <c r="O162" t="n">
-        <v>55806.99864624</v>
+        <v>55806.9999377472</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7456,10 +7456,10 @@
         <v>48</v>
       </c>
       <c r="N163" t="n">
-        <v>1579.3856972112</v>
+        <v>1579.38564</v>
       </c>
       <c r="O163" t="n">
-        <v>75810.51346613761</v>
+        <v>75810.51071999999</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -8797,10 +8797,10 @@
         <v>348</v>
       </c>
       <c r="N194" t="n">
-        <v>2029.8740827436</v>
+        <v>2029.8740849673</v>
       </c>
       <c r="O194" t="n">
-        <v>706396.1807947728</v>
+        <v>706396.1815686204</v>
       </c>
       <c r="P194" t="n">
         <v>3600</v>
@@ -9217,10 +9217,10 @@
         <v>24</v>
       </c>
       <c r="N204" t="n">
-        <v>3731.0244107744</v>
+        <v>3731.024440678</v>
       </c>
       <c r="O204" t="n">
-        <v>89544.5858585856</v>
+        <v>89544.58657627199</v>
       </c>
       <c r="P204" t="n">
         <v>5200</v>
@@ -9309,10 +9309,10 @@
         <v>1200</v>
       </c>
       <c r="N206" t="n">
-        <v>6207.9842244133</v>
+        <v>6207.9882238578</v>
       </c>
       <c r="O206" t="n">
-        <v>7449581.06929596</v>
+        <v>7449585.868629361</v>
       </c>
       <c r="P206" t="n">
         <v>9900</v>
@@ -10962,10 +10962,10 @@
         <v>97</v>
       </c>
       <c r="N244" t="n">
-        <v>7812.5456760049</v>
+        <v>7700</v>
       </c>
       <c r="O244" t="n">
-        <v>757816.9305724753</v>
+        <v>746900</v>
       </c>
       <c r="P244" t="n">
         <v>13900</v>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -12387,19 +12387,19 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N275" t="n">
         <v>4850</v>
       </c>
       <c r="O275" t="n">
-        <v>87300</v>
+        <v>67900</v>
       </c>
       <c r="P275" t="n">
         <v>7800</v>
       </c>
       <c r="Q275" t="n">
-        <v>140400</v>
+        <v>109200</v>
       </c>
     </row>
     <row r="276">
@@ -13922,10 +13922,10 @@
         <v>263</v>
       </c>
       <c r="N308" t="n">
-        <v>2252.2978962963</v>
+        <v>2252.2979080119</v>
       </c>
       <c r="O308" t="n">
-        <v>592354.346725927</v>
+        <v>592354.3498071297</v>
       </c>
       <c r="P308" t="n">
         <v>3900</v>
@@ -14523,10 +14523,10 @@
         <v>100</v>
       </c>
       <c r="N321" t="n">
-        <v>4907.82254</v>
+        <v>4907.8225450902</v>
       </c>
       <c r="O321" t="n">
-        <v>490782.254</v>
+        <v>490782.25450902</v>
       </c>
       <c r="P321" t="n">
         <v>8200</v>
@@ -14753,10 +14753,10 @@
         <v>84</v>
       </c>
       <c r="N326" t="n">
-        <v>3903.7388764045</v>
+        <v>3903.7389254766</v>
       </c>
       <c r="O326" t="n">
-        <v>327914.065617978</v>
+        <v>327914.0697400344</v>
       </c>
       <c r="P326" t="n">
         <v>7500</v>
@@ -16909,7 +16909,7 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>1164</v>
+        <v>1119</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
@@ -16918,19 +16918,19 @@
         <v>0</v>
       </c>
       <c r="M373" t="n">
-        <v>1164</v>
+        <v>1119</v>
       </c>
       <c r="N373" t="n">
         <v>5215</v>
       </c>
       <c r="O373" t="n">
-        <v>6070260</v>
+        <v>5835585</v>
       </c>
       <c r="P373" t="n">
         <v>8900</v>
       </c>
       <c r="Q373" t="n">
-        <v>10359600</v>
+        <v>9959100</v>
       </c>
     </row>
     <row r="374">
@@ -17825,10 +17825,10 @@
         <v>158</v>
       </c>
       <c r="N392" t="n">
-        <v>1690.870009298</v>
+        <v>1690.8700093371</v>
       </c>
       <c r="O392" t="n">
-        <v>267157.461469084</v>
+        <v>267157.4614752618</v>
       </c>
       <c r="P392" t="n">
         <v>3000</v>
@@ -18016,10 +18016,10 @@
         <v>1602</v>
       </c>
       <c r="N396" t="n">
-        <v>481.48791226097</v>
+        <v>481.48790873239</v>
       </c>
       <c r="O396" t="n">
-        <v>771343.6354420739</v>
+        <v>771343.6297892887</v>
       </c>
       <c r="P396" t="n">
         <v>650</v>
@@ -18202,10 +18202,10 @@
         <v>7734</v>
       </c>
       <c r="N400" t="n">
-        <v>711.33664937221</v>
+        <v>711.3366477489</v>
       </c>
       <c r="O400" t="n">
-        <v>5501477.646244672</v>
+        <v>5501477.633689992</v>
       </c>
       <c r="P400" t="n">
         <v>900</v>
@@ -18433,10 +18433,10 @@
         <v>45</v>
       </c>
       <c r="N405" t="n">
-        <v>4032.396796875</v>
+        <v>4032.3967885117</v>
       </c>
       <c r="O405" t="n">
-        <v>181457.855859375</v>
+        <v>181457.8554830265</v>
       </c>
       <c r="P405" t="n">
         <v>4200</v>
@@ -18854,10 +18854,10 @@
         <v>2</v>
       </c>
       <c r="N414" t="n">
-        <v>3110.8380493577</v>
+        <v>3110.8379516019</v>
       </c>
       <c r="O414" t="n">
-        <v>6221.6760987154</v>
+        <v>6221.6759032038</v>
       </c>
       <c r="P414" t="n">
         <v>4500</v>
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="J433" t="n">
-        <v>823</v>
+        <v>761</v>
       </c>
       <c r="K433" t="n">
         <v>0</v>
@@ -19736,19 +19736,19 @@
         <v>0</v>
       </c>
       <c r="M433" t="n">
-        <v>823</v>
+        <v>761</v>
       </c>
       <c r="N433" t="n">
         <v>1755.74</v>
       </c>
       <c r="O433" t="n">
-        <v>1444974.02</v>
+        <v>1336118.14</v>
       </c>
       <c r="P433" t="n">
         <v>1500</v>
       </c>
       <c r="Q433" t="n">
-        <v>1234500</v>
+        <v>1141500</v>
       </c>
     </row>
     <row r="434">
@@ -23093,10 +23093,10 @@
         <v>742</v>
       </c>
       <c r="N503" t="n">
-        <v>3248.0517671518</v>
+        <v>3181.9</v>
       </c>
       <c r="O503" t="n">
-        <v>2410054.411226636</v>
+        <v>2360969.8</v>
       </c>
       <c r="P503" t="n">
         <v>5100</v>
@@ -23178,10 +23178,10 @@
         <v>-72</v>
       </c>
       <c r="N505" t="n">
-        <v>1794.287966004</v>
+        <v>1794.2879651247</v>
       </c>
       <c r="O505" t="n">
-        <v>-129188.733552288</v>
+        <v>-129188.7334889784</v>
       </c>
       <c r="P505" t="n">
         <v>1600</v>
@@ -23751,10 +23751,10 @@
         <v>17</v>
       </c>
       <c r="N518" t="n">
-        <v>1991.055</v>
+        <v>1952.66</v>
       </c>
       <c r="O518" t="n">
-        <v>33847.935</v>
+        <v>33195.22</v>
       </c>
       <c r="P518" t="n">
         <v>3500</v>
@@ -24977,10 +24977,10 @@
         <v>93</v>
       </c>
       <c r="N544" t="n">
-        <v>3982.6707692308</v>
+        <v>3982.670776699</v>
       </c>
       <c r="O544" t="n">
-        <v>370388.3815384644</v>
+        <v>370388.382233007</v>
       </c>
       <c r="P544" t="n">
         <v>10900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0633365079</v>
+        <v>1098.0633810433</v>
       </c>
       <c r="O70" t="n">
-        <v>129571.4737079322</v>
+        <v>129571.4789631094</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4706,10 +4706,10 @@
         <v>179</v>
       </c>
       <c r="N102" t="n">
-        <v>3795.7100076147</v>
+        <v>3795.7100076161</v>
       </c>
       <c r="O102" t="n">
-        <v>679432.0913630313</v>
+        <v>679432.0913632819</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1944427152</v>
+        <v>1550.1944587288</v>
       </c>
       <c r="O162" t="n">
-        <v>55806.9999377472</v>
+        <v>55807.0005142368</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7456,10 +7456,10 @@
         <v>48</v>
       </c>
       <c r="N163" t="n">
-        <v>1579.38564</v>
+        <v>1579.3847234043</v>
       </c>
       <c r="O163" t="n">
-        <v>75810.51071999999</v>
+        <v>75810.4667234064</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -8797,10 +8797,10 @@
         <v>348</v>
       </c>
       <c r="N194" t="n">
-        <v>2029.8740849673</v>
+        <v>2029.874091653</v>
       </c>
       <c r="O194" t="n">
-        <v>706396.1815686204</v>
+        <v>706396.183895244</v>
       </c>
       <c r="P194" t="n">
         <v>3600</v>
@@ -9217,10 +9217,10 @@
         <v>24</v>
       </c>
       <c r="N204" t="n">
-        <v>3731.024440678</v>
+        <v>3731.0244863014</v>
       </c>
       <c r="O204" t="n">
-        <v>89544.58657627199</v>
+        <v>89544.5876712336</v>
       </c>
       <c r="P204" t="n">
         <v>5200</v>
@@ -14523,10 +14523,10 @@
         <v>100</v>
       </c>
       <c r="N321" t="n">
-        <v>4907.8225450902</v>
+        <v>4907.8225656566</v>
       </c>
       <c r="O321" t="n">
-        <v>490782.25450902</v>
+        <v>490782.25656566</v>
       </c>
       <c r="P321" t="n">
         <v>8200</v>
@@ -16220,10 +16220,10 @@
         <v>839</v>
       </c>
       <c r="N358" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O358" t="n">
-        <v>1271956.512420153</v>
+        <v>1271956.511994948</v>
       </c>
       <c r="P358" t="n">
         <v>2300</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1588,10 +1588,10 @@
         <v>89</v>
       </c>
       <c r="N30" t="n">
-        <v>3910.6279405034</v>
+        <v>3910.6279357798</v>
       </c>
       <c r="O30" t="n">
-        <v>348045.8867048026</v>
+        <v>348045.8862844022</v>
       </c>
       <c r="P30" t="n">
         <v>9100</v>
@@ -2536,10 +2536,10 @@
         <v>178</v>
       </c>
       <c r="N53" t="n">
-        <v>3340.6800838574</v>
+        <v>3340.6800840336</v>
       </c>
       <c r="O53" t="n">
-        <v>594641.0549266172</v>
+        <v>594641.0549579808</v>
       </c>
       <c r="P53" t="n">
         <v>7100</v>
@@ -2840,10 +2840,10 @@
         <v>148</v>
       </c>
       <c r="N60" t="n">
-        <v>1950.2140408627</v>
+        <v>1950.2139862543</v>
       </c>
       <c r="O60" t="n">
-        <v>288631.6780476796</v>
+        <v>288631.6699656364</v>
       </c>
       <c r="P60" t="n">
         <v>2900</v>
@@ -2927,10 +2927,10 @@
         <v>434</v>
       </c>
       <c r="N62" t="n">
-        <v>4937.3101659125</v>
+        <v>4937.3101654135</v>
       </c>
       <c r="O62" t="n">
-        <v>2142792.612006025</v>
+        <v>2142792.611789459</v>
       </c>
       <c r="P62" t="n">
         <v>7500</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0633810433</v>
+        <v>1098.0636670959</v>
       </c>
       <c r="O70" t="n">
-        <v>129571.4789631094</v>
+        <v>129571.5127173162</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -3630,10 +3630,10 @@
         <v>75</v>
       </c>
       <c r="N78" t="n">
-        <v>18694.410088692</v>
+        <v>18694.410088889</v>
       </c>
       <c r="O78" t="n">
-        <v>1402080.7566519</v>
+        <v>1402080.756666675</v>
       </c>
       <c r="P78" t="n">
         <v>29900</v>
@@ -4885,10 +4885,10 @@
         <v>435</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300510856</v>
+        <v>4890.9300511182</v>
       </c>
       <c r="O106" t="n">
-        <v>2127554.572222236</v>
+        <v>2127554.572236417</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
@@ -5333,10 +5333,10 @@
         <v>84</v>
       </c>
       <c r="N116" t="n">
-        <v>3240.8500493827</v>
+        <v>3240.8500508906</v>
       </c>
       <c r="O116" t="n">
-        <v>272231.4041481468</v>
+        <v>272231.4042748104</v>
       </c>
       <c r="P116" t="n">
         <v>5200</v>
@@ -5601,10 +5601,10 @@
         <v>289</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.462940415</v>
+        <v>12422.462941685</v>
       </c>
       <c r="O122" t="n">
-        <v>3590091.789779935</v>
+        <v>3590091.790146965</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.660013947</v>
+        <v>3041.6600139665</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.666987447</v>
+        <v>1523871.666997217</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5912,10 +5912,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1712623543</v>
+        <v>4371.1712626125</v>
       </c>
       <c r="O129" t="n">
-        <v>4852000.101213273</v>
+        <v>4852000.101499875</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9242710358</v>
+        <v>1630.9243202247</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.5357678378</v>
+        <v>311506.5451629177</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1944587288</v>
+        <v>1550.1945107573</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.0005142368</v>
+        <v>55807.00238726279</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7456,10 +7456,10 @@
         <v>48</v>
       </c>
       <c r="N163" t="n">
-        <v>1579.3847234043</v>
+        <v>1579.3845258621</v>
       </c>
       <c r="O163" t="n">
-        <v>75810.4667234064</v>
+        <v>75810.45724138079</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -8797,10 +8797,10 @@
         <v>348</v>
       </c>
       <c r="N194" t="n">
-        <v>2029.874091653</v>
+        <v>2029.8740983607</v>
       </c>
       <c r="O194" t="n">
-        <v>706396.183895244</v>
+        <v>706396.1862295236</v>
       </c>
       <c r="P194" t="n">
         <v>3600</v>
@@ -8838,10 +8838,10 @@
         <v>157</v>
       </c>
       <c r="N195" t="n">
-        <v>22485.695494368</v>
+        <v>22485.695483061</v>
       </c>
       <c r="O195" t="n">
-        <v>3530254.192615776</v>
+        <v>3530254.190840577</v>
       </c>
       <c r="P195" t="n">
         <v>36500</v>
@@ -9002,10 +9002,10 @@
         <v>170</v>
       </c>
       <c r="N199" t="n">
-        <v>2680.7396945137</v>
+        <v>2680.7396939413</v>
       </c>
       <c r="O199" t="n">
-        <v>455725.7480673291</v>
+        <v>455725.747970021</v>
       </c>
       <c r="P199" t="n">
         <v>4900</v>
@@ -9824,10 +9824,10 @@
         <v>37</v>
       </c>
       <c r="N218" t="n">
-        <v>27123.764869739</v>
+        <v>27123.764849095</v>
       </c>
       <c r="O218" t="n">
-        <v>1003579.300180343</v>
+        <v>1003579.299416515</v>
       </c>
       <c r="P218" t="n">
         <v>44500</v>
@@ -11654,10 +11654,10 @@
         <v>952</v>
       </c>
       <c r="N259" t="n">
-        <v>1778.47280077</v>
+        <v>1778.4728156749</v>
       </c>
       <c r="O259" t="n">
-        <v>1693106.10633304</v>
+        <v>1693106.120522505</v>
       </c>
       <c r="P259" t="n">
         <v>4900</v>
@@ -13922,10 +13922,10 @@
         <v>263</v>
       </c>
       <c r="N308" t="n">
-        <v>2252.2979080119</v>
+        <v>2252.2979790419</v>
       </c>
       <c r="O308" t="n">
-        <v>592354.3498071297</v>
+        <v>592354.3684880197</v>
       </c>
       <c r="P308" t="n">
         <v>3900</v>
@@ -14753,10 +14753,10 @@
         <v>84</v>
       </c>
       <c r="N326" t="n">
-        <v>3903.7389254766</v>
+        <v>3903.7390742358</v>
       </c>
       <c r="O326" t="n">
-        <v>327914.0697400344</v>
+        <v>327914.0822358072</v>
       </c>
       <c r="P326" t="n">
         <v>7500</v>
@@ -16024,7 +16024,7 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>1758</v>
+        <v>1748</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
@@ -16033,19 +16033,19 @@
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>1758</v>
+        <v>1748</v>
       </c>
       <c r="N354" t="n">
         <v>1326</v>
       </c>
       <c r="O354" t="n">
-        <v>2331108</v>
+        <v>2317848</v>
       </c>
       <c r="P354" t="n">
         <v>2500</v>
       </c>
       <c r="Q354" t="n">
-        <v>4395000</v>
+        <v>4370000</v>
       </c>
     </row>
     <row r="355">
@@ -16220,10 +16220,10 @@
         <v>839</v>
       </c>
       <c r="N358" t="n">
-        <v>1516.0387508879</v>
+        <v>1516.0387464358</v>
       </c>
       <c r="O358" t="n">
-        <v>1271956.511994948</v>
+        <v>1271956.508259636</v>
       </c>
       <c r="P358" t="n">
         <v>2300</v>
@@ -16627,10 +16627,10 @@
         <v>2063</v>
       </c>
       <c r="N367" t="n">
-        <v>692.1524039631501</v>
+        <v>692.15240898798</v>
       </c>
       <c r="O367" t="n">
-        <v>1427910.409375979</v>
+        <v>1427910.419742203</v>
       </c>
       <c r="P367" t="n">
         <v>1200</v>
@@ -16909,7 +16909,7 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>1119</v>
+        <v>1074</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
@@ -16918,19 +16918,19 @@
         <v>0</v>
       </c>
       <c r="M373" t="n">
-        <v>1119</v>
+        <v>1074</v>
       </c>
       <c r="N373" t="n">
         <v>5215</v>
       </c>
       <c r="O373" t="n">
-        <v>5835585</v>
+        <v>5600910</v>
       </c>
       <c r="P373" t="n">
         <v>8900</v>
       </c>
       <c r="Q373" t="n">
-        <v>9959100</v>
+        <v>9558600</v>
       </c>
     </row>
     <row r="374">
@@ -18854,10 +18854,10 @@
         <v>2</v>
       </c>
       <c r="N414" t="n">
-        <v>3110.8379516019</v>
+        <v>3110.8379310345</v>
       </c>
       <c r="O414" t="n">
-        <v>6221.6759032038</v>
+        <v>6221.675862069</v>
       </c>
       <c r="P414" t="n">
         <v>4500</v>
@@ -19044,10 +19044,10 @@
         <v>127</v>
       </c>
       <c r="N418" t="n">
-        <v>3182.2511257036</v>
+        <v>3182.2511299435</v>
       </c>
       <c r="O418" t="n">
-        <v>404145.8929643572</v>
+        <v>404145.8935028245</v>
       </c>
       <c r="P418" t="n">
         <v>6900</v>
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="J419" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K419" t="n">
         <v>0</v>
@@ -19087,19 +19087,19 @@
         <v>0</v>
       </c>
       <c r="M419" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="N419" t="n">
         <v>3584.72</v>
       </c>
       <c r="O419" t="n">
-        <v>60940.24</v>
+        <v>35847.2</v>
       </c>
       <c r="P419" t="n">
         <v>3700</v>
       </c>
       <c r="Q419" t="n">
-        <v>62900</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="420">
@@ -19228,10 +19228,10 @@
         <v>4</v>
       </c>
       <c r="N422" t="n">
-        <v>2501.3845177665</v>
+        <v>2501.3844329897</v>
       </c>
       <c r="O422" t="n">
-        <v>10005.538071066</v>
+        <v>10005.5377319588</v>
       </c>
       <c r="P422" t="n">
         <v>4100</v>
@@ -19932,10 +19932,10 @@
         <v>54</v>
       </c>
       <c r="N437" t="n">
-        <v>2098.4051335312</v>
+        <v>2098.4051488095</v>
       </c>
       <c r="O437" t="n">
-        <v>113313.8772106848</v>
+        <v>113313.878035713</v>
       </c>
       <c r="P437" t="n">
         <v>9500</v>
@@ -21921,10 +21921,10 @@
         <v>4</v>
       </c>
       <c r="N478" t="n">
-        <v>8931.441052631601</v>
+        <v>8931.4411111111</v>
       </c>
       <c r="O478" t="n">
-        <v>35725.7642105264</v>
+        <v>35725.7644444444</v>
       </c>
       <c r="P478" t="n">
         <v>19900</v>
@@ -22451,10 +22451,10 @@
         <v>1061</v>
       </c>
       <c r="N489" t="n">
-        <v>665.3238408644399</v>
+        <v>665.3238427518399</v>
       </c>
       <c r="O489" t="n">
-        <v>705908.5951571708</v>
+        <v>705908.5971597022</v>
       </c>
       <c r="P489" t="n">
         <v>2900</v>
@@ -22693,10 +22693,10 @@
         <v>288</v>
       </c>
       <c r="N494" t="n">
-        <v>430.60997569866</v>
+        <v>430.60997568389</v>
       </c>
       <c r="O494" t="n">
-        <v>124015.6730012141</v>
+        <v>124015.6729969603</v>
       </c>
       <c r="P494" t="n">
         <v>2200</v>
@@ -22964,10 +22964,10 @@
         <v>34</v>
       </c>
       <c r="N500" t="n">
-        <v>4703.6208791209</v>
+        <v>4703.6208888889</v>
       </c>
       <c r="O500" t="n">
-        <v>159923.1098901106</v>
+        <v>159923.1102222226</v>
       </c>
       <c r="P500" t="n">
         <v>5900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -751,10 +751,10 @@
         <v>402</v>
       </c>
       <c r="N9" t="n">
-        <v>4072</v>
+        <v>4088.8962655602</v>
       </c>
       <c r="O9" t="n">
-        <v>1636944</v>
+        <v>1643736.2987552</v>
       </c>
       <c r="P9" t="n">
         <v>7500</v>
@@ -2840,10 +2840,10 @@
         <v>148</v>
       </c>
       <c r="N60" t="n">
-        <v>1950.2139862543</v>
+        <v>1950.2139585731</v>
       </c>
       <c r="O60" t="n">
-        <v>288631.6699656364</v>
+        <v>288631.6658688188</v>
       </c>
       <c r="P60" t="n">
         <v>2900</v>
@@ -2927,10 +2927,10 @@
         <v>434</v>
       </c>
       <c r="N62" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.310165538</v>
       </c>
       <c r="O62" t="n">
-        <v>2142792.611789459</v>
+        <v>2142792.611843492</v>
       </c>
       <c r="P62" t="n">
         <v>7500</v>
@@ -3507,10 +3507,10 @@
         <v>218</v>
       </c>
       <c r="N75" t="n">
-        <v>13593.35</v>
+        <v>13626.343567961</v>
       </c>
       <c r="O75" t="n">
-        <v>2963350.3</v>
+        <v>2970542.897815498</v>
       </c>
       <c r="P75" t="n">
         <v>25500</v>
@@ -4578,10 +4578,10 @@
         <v>507</v>
       </c>
       <c r="N99" t="n">
-        <v>6507</v>
+        <v>6513.4596293845</v>
       </c>
       <c r="O99" t="n">
-        <v>3299049</v>
+        <v>3302324.032097941</v>
       </c>
       <c r="P99" t="n">
         <v>9900</v>
@@ -5115,10 +5115,10 @@
         <v>2</v>
       </c>
       <c r="N111" t="n">
-        <v>8662</v>
+        <v>8680.102403343801</v>
       </c>
       <c r="O111" t="n">
-        <v>17324</v>
+        <v>17360.2048066876</v>
       </c>
       <c r="P111" t="n">
         <v>14200</v>
@@ -5500,22 +5500,22 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M120" t="n">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="N120" t="n">
-        <v>2665.4</v>
+        <v>2668.7380087664</v>
       </c>
       <c r="O120" t="n">
-        <v>1732510</v>
+        <v>1729342.229680627</v>
       </c>
       <c r="P120" t="n">
         <v>20900</v>
       </c>
       <c r="Q120" t="n">
-        <v>13585000</v>
+        <v>13543200</v>
       </c>
     </row>
     <row r="121">
@@ -5726,22 +5726,22 @@
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M125" t="n">
-        <v>2520</v>
+        <v>2442</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2761671707</v>
+        <v>3490.9933434692</v>
       </c>
       <c r="O125" t="n">
-        <v>8750135.941270163</v>
+        <v>8525005.744751787</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
       </c>
       <c r="Q125" t="n">
-        <v>14868000</v>
+        <v>14407800</v>
       </c>
     </row>
     <row r="126">
@@ -6219,10 +6219,10 @@
         <v>267</v>
       </c>
       <c r="N136" t="n">
-        <v>6242.93</v>
+        <v>6260.7161253561</v>
       </c>
       <c r="O136" t="n">
-        <v>1666862.31</v>
+        <v>1671611.205470079</v>
       </c>
       <c r="P136" t="n">
         <v>10400</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9243202247</v>
+        <v>1630.9243287363</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.5451629177</v>
+        <v>311506.5467886333</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1945107573</v>
+        <v>1550.1945200974</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.00238726279</v>
+        <v>55807.0027235064</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -8797,10 +8797,10 @@
         <v>348</v>
       </c>
       <c r="N194" t="n">
-        <v>2029.8740983607</v>
+        <v>2029.8741050903</v>
       </c>
       <c r="O194" t="n">
-        <v>706396.1862295236</v>
+        <v>706396.1885714243</v>
       </c>
       <c r="P194" t="n">
         <v>3600</v>
@@ -9690,22 +9690,22 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M215" t="n">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="N215" t="n">
-        <v>4814.2679269747</v>
+        <v>4817.516083662</v>
       </c>
       <c r="O215" t="n">
-        <v>3466272.907421784</v>
+        <v>3405983.871149034</v>
       </c>
       <c r="P215" t="n">
         <v>9900</v>
       </c>
       <c r="Q215" t="n">
-        <v>7128000</v>
+        <v>6999300</v>
       </c>
     </row>
     <row r="216">
@@ -9859,22 +9859,22 @@
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M219" t="n">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="N219" t="n">
-        <v>4100.45</v>
+        <v>4114.8123467601</v>
       </c>
       <c r="O219" t="n">
-        <v>955404.85</v>
+        <v>934062.4027145427</v>
       </c>
       <c r="P219" t="n">
         <v>26900</v>
       </c>
       <c r="Q219" t="n">
-        <v>6267700</v>
+        <v>6106300</v>
       </c>
     </row>
     <row r="220">
@@ -10249,10 +10249,10 @@
         <v>180</v>
       </c>
       <c r="N228" t="n">
-        <v>7969.950169361</v>
+        <v>7988.3991280864</v>
       </c>
       <c r="O228" t="n">
-        <v>1434591.03048498</v>
+        <v>1437911.843055552</v>
       </c>
       <c r="P228" t="n">
         <v>12900</v>
@@ -13186,10 +13186,10 @@
         <v>42</v>
       </c>
       <c r="N292" t="n">
-        <v>13687</v>
+        <v>13795.340369393</v>
       </c>
       <c r="O292" t="n">
-        <v>574854</v>
+        <v>579404.2955145059</v>
       </c>
       <c r="P292" t="n">
         <v>21900</v>
@@ -13646,10 +13646,10 @@
         <v>348</v>
       </c>
       <c r="N302" t="n">
-        <v>8858.16</v>
+        <v>8872.673642818099</v>
       </c>
       <c r="O302" t="n">
-        <v>3082639.68</v>
+        <v>3087690.427700698</v>
       </c>
       <c r="P302" t="n">
         <v>15500</v>
@@ -14753,10 +14753,10 @@
         <v>84</v>
       </c>
       <c r="N326" t="n">
-        <v>3903.7390742358</v>
+        <v>3903.7391243433</v>
       </c>
       <c r="O326" t="n">
-        <v>327914.0822358072</v>
+        <v>327914.0864448372</v>
       </c>
       <c r="P326" t="n">
         <v>7500</v>
@@ -14799,10 +14799,10 @@
         <v>13</v>
       </c>
       <c r="N327" t="n">
-        <v>33000</v>
+        <v>33980.198019802</v>
       </c>
       <c r="O327" t="n">
-        <v>429000</v>
+        <v>441742.574257426</v>
       </c>
       <c r="P327" t="n">
         <v>52900</v>
@@ -14983,10 +14983,10 @@
         <v>438</v>
       </c>
       <c r="N331" t="n">
-        <v>6849.2</v>
+        <v>6855.7044634378</v>
       </c>
       <c r="O331" t="n">
-        <v>2999949.6</v>
+        <v>3002798.554985757</v>
       </c>
       <c r="P331" t="n">
         <v>11500</v>
@@ -16220,10 +16220,10 @@
         <v>839</v>
       </c>
       <c r="N358" t="n">
-        <v>1516.0387464358</v>
+        <v>1516.0387455416</v>
       </c>
       <c r="O358" t="n">
-        <v>1271956.508259636</v>
+        <v>1271956.507509402</v>
       </c>
       <c r="P358" t="n">
         <v>2300</v>
@@ -16768,22 +16768,22 @@
         <v>0</v>
       </c>
       <c r="L370" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M370" t="n">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="N370" t="n">
-        <v>13518</v>
+        <v>13559.454697519</v>
       </c>
       <c r="O370" t="n">
-        <v>8110800</v>
+        <v>7986518.816838691</v>
       </c>
       <c r="P370" t="n">
         <v>21900</v>
       </c>
       <c r="Q370" t="n">
-        <v>13140000</v>
+        <v>12899100</v>
       </c>
     </row>
     <row r="371">
@@ -16817,22 +16817,22 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M371" t="n">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="N371" t="n">
-        <v>9736</v>
+        <v>9760.865567680499</v>
       </c>
       <c r="O371" t="n">
-        <v>7009920</v>
+        <v>6920453.687485474</v>
       </c>
       <c r="P371" t="n">
         <v>15900</v>
       </c>
       <c r="Q371" t="n">
-        <v>11448000</v>
+        <v>11273100</v>
       </c>
     </row>
     <row r="372">
@@ -16872,10 +16872,10 @@
         <v>48</v>
       </c>
       <c r="N372" t="n">
-        <v>44470</v>
+        <v>45032.911392405</v>
       </c>
       <c r="O372" t="n">
-        <v>2134560</v>
+        <v>2161579.74683544</v>
       </c>
       <c r="P372" t="n">
         <v>71900</v>
@@ -16915,22 +16915,22 @@
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M373" t="n">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="N373" t="n">
-        <v>5215</v>
+        <v>5227.7693437806</v>
       </c>
       <c r="O373" t="n">
-        <v>5600910</v>
+        <v>5536207.735063655</v>
       </c>
       <c r="P373" t="n">
         <v>8900</v>
       </c>
       <c r="Q373" t="n">
-        <v>9558600</v>
+        <v>9425100</v>
       </c>
     </row>
     <row r="374">
@@ -18854,10 +18854,10 @@
         <v>2</v>
       </c>
       <c r="N414" t="n">
-        <v>3110.8379310345</v>
+        <v>3110.8378564067</v>
       </c>
       <c r="O414" t="n">
-        <v>6221.675862069</v>
+        <v>6221.6757128134</v>
       </c>
       <c r="P414" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -751,10 +751,10 @@
         <v>402</v>
       </c>
       <c r="N9" t="n">
-        <v>4088.8962655602</v>
+        <v>4072</v>
       </c>
       <c r="O9" t="n">
-        <v>1643736.2987552</v>
+        <v>1636944</v>
       </c>
       <c r="P9" t="n">
         <v>7500</v>
@@ -2799,10 +2799,10 @@
         <v>122</v>
       </c>
       <c r="N59" t="n">
-        <v>10897.588251121</v>
+        <v>10752.93</v>
       </c>
       <c r="O59" t="n">
-        <v>1329505.766636762</v>
+        <v>1311857.46</v>
       </c>
       <c r="P59" t="n">
         <v>18400</v>
@@ -3548,10 +3548,10 @@
         <v>98</v>
       </c>
       <c r="N76" t="n">
-        <v>17263.007447496</v>
+        <v>17207.41</v>
       </c>
       <c r="O76" t="n">
-        <v>1691774.729854608</v>
+        <v>1686326.18</v>
       </c>
       <c r="P76" t="n">
         <v>20000</v>
@@ -5642,10 +5642,10 @@
         <v>132</v>
       </c>
       <c r="N123" t="n">
-        <v>2718.841814346</v>
+        <v>2696.09</v>
       </c>
       <c r="O123" t="n">
-        <v>358887.119493672</v>
+        <v>355883.88</v>
       </c>
       <c r="P123" t="n">
         <v>8200</v>
@@ -6219,10 +6219,10 @@
         <v>267</v>
       </c>
       <c r="N136" t="n">
-        <v>6260.7161253561</v>
+        <v>6242.93</v>
       </c>
       <c r="O136" t="n">
-        <v>1671611.205470079</v>
+        <v>1666862.31</v>
       </c>
       <c r="P136" t="n">
         <v>10400</v>
@@ -7541,10 +7541,10 @@
         <v>48</v>
       </c>
       <c r="N165" t="n">
-        <v>11749.140699301</v>
+        <v>11507.72</v>
       </c>
       <c r="O165" t="n">
-        <v>563958.753566448</v>
+        <v>552370.5599999999</v>
       </c>
       <c r="P165" t="n">
         <v>25800</v>
@@ -8510,10 +8510,10 @@
         <v>1</v>
       </c>
       <c r="N187" t="n">
-        <v>2701.9479396985</v>
+        <v>2661.82</v>
       </c>
       <c r="O187" t="n">
-        <v>2701.9479396985</v>
+        <v>2661.82</v>
       </c>
       <c r="P187" t="n">
         <v>3200</v>
@@ -9824,10 +9824,10 @@
         <v>37</v>
       </c>
       <c r="N218" t="n">
-        <v>27233.355818182</v>
+        <v>27123.764828283</v>
       </c>
       <c r="O218" t="n">
-        <v>1007634.165272734</v>
+        <v>1003579.298646471</v>
       </c>
       <c r="P218" t="n">
         <v>44500</v>
@@ -10249,10 +10249,10 @@
         <v>180</v>
       </c>
       <c r="N228" t="n">
-        <v>7988.3991280864</v>
+        <v>7969.9501697531</v>
       </c>
       <c r="O228" t="n">
-        <v>1437911.843055552</v>
+        <v>1434591.030555558</v>
       </c>
       <c r="P228" t="n">
         <v>12900</v>
@@ -11106,10 +11106,10 @@
         <v>125</v>
       </c>
       <c r="N247" t="n">
-        <v>9379.0968275862</v>
+        <v>9188.98</v>
       </c>
       <c r="O247" t="n">
-        <v>1172387.103448275</v>
+        <v>1148622.5</v>
       </c>
       <c r="P247" t="n">
         <v>12900</v>
@@ -11746,10 +11746,10 @@
         <v>62</v>
       </c>
       <c r="N261" t="n">
-        <v>16092.984749455</v>
+        <v>16058</v>
       </c>
       <c r="O261" t="n">
-        <v>997765.05446621</v>
+        <v>995596</v>
       </c>
       <c r="P261" t="n">
         <v>25900</v>
@@ -11792,10 +11792,10 @@
         <v>24</v>
       </c>
       <c r="N262" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O262" t="n">
-        <v>613845.366181416</v>
+        <v>612816</v>
       </c>
       <c r="P262" t="n">
         <v>40900</v>
@@ -12022,10 +12022,10 @@
         <v>26</v>
       </c>
       <c r="N267" t="n">
-        <v>9927.272727272701</v>
+        <v>9750</v>
       </c>
       <c r="O267" t="n">
-        <v>258109.0909090902</v>
+        <v>253500</v>
       </c>
       <c r="P267" t="n">
         <v>15600</v>
@@ -12160,10 +12160,10 @@
         <v>61</v>
       </c>
       <c r="N270" t="n">
-        <v>7278.6868686869</v>
+        <v>7230</v>
       </c>
       <c r="O270" t="n">
-        <v>443999.8989899009</v>
+        <v>441030</v>
       </c>
       <c r="P270" t="n">
         <v>11600</v>
@@ -13140,10 +13140,10 @@
         <v>42</v>
       </c>
       <c r="N291" t="n">
-        <v>13795.055263158</v>
+        <v>13687</v>
       </c>
       <c r="O291" t="n">
-        <v>579392.321052636</v>
+        <v>574854</v>
       </c>
       <c r="P291" t="n">
         <v>21900</v>
@@ -14385,10 +14385,10 @@
         <v>44</v>
       </c>
       <c r="N318" t="n">
-        <v>3412.5148218527</v>
+        <v>3396.38</v>
       </c>
       <c r="O318" t="n">
-        <v>150150.6521615188</v>
+        <v>149440.72</v>
       </c>
       <c r="P318" t="n">
         <v>6500</v>
@@ -14615,10 +14615,10 @@
         <v>39</v>
       </c>
       <c r="N323" t="n">
-        <v>13233.257042254</v>
+        <v>13210</v>
       </c>
       <c r="O323" t="n">
-        <v>516097.024647906</v>
+        <v>515190</v>
       </c>
       <c r="P323" t="n">
         <v>23900</v>
@@ -14891,10 +14891,10 @@
         <v>120</v>
       </c>
       <c r="N329" t="n">
-        <v>2657.2435094002</v>
+        <v>2629</v>
       </c>
       <c r="O329" t="n">
-        <v>318869.221128024</v>
+        <v>315480</v>
       </c>
       <c r="P329" t="n">
         <v>4500</v>
@@ -14937,10 +14937,10 @@
         <v>438</v>
       </c>
       <c r="N330" t="n">
-        <v>6881.8463298379</v>
+        <v>6849.2</v>
       </c>
       <c r="O330" t="n">
-        <v>3014248.692469</v>
+        <v>2999949.6</v>
       </c>
       <c r="P330" t="n">
         <v>11500</v>
@@ -15397,10 +15397,10 @@
         <v>109</v>
       </c>
       <c r="N340" t="n">
-        <v>11478.737327189</v>
+        <v>11348</v>
       </c>
       <c r="O340" t="n">
-        <v>1251182.368663601</v>
+        <v>1236932</v>
       </c>
       <c r="P340" t="n">
         <v>19900</v>
@@ -16082,10 +16082,10 @@
         <v>1189</v>
       </c>
       <c r="N355" t="n">
-        <v>3823.6153319644</v>
+        <v>3821</v>
       </c>
       <c r="O355" t="n">
-        <v>4546278.629705671</v>
+        <v>4543169</v>
       </c>
       <c r="P355" t="n">
         <v>5900</v>
@@ -16128,10 +16128,10 @@
         <v>81</v>
       </c>
       <c r="N356" t="n">
-        <v>7295.3326848249</v>
+        <v>7253</v>
       </c>
       <c r="O356" t="n">
-        <v>590921.9474708169</v>
+        <v>587493</v>
       </c>
       <c r="P356" t="n">
         <v>11900</v>
@@ -17359,10 +17359,10 @@
         <v>780</v>
       </c>
       <c r="N382" t="n">
-        <v>1537.958258381</v>
+        <v>1530.4499182339</v>
       </c>
       <c r="O382" t="n">
-        <v>1199607.44153718</v>
+        <v>1193750.936222442</v>
       </c>
       <c r="P382" t="n">
         <v>2600</v>
@@ -21148,10 +21148,10 @@
         <v>240</v>
       </c>
       <c r="N462" t="n">
-        <v>5370.6369361702</v>
+        <v>5347.88</v>
       </c>
       <c r="O462" t="n">
-        <v>1288952.864680848</v>
+        <v>1283491.2</v>
       </c>
       <c r="P462" t="n">
         <v>7900</v>
@@ -21197,10 +21197,10 @@
         <v>231</v>
       </c>
       <c r="N463" t="n">
-        <v>4593.1990728477</v>
+        <v>4578.04</v>
       </c>
       <c r="O463" t="n">
-        <v>1061028.985827819</v>
+        <v>1057527.24</v>
       </c>
       <c r="P463" t="n">
         <v>7500</v>
@@ -21532,10 +21532,10 @@
         <v>26</v>
       </c>
       <c r="N470" t="n">
-        <v>10912.902659574</v>
+        <v>10798.03</v>
       </c>
       <c r="O470" t="n">
-        <v>283735.469148924</v>
+        <v>280748.78</v>
       </c>
       <c r="P470" t="n">
         <v>45000</v>
@@ -22310,10 +22310,10 @@
         <v>67</v>
       </c>
       <c r="N486" t="n">
-        <v>44654.875337423</v>
+        <v>44113.604171779</v>
       </c>
       <c r="O486" t="n">
-        <v>2991876.647607341</v>
+        <v>2955611.479509193</v>
       </c>
       <c r="P486" t="n">
         <v>71900</v>
@@ -23047,10 +23047,10 @@
         <v>742</v>
       </c>
       <c r="N502" t="n">
-        <v>3186.7802147239</v>
+        <v>3181.9</v>
       </c>
       <c r="O502" t="n">
-        <v>2364590.919325134</v>
+        <v>2360969.8</v>
       </c>
       <c r="P502" t="n">
         <v>5100</v>
@@ -23577,10 +23577,10 @@
         <v>30</v>
       </c>
       <c r="N514" t="n">
-        <v>2655.5149832776</v>
+        <v>2644.9</v>
       </c>
       <c r="O514" t="n">
-        <v>79665.449498328</v>
+        <v>79347</v>
       </c>
       <c r="P514" t="n">
         <v>3900</v>
@@ -24645,10 +24645,10 @@
         <v>169</v>
       </c>
       <c r="N537" t="n">
-        <v>1494.6085714286</v>
+        <v>1482.84</v>
       </c>
       <c r="O537" t="n">
-        <v>252588.8485714334</v>
+        <v>250599.96</v>
       </c>
       <c r="P537" t="n">
         <v>6500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q560"/>
+  <dimension ref="A1:Q558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>572</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464140994</v>
+        <v>3376.7464051196</v>
       </c>
       <c r="O7" t="n">
-        <v>1931498.948864857</v>
+        <v>1931498.943728411</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.855106383</v>
+        <v>6272.8551336898</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.560425538</v>
+        <v>1794036.568235283</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1112,10 +1112,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>12357.960425532</v>
+        <v>12357.960428571</v>
       </c>
       <c r="O18" t="n">
-        <v>444886.575319152</v>
+        <v>444886.575428556</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -2074,10 +2074,10 @@
         <v>34</v>
       </c>
       <c r="N42" t="n">
-        <v>61666.874241573</v>
+        <v>61666.874364162</v>
       </c>
       <c r="O42" t="n">
-        <v>2096673.724213482</v>
+        <v>2096673.728381508</v>
       </c>
       <c r="P42" t="n">
         <v>98900</v>
@@ -2341,10 +2341,10 @@
         <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>4878.2859393939</v>
+        <v>4878.2859756098</v>
       </c>
       <c r="O48" t="n">
-        <v>19513.1437575756</v>
+        <v>19513.1439024392</v>
       </c>
       <c r="P48" t="n">
         <v>13500</v>
@@ -2799,10 +2799,10 @@
         <v>122</v>
       </c>
       <c r="N59" t="n">
-        <v>10752.93</v>
+        <v>10899.560863636</v>
       </c>
       <c r="O59" t="n">
-        <v>1311857.46</v>
+        <v>1329746.425363592</v>
       </c>
       <c r="P59" t="n">
         <v>18400</v>
@@ -2840,10 +2840,10 @@
         <v>148</v>
       </c>
       <c r="N60" t="n">
-        <v>1950.2139585731</v>
+        <v>1953.5860864553</v>
       </c>
       <c r="O60" t="n">
-        <v>288631.6658688188</v>
+        <v>289130.7407953844</v>
       </c>
       <c r="P60" t="n">
         <v>2900</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0638359274</v>
+        <v>1098.0646017403</v>
       </c>
       <c r="O70" t="n">
-        <v>129571.5326394332</v>
+        <v>129571.6230053554</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -3507,10 +3507,10 @@
         <v>218</v>
       </c>
       <c r="N75" t="n">
-        <v>13593.35</v>
+        <v>13609.886922141</v>
       </c>
       <c r="O75" t="n">
-        <v>2963350.3</v>
+        <v>2966955.349026738</v>
       </c>
       <c r="P75" t="n">
         <v>25500</v>
@@ -4299,10 +4299,10 @@
         <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>8214</v>
+        <v>8252.563380281699</v>
       </c>
       <c r="O93" t="n">
-        <v>16428</v>
+        <v>16505.1267605634</v>
       </c>
       <c r="P93" t="n">
         <v>7900</v>
@@ -4706,10 +4706,10 @@
         <v>179</v>
       </c>
       <c r="N102" t="n">
-        <v>3795.7100076161</v>
+        <v>3795.7100076176</v>
       </c>
       <c r="O102" t="n">
-        <v>679432.0913632819</v>
+        <v>679432.0913635504</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4882,19 +4882,19 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300513149</v>
+        <v>4890.9300530504</v>
       </c>
       <c r="O106" t="n">
-        <v>2127554.572321982</v>
+        <v>1907462.720689656</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
       </c>
       <c r="Q106" t="n">
-        <v>3567000</v>
+        <v>3198000</v>
       </c>
     </row>
     <row r="107">
@@ -5601,10 +5601,10 @@
         <v>289</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.462946776</v>
+        <v>12422.462948052</v>
       </c>
       <c r="O122" t="n">
-        <v>3590091.791618264</v>
+        <v>3590091.791987028</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5732,10 +5732,10 @@
         <v>2442</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2761773616</v>
+        <v>3472.2761978447</v>
       </c>
       <c r="O125" t="n">
-        <v>8479298.425117027</v>
+        <v>8479298.475136757</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600140449</v>
+        <v>3041.6600141844</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.667036495</v>
+        <v>1523871.667106384</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5912,10 +5912,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1712626125</v>
+        <v>4372.0654674395</v>
       </c>
       <c r="O129" t="n">
-        <v>4852000.101499875</v>
+        <v>4852992.668857845</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -6045,10 +6045,10 @@
         <v>170</v>
       </c>
       <c r="N132" t="n">
-        <v>5331.69</v>
+        <v>5371.5779551122</v>
       </c>
       <c r="O132" t="n">
-        <v>906387.2999999999</v>
+        <v>913168.2523690739</v>
       </c>
       <c r="P132" t="n">
         <v>7900</v>
@@ -7192,10 +7192,10 @@
         <v>279</v>
       </c>
       <c r="N157" t="n">
-        <v>3761.6</v>
+        <v>3776.2176165803</v>
       </c>
       <c r="O157" t="n">
-        <v>1049486.4</v>
+        <v>1053564.715025904</v>
       </c>
       <c r="P157" t="n">
         <v>6900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9244361119</v>
+        <v>1630.924511587</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.5672973729</v>
+        <v>311506.581713117</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1945724495</v>
+        <v>1550.1946099379</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.004608182</v>
+        <v>55807.0059577644</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7456,10 +7456,10 @@
         <v>48</v>
       </c>
       <c r="N163" t="n">
-        <v>1579.3839013453</v>
+        <v>1579.3838288288</v>
       </c>
       <c r="O163" t="n">
-        <v>75810.42726457441</v>
+        <v>75810.4237837824</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -7582,10 +7582,10 @@
         <v>17</v>
       </c>
       <c r="N166" t="n">
-        <v>18598</v>
+        <v>19114.611111111</v>
       </c>
       <c r="O166" t="n">
-        <v>316166</v>
+        <v>324948.388888887</v>
       </c>
       <c r="P166" t="n">
         <v>21900</v>
@@ -8469,10 +8469,10 @@
         <v>91</v>
       </c>
       <c r="N186" t="n">
-        <v>7537.4722834646</v>
+        <v>7719.830483871</v>
       </c>
       <c r="O186" t="n">
-        <v>685909.9777952787</v>
+        <v>702504.574032261</v>
       </c>
       <c r="P186" t="n">
         <v>8900</v>
@@ -8633,10 +8633,10 @@
         <v>195</v>
       </c>
       <c r="N190" t="n">
-        <v>8794.48</v>
+        <v>8799.4655328798</v>
       </c>
       <c r="O190" t="n">
-        <v>1714923.6</v>
+        <v>1715895.778911561</v>
       </c>
       <c r="P190" t="n">
         <v>14500</v>
@@ -8838,10 +8838,10 @@
         <v>157</v>
       </c>
       <c r="N195" t="n">
-        <v>22485.695471698</v>
+        <v>22485.695454545</v>
       </c>
       <c r="O195" t="n">
-        <v>3530254.189056586</v>
+        <v>3530254.186363565</v>
       </c>
       <c r="P195" t="n">
         <v>36500</v>
@@ -9217,10 +9217,10 @@
         <v>24</v>
       </c>
       <c r="N204" t="n">
-        <v>3731.0244863014</v>
+        <v>3731.0245172414</v>
       </c>
       <c r="O204" t="n">
-        <v>89544.5876712336</v>
+        <v>89544.58841379361</v>
       </c>
       <c r="P204" t="n">
         <v>5200</v>
@@ -9696,10 +9696,10 @@
         <v>707</v>
       </c>
       <c r="N215" t="n">
-        <v>4814.2679265446</v>
+        <v>4814.2679260066</v>
       </c>
       <c r="O215" t="n">
-        <v>3403687.424067033</v>
+        <v>3403687.423686666</v>
       </c>
       <c r="P215" t="n">
         <v>9900</v>
@@ -9865,10 +9865,10 @@
         <v>227</v>
       </c>
       <c r="N219" t="n">
-        <v>4100.45</v>
+        <v>4102.8563673709</v>
       </c>
       <c r="O219" t="n">
-        <v>930802.1499999999</v>
+        <v>931348.3953931944</v>
       </c>
       <c r="P219" t="n">
         <v>26900</v>
@@ -9911,10 +9911,10 @@
         <v>57</v>
       </c>
       <c r="N220" t="n">
-        <v>5431.12</v>
+        <v>5455.0456387665</v>
       </c>
       <c r="O220" t="n">
-        <v>309573.84</v>
+        <v>310937.6014096905</v>
       </c>
       <c r="P220" t="n">
         <v>8900</v>
@@ -11106,10 +11106,10 @@
         <v>125</v>
       </c>
       <c r="N247" t="n">
-        <v>9188.98</v>
+        <v>9252.7923611111</v>
       </c>
       <c r="O247" t="n">
-        <v>1148622.5</v>
+        <v>1156599.045138888</v>
       </c>
       <c r="P247" t="n">
         <v>12900</v>
@@ -11608,10 +11608,10 @@
         <v>952</v>
       </c>
       <c r="N258" t="n">
-        <v>1778.4728179471</v>
+        <v>1778.4728348758</v>
       </c>
       <c r="O258" t="n">
-        <v>1693106.122685639</v>
+        <v>1693106.138801761</v>
       </c>
       <c r="P258" t="n">
         <v>4900</v>
@@ -11700,10 +11700,10 @@
         <v>73</v>
       </c>
       <c r="N260" t="n">
-        <v>18016</v>
+        <v>18023.2064</v>
       </c>
       <c r="O260" t="n">
-        <v>1315168</v>
+        <v>1315694.0672</v>
       </c>
       <c r="P260" t="n">
         <v>29900</v>
@@ -13045,10 +13045,10 @@
         <v>5</v>
       </c>
       <c r="N289" t="n">
-        <v>7108.85</v>
+        <v>7961.912</v>
       </c>
       <c r="O289" t="n">
-        <v>35544.25</v>
+        <v>39809.56</v>
       </c>
       <c r="P289" t="n">
         <v>7900</v>
@@ -13324,10 +13324,10 @@
         <v>5</v>
       </c>
       <c r="N295" t="n">
-        <v>3938.66</v>
+        <v>3950.9108864697</v>
       </c>
       <c r="O295" t="n">
-        <v>19693.3</v>
+        <v>19754.5544323485</v>
       </c>
       <c r="P295" t="n">
         <v>4500</v>
@@ -13830,10 +13830,10 @@
         <v>83</v>
       </c>
       <c r="N306" t="n">
-        <v>5858</v>
+        <v>6074.962962963</v>
       </c>
       <c r="O306" t="n">
-        <v>486214</v>
+        <v>504221.925925929</v>
       </c>
       <c r="P306" t="n">
         <v>9500</v>
@@ -13876,10 +13876,10 @@
         <v>263</v>
       </c>
       <c r="N307" t="n">
-        <v>2252.2979910045</v>
+        <v>2252.2981374046</v>
       </c>
       <c r="O307" t="n">
-        <v>592354.3716341836</v>
+        <v>592354.4101374098</v>
       </c>
       <c r="P307" t="n">
         <v>3900</v>
@@ -14063,10 +14063,10 @@
         <v>504</v>
       </c>
       <c r="N311" t="n">
-        <v>2328.1186691895</v>
+        <v>2328.1186615921</v>
       </c>
       <c r="O311" t="n">
-        <v>1173371.809271508</v>
+        <v>1173371.805442418</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
@@ -14477,10 +14477,10 @@
         <v>100</v>
       </c>
       <c r="N320" t="n">
-        <v>4907.8226185567</v>
+        <v>4907.8226736842</v>
       </c>
       <c r="O320" t="n">
-        <v>490782.26185567</v>
+        <v>490782.26736842</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -14707,10 +14707,10 @@
         <v>84</v>
       </c>
       <c r="N325" t="n">
-        <v>3903.7391411043</v>
+        <v>3903.7392422907</v>
       </c>
       <c r="O325" t="n">
-        <v>327914.0878527612</v>
+        <v>327914.0963524188</v>
       </c>
       <c r="P325" t="n">
         <v>7500</v>
@@ -15622,10 +15622,10 @@
         <v>176</v>
       </c>
       <c r="N345" t="n">
-        <v>59834</v>
+        <v>60093.865363735</v>
       </c>
       <c r="O345" t="n">
-        <v>10530784</v>
+        <v>10576520.30401736</v>
       </c>
       <c r="P345" t="n">
         <v>7900</v>
@@ -15944,10 +15944,10 @@
         <v>227</v>
       </c>
       <c r="N352" t="n">
-        <v>3639.35</v>
+        <v>3652.664695122</v>
       </c>
       <c r="O352" t="n">
-        <v>826132.45</v>
+        <v>829154.8857926941</v>
       </c>
       <c r="P352" t="n">
         <v>7500</v>
@@ -16174,10 +16174,10 @@
         <v>839</v>
       </c>
       <c r="N357" t="n">
-        <v>1516.0387429797</v>
+        <v>1516.0387397625</v>
       </c>
       <c r="O357" t="n">
-        <v>1271956.505359968</v>
+        <v>1271956.502660737</v>
       </c>
       <c r="P357" t="n">
         <v>2300</v>
@@ -16537,10 +16537,10 @@
         <v>145</v>
       </c>
       <c r="N365" t="n">
-        <v>2842.2744067797</v>
+        <v>2842.2743909348</v>
       </c>
       <c r="O365" t="n">
-        <v>412129.7889830565</v>
+        <v>412129.786685546</v>
       </c>
       <c r="P365" t="n">
         <v>4900</v>
@@ -16581,10 +16581,10 @@
         <v>2063</v>
       </c>
       <c r="N366" t="n">
-        <v>692.15240898798</v>
+        <v>692.1524140338601</v>
       </c>
       <c r="O366" t="n">
-        <v>1427910.419742203</v>
+        <v>1427910.430151853</v>
       </c>
       <c r="P366" t="n">
         <v>1200</v>
@@ -16863,7 +16863,7 @@
         </is>
       </c>
       <c r="J372" t="n">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
@@ -16872,19 +16872,19 @@
         <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="N372" t="n">
         <v>5215</v>
       </c>
       <c r="O372" t="n">
-        <v>5522685</v>
+        <v>5444460</v>
       </c>
       <c r="P372" t="n">
         <v>8900</v>
       </c>
       <c r="Q372" t="n">
-        <v>9425100</v>
+        <v>9291600</v>
       </c>
     </row>
     <row r="373">
@@ -17451,10 +17451,10 @@
         <v>190</v>
       </c>
       <c r="N384" t="n">
-        <v>3629.36</v>
+        <v>3650.5019029126</v>
       </c>
       <c r="O384" t="n">
-        <v>689578.4</v>
+        <v>693595.361553394</v>
       </c>
       <c r="P384" t="n">
         <v>3900</v>
@@ -17779,10 +17779,10 @@
         <v>158</v>
       </c>
       <c r="N391" t="n">
-        <v>1690.8700093502</v>
+        <v>1690.8700093809</v>
       </c>
       <c r="O391" t="n">
-        <v>267157.4614773316</v>
+        <v>267157.4614821822</v>
       </c>
       <c r="P391" t="n">
         <v>3000</v>
@@ -18014,10 +18014,10 @@
         <v>5845</v>
       </c>
       <c r="N396" t="n">
-        <v>345.55838633169</v>
+        <v>345.63428985635</v>
       </c>
       <c r="O396" t="n">
-        <v>2019788.768108728</v>
+        <v>2020232.424210366</v>
       </c>
       <c r="P396" t="n">
         <v>600</v>
@@ -18156,10 +18156,10 @@
         <v>7734</v>
       </c>
       <c r="N399" t="n">
-        <v>711.3366477489</v>
+        <v>711.87861852814</v>
       </c>
       <c r="O399" t="n">
-        <v>5501477.633689992</v>
+        <v>5505669.235696635</v>
       </c>
       <c r="P399" t="n">
         <v>900</v>
@@ -18672,10 +18672,10 @@
         <v>132</v>
       </c>
       <c r="N410" t="n">
-        <v>3259.1344047619</v>
+        <v>3285.20748</v>
       </c>
       <c r="O410" t="n">
-        <v>430205.7414285708</v>
+        <v>433647.38736</v>
       </c>
       <c r="P410" t="n">
         <v>3600</v>
@@ -18808,10 +18808,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8373975045</v>
+        <v>3110.837275018</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.674795009</v>
+        <v>6221.674550036</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -19742,10 +19742,10 @@
         <v>381</v>
       </c>
       <c r="N433" t="n">
-        <v>1595.4993541033</v>
+        <v>1595.4991666667</v>
       </c>
       <c r="O433" t="n">
-        <v>607885.2539133573</v>
+        <v>607885.1825000127</v>
       </c>
       <c r="P433" t="n">
         <v>2500</v>
@@ -20177,10 +20177,10 @@
         <v>23</v>
       </c>
       <c r="N442" t="n">
-        <v>2832.1952307692</v>
+        <v>2832.1953125</v>
       </c>
       <c r="O442" t="n">
-        <v>65140.4903076916</v>
+        <v>65140.4921875</v>
       </c>
       <c r="P442" t="n">
         <v>12900</v>
@@ -20563,10 +20563,10 @@
         <v>13</v>
       </c>
       <c r="N450" t="n">
-        <v>12448.353571429</v>
+        <v>12448.353703704</v>
       </c>
       <c r="O450" t="n">
-        <v>161828.596428577</v>
+        <v>161828.598148152</v>
       </c>
       <c r="P450" t="n">
         <v>22900</v>
@@ -20698,7 +20698,7 @@
         </is>
       </c>
       <c r="J453" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K453" t="n">
         <v>0</v>
@@ -20707,19 +20707,19 @@
         <v>0</v>
       </c>
       <c r="M453" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N453" t="n">
         <v>5697.97</v>
       </c>
       <c r="O453" t="n">
-        <v>547005.12</v>
+        <v>541307.15</v>
       </c>
       <c r="P453" t="n">
         <v>19500</v>
       </c>
       <c r="Q453" t="n">
-        <v>1872000</v>
+        <v>1852500</v>
       </c>
     </row>
     <row r="454">
@@ -21148,10 +21148,10 @@
         <v>240</v>
       </c>
       <c r="N462" t="n">
-        <v>5347.88</v>
+        <v>5370.7341880342</v>
       </c>
       <c r="O462" t="n">
-        <v>1283491.2</v>
+        <v>1288976.205128208</v>
       </c>
       <c r="P462" t="n">
         <v>7900</v>
@@ -21197,10 +21197,10 @@
         <v>231</v>
       </c>
       <c r="N463" t="n">
-        <v>4578.04</v>
+        <v>4593.2494352159</v>
       </c>
       <c r="O463" t="n">
-        <v>1057527.24</v>
+        <v>1061040.619534873</v>
       </c>
       <c r="P463" t="n">
         <v>7500</v>
@@ -21679,10 +21679,10 @@
         <v>152</v>
       </c>
       <c r="N473" t="n">
-        <v>7046.9398271765</v>
+        <v>7056.0857581657</v>
       </c>
       <c r="O473" t="n">
-        <v>1071134.853730828</v>
+        <v>1072525.035241186</v>
       </c>
       <c r="P473" t="n">
         <v>9900</v>
@@ -22405,10 +22405,10 @@
         <v>981</v>
       </c>
       <c r="N488" t="n">
-        <v>665.32396350735</v>
+        <v>665.32397155917</v>
       </c>
       <c r="O488" t="n">
-        <v>652682.8082007103</v>
+        <v>652682.8160995458</v>
       </c>
       <c r="P488" t="n">
         <v>2900</v>
@@ -22647,10 +22647,10 @@
         <v>288</v>
       </c>
       <c r="N493" t="n">
-        <v>430.60997568389</v>
+        <v>430.60997550521</v>
       </c>
       <c r="O493" t="n">
-        <v>124015.6729969603</v>
+        <v>124015.6729455005</v>
       </c>
       <c r="P493" t="n">
         <v>2200</v>
@@ -23132,10 +23132,10 @@
         <v>-72</v>
       </c>
       <c r="N504" t="n">
-        <v>1794.2879648314</v>
+        <v>1796.1048285838</v>
       </c>
       <c r="O504" t="n">
-        <v>-129188.7334678608</v>
+        <v>-129319.5476580336</v>
       </c>
       <c r="P504" t="n">
         <v>1600</v>
@@ -23265,10 +23265,10 @@
         <v>11</v>
       </c>
       <c r="N507" t="n">
-        <v>22951.704710526</v>
+        <v>22951.704689564</v>
       </c>
       <c r="O507" t="n">
-        <v>252468.751815786</v>
+        <v>252468.751585204</v>
       </c>
       <c r="P507" t="n">
         <v>37900</v>
@@ -23393,10 +23393,10 @@
         <v>11</v>
       </c>
       <c r="N510" t="n">
-        <v>12000</v>
+        <v>12545.454545455</v>
       </c>
       <c r="O510" t="n">
-        <v>132000</v>
+        <v>138000.000000005</v>
       </c>
       <c r="P510" t="n">
         <v>15000</v>
@@ -24027,10 +24027,10 @@
         <v>360</v>
       </c>
       <c r="N524" t="n">
-        <v>7480</v>
+        <v>7496.4757709251</v>
       </c>
       <c r="O524" t="n">
-        <v>2692800</v>
+        <v>2698731.277533036</v>
       </c>
       <c r="P524" t="n">
         <v>9500</v>
@@ -24073,10 +24073,10 @@
         <v>124</v>
       </c>
       <c r="N525" t="n">
-        <v>5280</v>
+        <v>5320.824742268</v>
       </c>
       <c r="O525" t="n">
-        <v>654720</v>
+        <v>659782.2680412319</v>
       </c>
       <c r="P525" t="n">
         <v>6900</v>
@@ -24088,12 +24088,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>J-1323</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>CARRO FRICCION TODO TERRENO OJITOS J-1323</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -24107,7 +24107,7 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -24116,30 +24116,30 @@
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="N526" t="n">
-        <v>3872</v>
+        <v>4576</v>
       </c>
       <c r="O526" t="n">
-        <v>224576</v>
+        <v>576576</v>
       </c>
       <c r="P526" t="n">
-        <v>4900</v>
+        <v>5900</v>
       </c>
       <c r="Q526" t="n">
-        <v>284200</v>
+        <v>743400</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>J-1331</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>CARRO TODO TERRENO DOBLE IMAGEN J-1331</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -24153,7 +24153,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>33</v>
+        <v>242</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -24162,35 +24162,35 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>33</v>
+        <v>242</v>
       </c>
       <c r="N527" t="n">
-        <v>4400</v>
+        <v>5280</v>
       </c>
       <c r="O527" t="n">
-        <v>145200</v>
+        <v>1277760</v>
       </c>
       <c r="P527" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q527" t="n">
-        <v>194700</v>
+        <v>1669800</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>J-718</t>
+          <t>MG040</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>MOTO DE IMPULSO BLISTER J-718</t>
+          <t>ABACO ANIMALES PT17058</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -24199,7 +24199,7 @@
         </is>
       </c>
       <c r="J528" t="n">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -24208,35 +24208,40 @@
         <v>0</v>
       </c>
       <c r="M528" t="n">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="N528" t="n">
-        <v>4576</v>
+        <v>5280</v>
       </c>
       <c r="O528" t="n">
-        <v>576576</v>
+        <v>121440</v>
       </c>
       <c r="P528" t="n">
-        <v>5900</v>
+        <v>6600</v>
       </c>
       <c r="Q528" t="n">
-        <v>743400</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>J-719</t>
+          <t>MG044</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>PT19323</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>ABACO TREN PT19323</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -24245,7 +24250,7 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>242</v>
+        <v>24</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
@@ -24254,30 +24259,30 @@
         <v>0</v>
       </c>
       <c r="M529" t="n">
-        <v>242</v>
+        <v>24</v>
       </c>
       <c r="N529" t="n">
-        <v>5280</v>
+        <v>7760</v>
       </c>
       <c r="O529" t="n">
-        <v>1277760</v>
+        <v>186240</v>
       </c>
       <c r="P529" t="n">
-        <v>6900</v>
+        <v>9700</v>
       </c>
       <c r="Q529" t="n">
-        <v>1669800</v>
+        <v>232800</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>MG040</t>
+          <t>MG051</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>ABACO ANIMALES PT17058</t>
+          <t>CAJON DIDACTICO RELOJ PT21204</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -24291,7 +24296,7 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -24300,40 +24305,40 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="N530" t="n">
-        <v>5280</v>
+        <v>22320</v>
       </c>
       <c r="O530" t="n">
-        <v>121440</v>
+        <v>624960</v>
       </c>
       <c r="P530" t="n">
-        <v>6600</v>
+        <v>27900</v>
       </c>
       <c r="Q530" t="n">
-        <v>151800</v>
+        <v>781200</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>MG044</t>
+          <t>MG067</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>PT19323</t>
+          <t>MG21283</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>ABACO TREN PT19323</t>
+          <t>KARAOKE BLUETOOTH MG21283MG</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -24342,7 +24347,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24351,35 +24356,40 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N531" t="n">
-        <v>7760</v>
+        <v>41161.350714286</v>
       </c>
       <c r="O531" t="n">
-        <v>186240</v>
+        <v>1029033.76785715</v>
       </c>
       <c r="P531" t="n">
-        <v>9700</v>
+        <v>55000</v>
       </c>
       <c r="Q531" t="n">
-        <v>232800</v>
+        <v>1375000</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>MG051</t>
+          <t>MG094</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>mg33153</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>CAJON DIDACTICO RELOJ PT21204</t>
+          <t>LANZA DISCOS MED MULTICOLOR MG33153</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -24388,7 +24398,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24397,40 +24407,35 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="N532" t="n">
-        <v>22320</v>
+        <v>3840</v>
       </c>
       <c r="O532" t="n">
-        <v>624960</v>
+        <v>65280</v>
       </c>
       <c r="P532" t="n">
-        <v>27900</v>
+        <v>3900</v>
       </c>
       <c r="Q532" t="n">
-        <v>781200</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>MG067</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>MG21283</t>
+          <t>MG16421</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>KARAOKE BLUETOOTH MG21283MG</t>
+          <t>CARRO MEZCALDOR BOLSA MDE MG16421</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -24439,7 +24444,7 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -24448,40 +24453,40 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="N533" t="n">
-        <v>41161.350714286</v>
+        <v>2775.86</v>
       </c>
       <c r="O533" t="n">
-        <v>1029033.76785715</v>
+        <v>141568.86</v>
       </c>
       <c r="P533" t="n">
-        <v>55000</v>
+        <v>12500</v>
       </c>
       <c r="Q533" t="n">
-        <v>1375000</v>
+        <v>637500</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>MG094</t>
+          <t>MG18991</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>mg33153</t>
+          <t>MG18991</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>LANZA DISCOS MED MULTICOLOR MG33153</t>
+          <t>MAQUINA DE COSER PILAS MG18991</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -24490,7 +24495,7 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -24499,35 +24504,35 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N534" t="n">
-        <v>3840</v>
+        <v>8949.32</v>
       </c>
       <c r="O534" t="n">
-        <v>65280</v>
+        <v>125290.48</v>
       </c>
       <c r="P534" t="n">
-        <v>3900</v>
+        <v>28900</v>
       </c>
       <c r="Q534" t="n">
-        <v>66300</v>
+        <v>404600</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>MG16421</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>CARRO MEZCALDOR BOLSA MDE MG16421</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -24536,7 +24541,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -24545,40 +24550,40 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="N535" t="n">
-        <v>2775.86</v>
+        <v>1482.84</v>
       </c>
       <c r="O535" t="n">
-        <v>141568.86</v>
+        <v>250599.96</v>
       </c>
       <c r="P535" t="n">
-        <v>12500</v>
+        <v>6500</v>
       </c>
       <c r="Q535" t="n">
-        <v>637500</v>
+        <v>1098500</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>MG18991</t>
+          <t>MG20930</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MG18991</t>
+          <t>MG20930</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER PILAS MG18991</t>
+          <t>CARRO BUGGY RECARGABLE MG20930</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -24587,7 +24592,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -24596,35 +24601,35 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N536" t="n">
-        <v>8949.32</v>
+        <v>63353.92</v>
       </c>
       <c r="O536" t="n">
-        <v>125290.48</v>
+        <v>380123.52</v>
       </c>
       <c r="P536" t="n">
-        <v>28900</v>
+        <v>128000</v>
       </c>
       <c r="Q536" t="n">
-        <v>404600</v>
+        <v>768000</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -24633,7 +24638,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24642,40 +24647,35 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="N537" t="n">
-        <v>1482.84</v>
+        <v>1129.14</v>
       </c>
       <c r="O537" t="n">
-        <v>250599.96</v>
+        <v>91460.34000000001</v>
       </c>
       <c r="P537" t="n">
-        <v>6500</v>
+        <v>6900</v>
       </c>
       <c r="Q537" t="n">
-        <v>1098500</v>
+        <v>558900</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>MG20930</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>MG20930</t>
+          <t>MG27668</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CARRO BUGGY RECARGABLE MG20930</t>
+          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -24684,7 +24684,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -24693,35 +24693,35 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="N538" t="n">
-        <v>63353.92</v>
+        <v>15239.8</v>
       </c>
       <c r="O538" t="n">
-        <v>380123.52</v>
+        <v>320035.8</v>
       </c>
       <c r="P538" t="n">
-        <v>128000</v>
+        <v>15900</v>
       </c>
       <c r="Q538" t="n">
-        <v>768000</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG28914</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -24730,7 +24730,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -24739,35 +24739,35 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="N539" t="n">
-        <v>1129.14</v>
+        <v>5563</v>
       </c>
       <c r="O539" t="n">
-        <v>91460.34000000001</v>
+        <v>133512</v>
       </c>
       <c r="P539" t="n">
-        <v>6900</v>
+        <v>11900</v>
       </c>
       <c r="Q539" t="n">
-        <v>558900</v>
+        <v>285600</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>MG27668</t>
+          <t>MG30041</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
+          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -24776,7 +24776,7 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
@@ -24785,35 +24785,40 @@
         <v>0</v>
       </c>
       <c r="M540" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N540" t="n">
-        <v>15239.8</v>
+        <v>9046.99</v>
       </c>
       <c r="O540" t="n">
-        <v>320035.8</v>
+        <v>217127.76</v>
       </c>
       <c r="P540" t="n">
-        <v>15900</v>
+        <v>22500</v>
       </c>
       <c r="Q540" t="n">
-        <v>333900</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>MG28914</t>
+          <t>MG30183</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>MG30183</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
+          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24822,7 +24827,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -24831,35 +24836,35 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="N541" t="n">
-        <v>5563</v>
+        <v>3982.670776699</v>
       </c>
       <c r="O541" t="n">
-        <v>133512</v>
+        <v>370388.382233007</v>
       </c>
       <c r="P541" t="n">
-        <v>11900</v>
+        <v>10900</v>
       </c>
       <c r="Q541" t="n">
-        <v>285600</v>
+        <v>1013700</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MG30041</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -24868,7 +24873,7 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>24</v>
+        <v>399</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
@@ -24877,40 +24882,40 @@
         <v>0</v>
       </c>
       <c r="M542" t="n">
-        <v>24</v>
+        <v>399</v>
       </c>
       <c r="N542" t="n">
-        <v>9046.99</v>
+        <v>571.87</v>
       </c>
       <c r="O542" t="n">
-        <v>217127.76</v>
+        <v>228176.13</v>
       </c>
       <c r="P542" t="n">
-        <v>22500</v>
+        <v>2500</v>
       </c>
       <c r="Q542" t="n">
-        <v>540000</v>
+        <v>997500</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>MG30183</t>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MG30183</t>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -24919,7 +24924,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -24928,35 +24933,40 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="N543" t="n">
-        <v>3982.670776699</v>
+        <v>2432.1358227848</v>
       </c>
       <c r="O543" t="n">
-        <v>370388.382233007</v>
+        <v>7296.4074683544</v>
       </c>
       <c r="P543" t="n">
-        <v>10900</v>
+        <v>4500</v>
       </c>
       <c r="Q543" t="n">
-        <v>1013700</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40324</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>MG40324</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>JUEGO DE PESCA MG40324</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -24965,7 +24975,7 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>399</v>
+        <v>1</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -24974,40 +24984,35 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>399</v>
+        <v>1</v>
       </c>
       <c r="N544" t="n">
-        <v>571.87</v>
+        <v>2005.78</v>
       </c>
       <c r="O544" t="n">
-        <v>228176.13</v>
+        <v>2005.78</v>
       </c>
       <c r="P544" t="n">
-        <v>2500</v>
+        <v>9500</v>
       </c>
       <c r="Q544" t="n">
-        <v>997500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>MG40269</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>MG40269</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -25016,7 +25021,7 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>3</v>
+        <v>271</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -25025,35 +25030,35 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>3</v>
+        <v>271</v>
       </c>
       <c r="N545" t="n">
-        <v>2432.1358227848</v>
+        <v>227.41614285714</v>
       </c>
       <c r="O545" t="n">
-        <v>7296.4074683544</v>
+        <v>61629.77471428494</v>
       </c>
       <c r="P545" t="n">
-        <v>4500</v>
+        <v>1200</v>
       </c>
       <c r="Q545" t="n">
-        <v>13500</v>
+        <v>325200</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>MG40324</t>
+          <t>MG40642</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MG40324</t>
+          <t>MG40642</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>JUEGO DE PESCA MG40324</t>
+          <t>MORRAL TOCADOR PORTABLE MG40642</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -25067,7 +25072,7 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -25076,35 +25081,40 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N546" t="n">
-        <v>2005.78</v>
+        <v>19081.85</v>
       </c>
       <c r="O546" t="n">
-        <v>2005.78</v>
+        <v>286227.75</v>
       </c>
       <c r="P546" t="n">
-        <v>9500</v>
+        <v>36900</v>
       </c>
       <c r="Q546" t="n">
-        <v>9500</v>
+        <v>553500</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40888</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>MG40888</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>SET DE RESCATE EN BOLSA MG40888</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -25113,7 +25123,7 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
@@ -25122,40 +25132,35 @@
         <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="N547" t="n">
-        <v>227.41614285714</v>
+        <v>7540.09</v>
       </c>
       <c r="O547" t="n">
-        <v>61629.77471428494</v>
+        <v>37700.45</v>
       </c>
       <c r="P547" t="n">
-        <v>1200</v>
+        <v>18500</v>
       </c>
       <c r="Q547" t="n">
-        <v>325200</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>MG40642</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>MG40642</t>
+          <t>MG41171</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>MORRAL TOCADOR PORTABLE MG40642</t>
+          <t>LANZA AGUA COLORES GDE MG41171</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -25164,7 +25169,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -25173,49 +25178,34 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="N548" t="n">
-        <v>19081.85</v>
+        <v>25110.1</v>
       </c>
       <c r="O548" t="n">
-        <v>286227.75</v>
+        <v>778413.1</v>
       </c>
       <c r="P548" t="n">
-        <v>36900</v>
+        <v>27900</v>
       </c>
       <c r="Q548" t="n">
-        <v>553500</v>
+        <v>864900</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>MG40888</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>MG40888</t>
+          <t>MR044</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>SET DE RESCATE EN BOLSA MG40888</t>
-        </is>
-      </c>
-      <c r="E549" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I549" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
         </is>
       </c>
       <c r="J549" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
@@ -25224,35 +25214,35 @@
         <v>0</v>
       </c>
       <c r="M549" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N549" t="n">
-        <v>7540.09</v>
+        <v>20720</v>
       </c>
       <c r="O549" t="n">
-        <v>37700.45</v>
+        <v>124320</v>
       </c>
       <c r="P549" t="n">
-        <v>18500</v>
+        <v>25900</v>
       </c>
       <c r="Q549" t="n">
-        <v>92500</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>MG41171</t>
+          <t>MR045</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>LANZA AGUA COLORES GDE MG41171</t>
+          <t>MORRAL ANIMALES STD 0230-02-002</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -25261,7 +25251,7 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
@@ -25270,34 +25260,34 @@
         <v>0</v>
       </c>
       <c r="M550" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="N550" t="n">
-        <v>25110.1</v>
+        <v>22080.08</v>
       </c>
       <c r="O550" t="n">
-        <v>778413.1</v>
+        <v>287041.04</v>
       </c>
       <c r="P550" t="n">
-        <v>27900</v>
+        <v>29900</v>
       </c>
       <c r="Q550" t="n">
-        <v>864900</v>
+        <v>388700</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>MR044</t>
+          <t>MR081</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
+          <t>MORRAL GATICO STD MR081</t>
         </is>
       </c>
       <c r="J551" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -25306,35 +25296,35 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N551" t="n">
-        <v>20720</v>
+        <v>22865</v>
       </c>
       <c r="O551" t="n">
-        <v>124320</v>
+        <v>91460</v>
       </c>
       <c r="P551" t="n">
-        <v>25900</v>
+        <v>26900</v>
       </c>
       <c r="Q551" t="n">
-        <v>155400</v>
+        <v>107600</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>MR045</t>
+          <t>PT14019</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>MORRAL ANIMALES STD 0230-02-002</t>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -25343,7 +25333,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25352,34 +25342,34 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="N552" t="n">
-        <v>22080.08</v>
+        <v>1950.7</v>
       </c>
       <c r="O552" t="n">
-        <v>287041.04</v>
+        <v>64373.1</v>
       </c>
       <c r="P552" t="n">
-        <v>29900</v>
+        <v>7500</v>
       </c>
       <c r="Q552" t="n">
-        <v>388700</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>MR081</t>
+          <t>SLBT04</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>MORRAL GATICO STD MR081</t>
+          <t>BOLSA DE REGALO  SLT2023</t>
         </is>
       </c>
       <c r="J553" t="n">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="K553" t="n">
         <v>0</v>
@@ -25388,35 +25378,35 @@
         <v>0</v>
       </c>
       <c r="M553" t="n">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="N553" t="n">
-        <v>22865</v>
+        <v>480</v>
       </c>
       <c r="O553" t="n">
-        <v>91460</v>
+        <v>70080</v>
       </c>
       <c r="P553" t="n">
-        <v>26900</v>
+        <v>600</v>
       </c>
       <c r="Q553" t="n">
-        <v>107600</v>
+        <v>87600</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>SLT014</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -25425,7 +25415,7 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
@@ -25434,34 +25424,44 @@
         <v>0</v>
       </c>
       <c r="M554" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="N554" t="n">
-        <v>1950.7</v>
+        <v>12000</v>
       </c>
       <c r="O554" t="n">
-        <v>64373.1</v>
+        <v>864000</v>
       </c>
       <c r="P554" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="Q554" t="n">
-        <v>247500</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>SLBT04</t>
+          <t>SLT035</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>BOLSA DE REGALO  SLT2023</t>
+          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J555" t="n">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -25470,30 +25470,30 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="N555" t="n">
-        <v>480</v>
+        <v>6917.54</v>
       </c>
       <c r="O555" t="n">
-        <v>70080</v>
+        <v>380464.7</v>
       </c>
       <c r="P555" t="n">
-        <v>600</v>
+        <v>11500</v>
       </c>
       <c r="Q555" t="n">
-        <v>87600</v>
+        <v>632500</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>SLT014</t>
+          <t>SLT05</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
+          <t>ESPADA DOBLE SLT2074</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -25507,7 +25507,7 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -25516,35 +25516,35 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="N556" t="n">
-        <v>12000</v>
+        <v>4720</v>
       </c>
       <c r="O556" t="n">
-        <v>864000</v>
+        <v>1123360</v>
       </c>
       <c r="P556" t="n">
-        <v>15000</v>
+        <v>5900</v>
       </c>
       <c r="Q556" t="n">
-        <v>1080000</v>
+        <v>1404200</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>SLT035</t>
+          <t>SLT2640</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -25553,7 +25553,7 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -25562,35 +25562,35 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="N557" t="n">
-        <v>6917.54</v>
+        <v>1059.1847727273</v>
       </c>
       <c r="O557" t="n">
-        <v>380464.7</v>
+        <v>22242.8802272733</v>
       </c>
       <c r="P557" t="n">
-        <v>11500</v>
+        <v>9500</v>
       </c>
       <c r="Q557" t="n">
-        <v>632500</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>SLT05</t>
+          <t>SLT2642</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>ESPADA DOBLE SLT2074</t>
+          <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -25599,7 +25599,7 @@
         </is>
       </c>
       <c r="J558" t="n">
-        <v>238</v>
+        <v>53</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
@@ -25608,110 +25608,18 @@
         <v>0</v>
       </c>
       <c r="M558" t="n">
-        <v>238</v>
+        <v>53</v>
       </c>
       <c r="N558" t="n">
-        <v>4720</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O558" t="n">
-        <v>1123360</v>
+        <v>18074.13602459019</v>
       </c>
       <c r="P558" t="n">
-        <v>5900</v>
+        <v>14500</v>
       </c>
       <c r="Q558" t="n">
-        <v>1404200</v>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>SLT2640</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
-        </is>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I559" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J559" t="n">
-        <v>21</v>
-      </c>
-      <c r="K559" t="n">
-        <v>0</v>
-      </c>
-      <c r="L559" t="n">
-        <v>0</v>
-      </c>
-      <c r="M559" t="n">
-        <v>21</v>
-      </c>
-      <c r="N559" t="n">
-        <v>1059.1847727273</v>
-      </c>
-      <c r="O559" t="n">
-        <v>22242.8802272733</v>
-      </c>
-      <c r="P559" t="n">
-        <v>9500</v>
-      </c>
-      <c r="Q559" t="n">
-        <v>199500</v>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>SLT2642</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>BALON BASQUEBOL # 7 ST2642</t>
-        </is>
-      </c>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I560" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J560" t="n">
-        <v>53</v>
-      </c>
-      <c r="K560" t="n">
-        <v>0</v>
-      </c>
-      <c r="L560" t="n">
-        <v>0</v>
-      </c>
-      <c r="M560" t="n">
-        <v>53</v>
-      </c>
-      <c r="N560" t="n">
-        <v>341.02143442623</v>
-      </c>
-      <c r="O560" t="n">
-        <v>18074.13602459019</v>
-      </c>
-      <c r="P560" t="n">
-        <v>14500</v>
-      </c>
-      <c r="Q560" t="n">
         <v>768500</v>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -2799,10 +2799,10 @@
         <v>122</v>
       </c>
       <c r="N59" t="n">
-        <v>10899.560863636</v>
+        <v>10752.93</v>
       </c>
       <c r="O59" t="n">
-        <v>1329746.425363592</v>
+        <v>1311857.46</v>
       </c>
       <c r="P59" t="n">
         <v>18400</v>
@@ -2840,10 +2840,10 @@
         <v>148</v>
       </c>
       <c r="N60" t="n">
-        <v>1953.5860864553</v>
+        <v>1950.2139481268</v>
       </c>
       <c r="O60" t="n">
-        <v>289130.7407953844</v>
+        <v>288631.6643227664</v>
       </c>
       <c r="P60" t="n">
         <v>2900</v>
@@ -3507,10 +3507,10 @@
         <v>218</v>
       </c>
       <c r="N75" t="n">
-        <v>13609.886922141</v>
+        <v>13593.35</v>
       </c>
       <c r="O75" t="n">
-        <v>2966955.349026738</v>
+        <v>2963350.3</v>
       </c>
       <c r="P75" t="n">
         <v>25500</v>
@@ -4299,10 +4299,10 @@
         <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>8252.563380281699</v>
+        <v>8214</v>
       </c>
       <c r="O93" t="n">
-        <v>16505.1267605634</v>
+        <v>16428</v>
       </c>
       <c r="P93" t="n">
         <v>7900</v>
@@ -5912,10 +5912,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O129" t="n">
-        <v>4852992.668857845</v>
+        <v>4852000.101786588</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -6045,10 +6045,10 @@
         <v>170</v>
       </c>
       <c r="N132" t="n">
-        <v>5371.5779551122</v>
+        <v>5331.69</v>
       </c>
       <c r="O132" t="n">
-        <v>913168.2523690739</v>
+        <v>906387.2999999999</v>
       </c>
       <c r="P132" t="n">
         <v>7900</v>
@@ -7192,10 +7192,10 @@
         <v>279</v>
       </c>
       <c r="N157" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="O157" t="n">
-        <v>1053564.715025904</v>
+        <v>1049486.4</v>
       </c>
       <c r="P157" t="n">
         <v>6900</v>
@@ -7582,10 +7582,10 @@
         <v>17</v>
       </c>
       <c r="N166" t="n">
-        <v>19114.611111111</v>
+        <v>18598</v>
       </c>
       <c r="O166" t="n">
-        <v>324948.388888887</v>
+        <v>316166</v>
       </c>
       <c r="P166" t="n">
         <v>21900</v>
@@ -8469,10 +8469,10 @@
         <v>91</v>
       </c>
       <c r="N186" t="n">
-        <v>7719.830483871</v>
+        <v>7537.4723387097</v>
       </c>
       <c r="O186" t="n">
-        <v>702504.574032261</v>
+        <v>685909.9828225827</v>
       </c>
       <c r="P186" t="n">
         <v>8900</v>
@@ -8633,10 +8633,10 @@
         <v>195</v>
       </c>
       <c r="N190" t="n">
-        <v>8799.4655328798</v>
+        <v>8794.48</v>
       </c>
       <c r="O190" t="n">
-        <v>1715895.778911561</v>
+        <v>1714923.6</v>
       </c>
       <c r="P190" t="n">
         <v>14500</v>
@@ -9865,10 +9865,10 @@
         <v>227</v>
       </c>
       <c r="N219" t="n">
-        <v>4102.8563673709</v>
+        <v>4100.45</v>
       </c>
       <c r="O219" t="n">
-        <v>931348.3953931944</v>
+        <v>930802.1499999999</v>
       </c>
       <c r="P219" t="n">
         <v>26900</v>
@@ -9911,10 +9911,10 @@
         <v>57</v>
       </c>
       <c r="N220" t="n">
-        <v>5455.0456387665</v>
+        <v>5431.12</v>
       </c>
       <c r="O220" t="n">
-        <v>310937.6014096905</v>
+        <v>309573.84</v>
       </c>
       <c r="P220" t="n">
         <v>8900</v>
@@ -11106,10 +11106,10 @@
         <v>125</v>
       </c>
       <c r="N247" t="n">
-        <v>9252.7923611111</v>
+        <v>9188.98</v>
       </c>
       <c r="O247" t="n">
-        <v>1156599.045138888</v>
+        <v>1148622.5</v>
       </c>
       <c r="P247" t="n">
         <v>12900</v>
@@ -11700,10 +11700,10 @@
         <v>73</v>
       </c>
       <c r="N260" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O260" t="n">
-        <v>1315694.0672</v>
+        <v>1315168</v>
       </c>
       <c r="P260" t="n">
         <v>29900</v>
@@ -13045,10 +13045,10 @@
         <v>5</v>
       </c>
       <c r="N289" t="n">
-        <v>7961.912</v>
+        <v>7108.85</v>
       </c>
       <c r="O289" t="n">
-        <v>39809.56</v>
+        <v>35544.25</v>
       </c>
       <c r="P289" t="n">
         <v>7900</v>
@@ -13324,10 +13324,10 @@
         <v>5</v>
       </c>
       <c r="N295" t="n">
-        <v>3950.9108864697</v>
+        <v>3938.66</v>
       </c>
       <c r="O295" t="n">
-        <v>19754.5544323485</v>
+        <v>19693.3</v>
       </c>
       <c r="P295" t="n">
         <v>4500</v>
@@ -13830,10 +13830,10 @@
         <v>83</v>
       </c>
       <c r="N306" t="n">
-        <v>6074.962962963</v>
+        <v>5858</v>
       </c>
       <c r="O306" t="n">
-        <v>504221.925925929</v>
+        <v>486214</v>
       </c>
       <c r="P306" t="n">
         <v>9500</v>
@@ -15622,10 +15622,10 @@
         <v>176</v>
       </c>
       <c r="N345" t="n">
-        <v>60093.865363735</v>
+        <v>59834</v>
       </c>
       <c r="O345" t="n">
-        <v>10576520.30401736</v>
+        <v>10530784</v>
       </c>
       <c r="P345" t="n">
         <v>7900</v>
@@ -15944,10 +15944,10 @@
         <v>227</v>
       </c>
       <c r="N352" t="n">
-        <v>3652.664695122</v>
+        <v>3639.35</v>
       </c>
       <c r="O352" t="n">
-        <v>829154.8857926941</v>
+        <v>826132.45</v>
       </c>
       <c r="P352" t="n">
         <v>7500</v>
@@ -17451,10 +17451,10 @@
         <v>190</v>
       </c>
       <c r="N384" t="n">
-        <v>3650.5019029126</v>
+        <v>3629.36</v>
       </c>
       <c r="O384" t="n">
-        <v>693595.361553394</v>
+        <v>689578.4</v>
       </c>
       <c r="P384" t="n">
         <v>3900</v>
@@ -18014,10 +18014,10 @@
         <v>5845</v>
       </c>
       <c r="N396" t="n">
-        <v>345.63428985635</v>
+        <v>345.55838597724</v>
       </c>
       <c r="O396" t="n">
-        <v>2020232.424210366</v>
+        <v>2019788.766036968</v>
       </c>
       <c r="P396" t="n">
         <v>600</v>
@@ -18156,10 +18156,10 @@
         <v>7734</v>
       </c>
       <c r="N399" t="n">
-        <v>711.87861852814</v>
+        <v>711.33664519481</v>
       </c>
       <c r="O399" t="n">
-        <v>5505669.235696635</v>
+        <v>5501477.613936661</v>
       </c>
       <c r="P399" t="n">
         <v>900</v>
@@ -18672,10 +18672,10 @@
         <v>132</v>
       </c>
       <c r="N410" t="n">
-        <v>3285.20748</v>
+        <v>3259.13444</v>
       </c>
       <c r="O410" t="n">
-        <v>433647.38736</v>
+        <v>430205.74608</v>
       </c>
       <c r="P410" t="n">
         <v>3600</v>
@@ -21148,10 +21148,10 @@
         <v>240</v>
       </c>
       <c r="N462" t="n">
-        <v>5370.7341880342</v>
+        <v>5347.88</v>
       </c>
       <c r="O462" t="n">
-        <v>1288976.205128208</v>
+        <v>1283491.2</v>
       </c>
       <c r="P462" t="n">
         <v>7900</v>
@@ -21197,10 +21197,10 @@
         <v>231</v>
       </c>
       <c r="N463" t="n">
-        <v>4593.2494352159</v>
+        <v>4578.04</v>
       </c>
       <c r="O463" t="n">
-        <v>1061040.619534873</v>
+        <v>1057527.24</v>
       </c>
       <c r="P463" t="n">
         <v>7500</v>
@@ -21679,10 +21679,10 @@
         <v>152</v>
       </c>
       <c r="N473" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O473" t="n">
-        <v>1072525.035241186</v>
+        <v>1071134.853696734</v>
       </c>
       <c r="P473" t="n">
         <v>9900</v>
@@ -23132,10 +23132,10 @@
         <v>-72</v>
       </c>
       <c r="N504" t="n">
-        <v>1796.1048285838</v>
+        <v>1794.2879574714</v>
       </c>
       <c r="O504" t="n">
-        <v>-129319.5476580336</v>
+        <v>-129188.7329379408</v>
       </c>
       <c r="P504" t="n">
         <v>1600</v>
@@ -23393,10 +23393,10 @@
         <v>11</v>
       </c>
       <c r="N510" t="n">
-        <v>12545.454545455</v>
+        <v>12000</v>
       </c>
       <c r="O510" t="n">
-        <v>138000.000000005</v>
+        <v>132000</v>
       </c>
       <c r="P510" t="n">
         <v>15000</v>
@@ -24027,10 +24027,10 @@
         <v>360</v>
       </c>
       <c r="N524" t="n">
-        <v>7496.4757709251</v>
+        <v>7480</v>
       </c>
       <c r="O524" t="n">
-        <v>2698731.277533036</v>
+        <v>2692800</v>
       </c>
       <c r="P524" t="n">
         <v>9500</v>
@@ -24073,10 +24073,10 @@
         <v>124</v>
       </c>
       <c r="N525" t="n">
-        <v>5320.824742268</v>
+        <v>5280</v>
       </c>
       <c r="O525" t="n">
-        <v>659782.2680412319</v>
+        <v>654720</v>
       </c>
       <c r="P525" t="n">
         <v>6900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8551336898</v>
+        <v>6272.8551705566</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.568235283</v>
+        <v>1794036.578779188</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1151,10 +1151,10 @@
         <v>440</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8370787689</v>
+        <v>3926.8370772443</v>
       </c>
       <c r="O19" t="n">
-        <v>1727808.314658316</v>
+        <v>1727808.313987492</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -1310,10 +1310,10 @@
         <v>48</v>
       </c>
       <c r="N23" t="n">
-        <v>3716.3301963993</v>
+        <v>3716.3301967213</v>
       </c>
       <c r="O23" t="n">
-        <v>178383.8494271664</v>
+        <v>178383.8494426224</v>
       </c>
       <c r="P23" t="n">
         <v>9500</v>
@@ -1588,10 +1588,10 @@
         <v>89</v>
       </c>
       <c r="N30" t="n">
-        <v>3910.6279357798</v>
+        <v>3910.6279310345</v>
       </c>
       <c r="O30" t="n">
-        <v>348045.8862844022</v>
+        <v>348045.8858620705</v>
       </c>
       <c r="P30" t="n">
         <v>9100</v>
@@ -2536,10 +2536,10 @@
         <v>178</v>
       </c>
       <c r="N53" t="n">
-        <v>3340.6800840336</v>
+        <v>3340.6800842105</v>
       </c>
       <c r="O53" t="n">
-        <v>594641.0549579808</v>
+        <v>594641.054989469</v>
       </c>
       <c r="P53" t="n">
         <v>7100</v>
@@ -2840,10 +2840,10 @@
         <v>148</v>
       </c>
       <c r="N60" t="n">
-        <v>1950.2139481268</v>
+        <v>1950.2139095128</v>
       </c>
       <c r="O60" t="n">
-        <v>288631.6643227664</v>
+        <v>288631.6586078944</v>
       </c>
       <c r="P60" t="n">
         <v>2900</v>
@@ -2927,10 +2927,10 @@
         <v>434</v>
       </c>
       <c r="N62" t="n">
-        <v>4937.3101685824</v>
+        <v>4937.310172549</v>
       </c>
       <c r="O62" t="n">
-        <v>2142792.613164762</v>
+        <v>2142792.614886266</v>
       </c>
       <c r="P62" t="n">
         <v>7500</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0646017403</v>
+        <v>1098.0684371373</v>
       </c>
       <c r="O70" t="n">
-        <v>129571.6230053554</v>
+        <v>129572.0755822014</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4065,19 +4065,19 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="N88" t="n">
         <v>10600</v>
       </c>
       <c r="O88" t="n">
-        <v>9253800</v>
+        <v>9222000</v>
       </c>
       <c r="P88" t="n">
         <v>17200</v>
       </c>
       <c r="Q88" t="n">
-        <v>15015600</v>
+        <v>14964000</v>
       </c>
     </row>
     <row r="89">
@@ -4885,10 +4885,10 @@
         <v>390</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300530504</v>
+        <v>4890.9300534045</v>
       </c>
       <c r="O106" t="n">
-        <v>1907462.720689656</v>
+        <v>1907462.720827755</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
@@ -5333,10 +5333,10 @@
         <v>84</v>
       </c>
       <c r="N116" t="n">
-        <v>3240.8500514139</v>
+        <v>3240.8500533333</v>
       </c>
       <c r="O116" t="n">
-        <v>272231.4043187676</v>
+        <v>272231.4044799972</v>
       </c>
       <c r="P116" t="n">
         <v>5200</v>
@@ -5418,10 +5418,10 @@
         <v>135</v>
       </c>
       <c r="N118" t="n">
-        <v>5191.4800283688</v>
+        <v>5191.4800284495</v>
       </c>
       <c r="O118" t="n">
-        <v>700849.803829788</v>
+        <v>700849.8038406826</v>
       </c>
       <c r="P118" t="n">
         <v>9100</v>
@@ -5601,10 +5601,10 @@
         <v>289</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.462948052</v>
+        <v>12422.462959583</v>
       </c>
       <c r="O122" t="n">
-        <v>3590091.791987028</v>
+        <v>3590091.795319487</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5732,10 +5732,10 @@
         <v>2442</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2761978447</v>
+        <v>3472.2762167406</v>
       </c>
       <c r="O125" t="n">
-        <v>8479298.475136757</v>
+        <v>8479298.521280546</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5912,10 +5912,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1712628708</v>
+        <v>4371.1712629569</v>
       </c>
       <c r="O129" t="n">
-        <v>4852000.101786588</v>
+        <v>4852000.101882159</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.924511587</v>
+        <v>1630.9246047904</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.581713117</v>
+        <v>311506.5995149664</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1946099379</v>
+        <v>1550.1946673374</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.0059577644</v>
+        <v>55807.0080241464</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7456,10 +7456,10 @@
         <v>48</v>
       </c>
       <c r="N163" t="n">
-        <v>1579.3838288288</v>
+        <v>1579.3828229665</v>
       </c>
       <c r="O163" t="n">
-        <v>75810.4237837824</v>
+        <v>75810.37550239201</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -7667,10 +7667,10 @@
         <v>1057</v>
       </c>
       <c r="N168" t="n">
-        <v>1301.3994036697</v>
+        <v>1302.8935476464</v>
       </c>
       <c r="O168" t="n">
-        <v>1375579.169678873</v>
+        <v>1377158.479862245</v>
       </c>
       <c r="P168" t="n">
         <v>2000</v>
@@ -8797,10 +8797,10 @@
         <v>348</v>
       </c>
       <c r="N194" t="n">
-        <v>2029.8741413584</v>
+        <v>2029.8741689828</v>
       </c>
       <c r="O194" t="n">
-        <v>706396.2011927232</v>
+        <v>706396.2108060144</v>
       </c>
       <c r="P194" t="n">
         <v>3600</v>
@@ -9002,10 +9002,10 @@
         <v>170</v>
       </c>
       <c r="N199" t="n">
-        <v>2680.7396939413</v>
+        <v>2680.7396933667</v>
       </c>
       <c r="O199" t="n">
-        <v>455725.747970021</v>
+        <v>455725.747872339</v>
       </c>
       <c r="P199" t="n">
         <v>4900</v>
@@ -9696,10 +9696,10 @@
         <v>707</v>
       </c>
       <c r="N215" t="n">
-        <v>4814.2679260066</v>
+        <v>4814.2679256837</v>
       </c>
       <c r="O215" t="n">
-        <v>3403687.423686666</v>
+        <v>3403687.423458376</v>
       </c>
       <c r="P215" t="n">
         <v>9900</v>
@@ -10249,10 +10249,10 @@
         <v>180</v>
       </c>
       <c r="N228" t="n">
-        <v>7969.9501697531</v>
+        <v>7969.9501704105</v>
       </c>
       <c r="O228" t="n">
-        <v>1434591.030555558</v>
+        <v>1434591.03067389</v>
       </c>
       <c r="P228" t="n">
         <v>12900</v>
@@ -10521,10 +10521,10 @@
         <v>154</v>
       </c>
       <c r="N234" t="n">
-        <v>548.14709290709</v>
+        <v>548.14707537688</v>
       </c>
       <c r="O234" t="n">
-        <v>84414.65230769187</v>
+        <v>84414.64960803953</v>
       </c>
       <c r="P234" t="n">
         <v>2000</v>
@@ -11608,10 +11608,10 @@
         <v>952</v>
       </c>
       <c r="N258" t="n">
-        <v>1778.4728348758</v>
+        <v>1778.4728413344</v>
       </c>
       <c r="O258" t="n">
-        <v>1693106.138801761</v>
+        <v>1693106.144950349</v>
       </c>
       <c r="P258" t="n">
         <v>4900</v>
@@ -12436,10 +12436,10 @@
         <v>15</v>
       </c>
       <c r="N276" t="n">
-        <v>3259.2102631579</v>
+        <v>3259.2102666667</v>
       </c>
       <c r="O276" t="n">
-        <v>48888.1539473685</v>
+        <v>48888.1540000005</v>
       </c>
       <c r="P276" t="n">
         <v>5300</v>
@@ -13876,10 +13876,10 @@
         <v>263</v>
       </c>
       <c r="N307" t="n">
-        <v>2252.2981374046</v>
+        <v>2252.298328125</v>
       </c>
       <c r="O307" t="n">
-        <v>592354.4101374098</v>
+        <v>592354.460296875</v>
       </c>
       <c r="P307" t="n">
         <v>3900</v>
@@ -14063,10 +14063,10 @@
         <v>504</v>
       </c>
       <c r="N311" t="n">
-        <v>2328.1186615921</v>
+        <v>2328.118659892</v>
       </c>
       <c r="O311" t="n">
-        <v>1173371.805442418</v>
+        <v>1173371.804585568</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
@@ -14477,10 +14477,10 @@
         <v>100</v>
       </c>
       <c r="N320" t="n">
-        <v>4907.8226736842</v>
+        <v>4907.822690678</v>
       </c>
       <c r="O320" t="n">
-        <v>490782.26736842</v>
+        <v>490782.2690678</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -14707,10 +14707,10 @@
         <v>84</v>
       </c>
       <c r="N325" t="n">
-        <v>3903.7392422907</v>
+        <v>3903.7394479074</v>
       </c>
       <c r="O325" t="n">
-        <v>327914.0963524188</v>
+        <v>327914.1136242216</v>
       </c>
       <c r="P325" t="n">
         <v>7500</v>
@@ -15932,7 +15932,7 @@
         </is>
       </c>
       <c r="J352" t="n">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
@@ -15941,19 +15941,19 @@
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="N352" t="n">
         <v>3639.35</v>
       </c>
       <c r="O352" t="n">
-        <v>826132.45</v>
+        <v>793378.2999999999</v>
       </c>
       <c r="P352" t="n">
         <v>7500</v>
       </c>
       <c r="Q352" t="n">
-        <v>1702500</v>
+        <v>1635000</v>
       </c>
     </row>
     <row r="353">
@@ -16174,10 +16174,10 @@
         <v>839</v>
       </c>
       <c r="N357" t="n">
-        <v>1516.0387397625</v>
+        <v>1516.0387386003</v>
       </c>
       <c r="O357" t="n">
-        <v>1271956.502660737</v>
+        <v>1271956.501685652</v>
       </c>
       <c r="P357" t="n">
         <v>2300</v>
@@ -16581,10 +16581,10 @@
         <v>2063</v>
       </c>
       <c r="N366" t="n">
-        <v>692.1524140338601</v>
+        <v>692.15241910093</v>
       </c>
       <c r="O366" t="n">
-        <v>1427910.430151853</v>
+        <v>1427910.440605219</v>
       </c>
       <c r="P366" t="n">
         <v>1200</v>
@@ -17359,10 +17359,10 @@
         <v>780</v>
       </c>
       <c r="N382" t="n">
-        <v>1530.4499182339</v>
+        <v>1530.4499180664</v>
       </c>
       <c r="O382" t="n">
-        <v>1193750.936222442</v>
+        <v>1193750.936091792</v>
       </c>
       <c r="P382" t="n">
         <v>2600</v>
@@ -17779,10 +17779,10 @@
         <v>158</v>
       </c>
       <c r="N391" t="n">
-        <v>1690.8700093809</v>
+        <v>1690.8700094029</v>
       </c>
       <c r="O391" t="n">
-        <v>267157.4614821822</v>
+        <v>267157.4614856582</v>
       </c>
       <c r="P391" t="n">
         <v>3000</v>
@@ -18014,10 +18014,10 @@
         <v>5845</v>
       </c>
       <c r="N396" t="n">
-        <v>345.55838597724</v>
+        <v>345.55838583542</v>
       </c>
       <c r="O396" t="n">
-        <v>2019788.766036968</v>
+        <v>2019788.76520803</v>
       </c>
       <c r="P396" t="n">
         <v>600</v>
@@ -18156,10 +18156,10 @@
         <v>7734</v>
       </c>
       <c r="N399" t="n">
-        <v>711.33664519481</v>
+        <v>711.33664496242</v>
       </c>
       <c r="O399" t="n">
-        <v>5501477.613936661</v>
+        <v>5501477.612139356</v>
       </c>
       <c r="P399" t="n">
         <v>900</v>
@@ -18672,10 +18672,10 @@
         <v>132</v>
       </c>
       <c r="N410" t="n">
-        <v>3259.13444</v>
+        <v>3259.134625</v>
       </c>
       <c r="O410" t="n">
-        <v>430205.74608</v>
+        <v>430205.7705</v>
       </c>
       <c r="P410" t="n">
         <v>3600</v>
@@ -18808,10 +18808,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.837275018</v>
+        <v>3110.8368831169</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.674550036</v>
+        <v>6221.6737662338</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18998,10 +18998,10 @@
         <v>127</v>
       </c>
       <c r="N417" t="n">
-        <v>3182.2511299435</v>
+        <v>3182.2511320755</v>
       </c>
       <c r="O417" t="n">
-        <v>404145.8935028245</v>
+        <v>404145.8937735885</v>
       </c>
       <c r="P417" t="n">
         <v>6900</v>
@@ -19182,10 +19182,10 @@
         <v>4</v>
       </c>
       <c r="N421" t="n">
-        <v>2501.3844329897</v>
+        <v>2501.3844041451</v>
       </c>
       <c r="O421" t="n">
-        <v>10005.5377319588</v>
+        <v>10005.5376165804</v>
       </c>
       <c r="P421" t="n">
         <v>4100</v>
@@ -21679,10 +21679,10 @@
         <v>152</v>
       </c>
       <c r="N473" t="n">
-        <v>7046.9398269522</v>
+        <v>7046.9398267273</v>
       </c>
       <c r="O473" t="n">
-        <v>1071134.853696734</v>
+        <v>1071134.85366255</v>
       </c>
       <c r="P473" t="n">
         <v>9900</v>
@@ -22310,10 +22310,10 @@
         <v>67</v>
       </c>
       <c r="N486" t="n">
-        <v>44113.604171779</v>
+        <v>44113.604197531</v>
       </c>
       <c r="O486" t="n">
-        <v>2955611.479509193</v>
+        <v>2955611.481234577</v>
       </c>
       <c r="P486" t="n">
         <v>71900</v>
@@ -22405,10 +22405,10 @@
         <v>981</v>
       </c>
       <c r="N488" t="n">
-        <v>665.32397155917</v>
+        <v>665.32398369842</v>
       </c>
       <c r="O488" t="n">
-        <v>652682.8160995458</v>
+        <v>652682.82800815</v>
       </c>
       <c r="P488" t="n">
         <v>2900</v>
@@ -22647,10 +22647,10 @@
         <v>288</v>
       </c>
       <c r="N493" t="n">
-        <v>430.60997550521</v>
+        <v>430.60997530864</v>
       </c>
       <c r="O493" t="n">
-        <v>124015.6729455005</v>
+        <v>124015.6728888883</v>
       </c>
       <c r="P493" t="n">
         <v>2200</v>
@@ -24839,10 +24839,10 @@
         <v>93</v>
       </c>
       <c r="N541" t="n">
-        <v>3982.670776699</v>
+        <v>3982.6708</v>
       </c>
       <c r="O541" t="n">
-        <v>370388.382233007</v>
+        <v>370388.3844</v>
       </c>
       <c r="P541" t="n">
         <v>10900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -7667,10 +7667,10 @@
         <v>1057</v>
       </c>
       <c r="N168" t="n">
-        <v>1302.8935476464</v>
+        <v>1301.3994029851</v>
       </c>
       <c r="O168" t="n">
-        <v>1377158.479862245</v>
+        <v>1375579.168955251</v>
       </c>
       <c r="P168" t="n">
         <v>2000</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8551705566</v>
+        <v>6272.8551798561</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.578779188</v>
+        <v>1794036.581438845</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0684371373</v>
+        <v>1098.0685808709</v>
       </c>
       <c r="O70" t="n">
-        <v>129572.0755822014</v>
+        <v>129572.0925427662</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4706,10 +4706,10 @@
         <v>179</v>
       </c>
       <c r="N102" t="n">
-        <v>3795.7100076176</v>
+        <v>3795.7100076234</v>
       </c>
       <c r="O102" t="n">
-        <v>679432.0913635504</v>
+        <v>679432.0913645886</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -4885,10 +4885,10 @@
         <v>390</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300534045</v>
+        <v>4890.9300534402</v>
       </c>
       <c r="O106" t="n">
-        <v>1907462.720827755</v>
+        <v>1907462.720841678</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
@@ -5732,10 +5732,10 @@
         <v>2442</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2762167406</v>
+        <v>3472.276224504</v>
       </c>
       <c r="O125" t="n">
-        <v>8479298.521280546</v>
+        <v>8479298.540238768</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600141844</v>
+        <v>3041.6600141945</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.667106384</v>
+        <v>1523871.667111445</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5912,10 +5912,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1712629569</v>
+        <v>4371.7675214841</v>
       </c>
       <c r="O129" t="n">
-        <v>4852000.101882159</v>
+        <v>4852661.948847352</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -6004,10 +6004,10 @@
         <v>756</v>
       </c>
       <c r="N131" t="n">
-        <v>3655.96</v>
+        <v>3668.2806919793</v>
       </c>
       <c r="O131" t="n">
-        <v>2763905.76</v>
+        <v>2773220.203136351</v>
       </c>
       <c r="P131" t="n">
         <v>5500</v>
@@ -6268,10 +6268,10 @@
         <v>798</v>
       </c>
       <c r="N137" t="n">
-        <v>4648.6</v>
+        <v>4649.4131187686</v>
       </c>
       <c r="O137" t="n">
-        <v>3709582.8</v>
+        <v>3710231.668777343</v>
       </c>
       <c r="P137" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9246047904</v>
+        <v>1630.9246075494</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.5995149664</v>
+        <v>311506.6000419354</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1946673374</v>
+        <v>1551.3666948085</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.0080241464</v>
+        <v>55849.20101310599</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -8510,10 +8510,10 @@
         <v>1</v>
       </c>
       <c r="N187" t="n">
-        <v>2661.82</v>
+        <v>2668.524836272</v>
       </c>
       <c r="O187" t="n">
-        <v>2661.82</v>
+        <v>2668.524836272</v>
       </c>
       <c r="P187" t="n">
         <v>3200</v>
@@ -8756,10 +8756,10 @@
         <v>491</v>
       </c>
       <c r="N193" t="n">
-        <v>2517.22</v>
+        <v>2545.636406397</v>
       </c>
       <c r="O193" t="n">
-        <v>1235955.02</v>
+        <v>1249907.475540927</v>
       </c>
       <c r="P193" t="n">
         <v>4200</v>
@@ -9859,22 +9859,22 @@
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M219" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N219" t="n">
-        <v>4100.45</v>
+        <v>4107.6818342152</v>
       </c>
       <c r="O219" t="n">
-        <v>930802.1499999999</v>
+        <v>920120.7308642048</v>
       </c>
       <c r="P219" t="n">
         <v>26900</v>
       </c>
       <c r="Q219" t="n">
-        <v>6106300</v>
+        <v>6025600</v>
       </c>
     </row>
     <row r="220">
@@ -10249,10 +10249,10 @@
         <v>180</v>
       </c>
       <c r="N228" t="n">
-        <v>7969.9501704105</v>
+        <v>7969.9501706749</v>
       </c>
       <c r="O228" t="n">
-        <v>1434591.03067389</v>
+        <v>1434591.030721482</v>
       </c>
       <c r="P228" t="n">
         <v>12900</v>
@@ -10521,10 +10521,10 @@
         <v>154</v>
       </c>
       <c r="N234" t="n">
-        <v>548.14707537688</v>
+        <v>548.1470665322601</v>
       </c>
       <c r="O234" t="n">
-        <v>84414.64960803953</v>
+        <v>84414.64824596806</v>
       </c>
       <c r="P234" t="n">
         <v>2000</v>
@@ -11608,10 +11608,10 @@
         <v>952</v>
       </c>
       <c r="N258" t="n">
-        <v>1778.4728413344</v>
+        <v>1778.4728487518</v>
       </c>
       <c r="O258" t="n">
-        <v>1693106.144950349</v>
+        <v>1693106.152011714</v>
       </c>
       <c r="P258" t="n">
         <v>4900</v>
@@ -13876,10 +13876,10 @@
         <v>263</v>
       </c>
       <c r="N307" t="n">
-        <v>2252.298328125</v>
+        <v>2252.2983673469</v>
       </c>
       <c r="O307" t="n">
-        <v>592354.460296875</v>
+        <v>592354.4706122347</v>
       </c>
       <c r="P307" t="n">
         <v>3900</v>
@@ -14523,10 +14523,10 @@
         <v>24</v>
       </c>
       <c r="N321" t="n">
-        <v>6414</v>
+        <v>6426.9445005045</v>
       </c>
       <c r="O321" t="n">
-        <v>153936</v>
+        <v>154246.668012108</v>
       </c>
       <c r="P321" t="n">
         <v>10900</v>
@@ -14707,10 +14707,10 @@
         <v>84</v>
       </c>
       <c r="N325" t="n">
-        <v>3903.7394479074</v>
+        <v>3903.7394652406</v>
       </c>
       <c r="O325" t="n">
-        <v>327914.1136242216</v>
+        <v>327914.1150802104</v>
       </c>
       <c r="P325" t="n">
         <v>7500</v>
@@ -15121,10 +15121,10 @@
         <v>224</v>
       </c>
       <c r="N334" t="n">
-        <v>6645</v>
+        <v>6648.7102177554</v>
       </c>
       <c r="O334" t="n">
-        <v>1488480</v>
+        <v>1489311.08877721</v>
       </c>
       <c r="P334" t="n">
         <v>10900</v>
@@ -15259,10 +15259,10 @@
         <v>159</v>
       </c>
       <c r="N337" t="n">
-        <v>3898</v>
+        <v>3904.464344942</v>
       </c>
       <c r="O337" t="n">
-        <v>619782</v>
+        <v>620809.830845778</v>
       </c>
       <c r="P337" t="n">
         <v>6900</v>
@@ -17359,10 +17359,10 @@
         <v>780</v>
       </c>
       <c r="N382" t="n">
-        <v>1530.4499180664</v>
+        <v>1538.0108069164</v>
       </c>
       <c r="O382" t="n">
-        <v>1193750.936091792</v>
+        <v>1199648.429394792</v>
       </c>
       <c r="P382" t="n">
         <v>2600</v>
@@ -18808,10 +18808,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8368831169</v>
+        <v>3110.8366754617</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.6737662338</v>
+        <v>6221.6733509234</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -22647,10 +22647,10 @@
         <v>288</v>
       </c>
       <c r="N493" t="n">
-        <v>430.60997530864</v>
+        <v>430.60997520149</v>
       </c>
       <c r="O493" t="n">
-        <v>124015.6728888883</v>
+        <v>124015.6728580291</v>
       </c>
       <c r="P493" t="n">
         <v>2200</v>
@@ -25565,10 +25565,10 @@
         <v>21</v>
       </c>
       <c r="N557" t="n">
-        <v>1059.1847727273</v>
+        <v>1059.1855263158</v>
       </c>
       <c r="O557" t="n">
-        <v>22242.8802272733</v>
+        <v>22242.8960526318</v>
       </c>
       <c r="P557" t="n">
         <v>9500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q558"/>
+  <dimension ref="A1:Q557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -2755,10 +2755,10 @@
         <v>9</v>
       </c>
       <c r="N58" t="n">
-        <v>11108.253513514</v>
+        <v>11108.253333333</v>
       </c>
       <c r="O58" t="n">
-        <v>99974.28162162601</v>
+        <v>99974.279999997</v>
       </c>
       <c r="P58" t="n">
         <v>18900</v>
@@ -2840,10 +2840,10 @@
         <v>148</v>
       </c>
       <c r="N60" t="n">
-        <v>1950.2139095128</v>
+        <v>1950.2137350835</v>
       </c>
       <c r="O60" t="n">
-        <v>288631.6586078944</v>
+        <v>288631.632792358</v>
       </c>
       <c r="P60" t="n">
         <v>2900</v>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3458,19 +3458,19 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N74" t="n">
         <v>18291</v>
       </c>
       <c r="O74" t="n">
-        <v>420693</v>
+        <v>310947</v>
       </c>
       <c r="P74" t="n">
         <v>22900</v>
       </c>
       <c r="Q74" t="n">
-        <v>526700</v>
+        <v>389300</v>
       </c>
     </row>
     <row r="75">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3504,19 +3504,19 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="N75" t="n">
         <v>13593.35</v>
       </c>
       <c r="O75" t="n">
-        <v>2963350.3</v>
+        <v>2664296.6</v>
       </c>
       <c r="P75" t="n">
         <v>25500</v>
       </c>
       <c r="Q75" t="n">
-        <v>5559000</v>
+        <v>4998000</v>
       </c>
     </row>
     <row r="76">
@@ -4706,10 +4706,10 @@
         <v>179</v>
       </c>
       <c r="N102" t="n">
-        <v>3795.7100076234</v>
+        <v>3795.7100076292</v>
       </c>
       <c r="O102" t="n">
-        <v>679432.0913645886</v>
+        <v>679432.0913656268</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4882,19 +4882,19 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="N106" t="n">
         <v>4890.9300534402</v>
       </c>
       <c r="O106" t="n">
-        <v>1907462.720841678</v>
+        <v>1809644.119772874</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
       </c>
       <c r="Q106" t="n">
-        <v>3198000</v>
+        <v>3034000</v>
       </c>
     </row>
     <row r="107">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -5066,19 +5066,19 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="N110" t="n">
         <v>5667.94</v>
       </c>
       <c r="O110" t="n">
-        <v>3287405.2</v>
+        <v>3174046.4</v>
       </c>
       <c r="P110" t="n">
         <v>9500</v>
       </c>
       <c r="Q110" t="n">
-        <v>5510000</v>
+        <v>5320000</v>
       </c>
     </row>
     <row r="111">
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5503,19 +5503,19 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="N120" t="n">
         <v>2665.4</v>
       </c>
       <c r="O120" t="n">
-        <v>1727179.2</v>
+        <v>1711186.8</v>
       </c>
       <c r="P120" t="n">
         <v>20900</v>
       </c>
       <c r="Q120" t="n">
-        <v>13543200</v>
+        <v>13417800</v>
       </c>
     </row>
     <row r="121">
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5598,19 +5598,19 @@
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="N122" t="n">
         <v>12422.462959583</v>
       </c>
       <c r="O122" t="n">
-        <v>3590091.795319487</v>
+        <v>3503134.554602406</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
       </c>
       <c r="Q122" t="n">
-        <v>5751100</v>
+        <v>5611800</v>
       </c>
     </row>
     <row r="123">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>2442</v>
+        <v>2406</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5729,19 +5729,19 @@
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>2442</v>
+        <v>2406</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.276224504</v>
+        <v>3472.2762270961</v>
       </c>
       <c r="O125" t="n">
-        <v>8479298.540238768</v>
+        <v>8354296.602393216</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
       </c>
       <c r="Q125" t="n">
-        <v>14407800</v>
+        <v>14195400</v>
       </c>
     </row>
     <row r="126">
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600141945</v>
+        <v>3041.6600142959</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.667111445</v>
+        <v>1523871.667162246</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1110</v>
+        <v>1101</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5909,19 +5909,19 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>1110</v>
+        <v>1101</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.7675214841</v>
+        <v>4371.1712631292</v>
       </c>
       <c r="O129" t="n">
-        <v>4852661.948847352</v>
+        <v>4812659.560705249</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
       </c>
       <c r="Q129" t="n">
-        <v>9879000</v>
+        <v>9798900</v>
       </c>
     </row>
     <row r="130">
@@ -6004,10 +6004,10 @@
         <v>756</v>
       </c>
       <c r="N131" t="n">
-        <v>3668.2806919793</v>
+        <v>3655.96</v>
       </c>
       <c r="O131" t="n">
-        <v>2773220.203136351</v>
+        <v>2763905.76</v>
       </c>
       <c r="P131" t="n">
         <v>5500</v>
@@ -6268,10 +6268,10 @@
         <v>798</v>
       </c>
       <c r="N137" t="n">
-        <v>4649.4131187686</v>
+        <v>4648.6</v>
       </c>
       <c r="O137" t="n">
-        <v>3710231.668777343</v>
+        <v>3709582.8</v>
       </c>
       <c r="P137" t="n">
         <v>8900</v>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6626,19 +6626,19 @@
         <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="N145" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O145" t="n">
-        <v>517787.05</v>
+        <v>480129.81</v>
       </c>
       <c r="P145" t="n">
         <v>16900</v>
       </c>
       <c r="Q145" t="n">
-        <v>929500</v>
+        <v>861900</v>
       </c>
     </row>
     <row r="146">
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -6905,19 +6905,19 @@
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="N151" t="n">
         <v>13304.13</v>
       </c>
       <c r="O151" t="n">
-        <v>1516670.82</v>
+        <v>1343717.13</v>
       </c>
       <c r="P151" t="n">
         <v>20900</v>
       </c>
       <c r="Q151" t="n">
-        <v>2382600</v>
+        <v>2110900</v>
       </c>
     </row>
     <row r="152">
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9246075494</v>
+        <v>1630.9246283479</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.6000419354</v>
+        <v>311506.6040144489</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1551.3666948085</v>
+        <v>1550.1947087933</v>
       </c>
       <c r="O162" t="n">
-        <v>55849.20101310599</v>
+        <v>55807.0095165588</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7456,10 +7456,10 @@
         <v>48</v>
       </c>
       <c r="N163" t="n">
-        <v>1579.3828229665</v>
+        <v>1579.3814948454</v>
       </c>
       <c r="O163" t="n">
-        <v>75810.37550239201</v>
+        <v>75810.3117525792</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7899,19 +7899,19 @@
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N173" t="n">
         <v>12264.63</v>
       </c>
       <c r="O173" t="n">
-        <v>809465.58</v>
+        <v>735877.7999999999</v>
       </c>
       <c r="P173" t="n">
         <v>17900</v>
       </c>
       <c r="Q173" t="n">
-        <v>1181400</v>
+        <v>1074000</v>
       </c>
     </row>
     <row r="174">
@@ -8346,10 +8346,10 @@
         <v>674</v>
       </c>
       <c r="N183" t="n">
-        <v>4196.872541806</v>
+        <v>4196.8725453531</v>
       </c>
       <c r="O183" t="n">
-        <v>2828692.093177244</v>
+        <v>2828692.095567989</v>
       </c>
       <c r="P183" t="n">
         <v>5900</v>
@@ -8469,10 +8469,10 @@
         <v>91</v>
       </c>
       <c r="N186" t="n">
-        <v>7537.4723387097</v>
+        <v>7537.4723577236</v>
       </c>
       <c r="O186" t="n">
-        <v>685909.9828225827</v>
+        <v>685909.9845528476</v>
       </c>
       <c r="P186" t="n">
         <v>8900</v>
@@ -8510,10 +8510,10 @@
         <v>1</v>
       </c>
       <c r="N187" t="n">
-        <v>2668.524836272</v>
+        <v>2661.82</v>
       </c>
       <c r="O187" t="n">
-        <v>2668.524836272</v>
+        <v>2661.82</v>
       </c>
       <c r="P187" t="n">
         <v>3200</v>
@@ -8756,10 +8756,10 @@
         <v>491</v>
       </c>
       <c r="N193" t="n">
-        <v>2545.636406397</v>
+        <v>2517.22</v>
       </c>
       <c r="O193" t="n">
-        <v>1249907.475540927</v>
+        <v>1235955.02</v>
       </c>
       <c r="P193" t="n">
         <v>4200</v>
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -8835,19 +8835,19 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="N195" t="n">
-        <v>22485.695454545</v>
+        <v>22485.695448799</v>
       </c>
       <c r="O195" t="n">
-        <v>3530254.186363565</v>
+        <v>3327882.926422252</v>
       </c>
       <c r="P195" t="n">
         <v>36500</v>
       </c>
       <c r="Q195" t="n">
-        <v>5730500</v>
+        <v>5402000</v>
       </c>
     </row>
     <row r="196">
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -9086,19 +9086,19 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="N201" t="n">
         <v>14060.64</v>
       </c>
       <c r="O201" t="n">
-        <v>365576.64</v>
+        <v>253091.52</v>
       </c>
       <c r="P201" t="n">
         <v>22900</v>
       </c>
       <c r="Q201" t="n">
-        <v>595400</v>
+        <v>412200</v>
       </c>
     </row>
     <row r="202">
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9734,19 +9734,19 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="N216" t="n">
         <v>3591.13</v>
       </c>
       <c r="O216" t="n">
-        <v>3314612.99</v>
+        <v>3260746.04</v>
       </c>
       <c r="P216" t="n">
         <v>6300</v>
       </c>
       <c r="Q216" t="n">
-        <v>5814900</v>
+        <v>5720400</v>
       </c>
     </row>
     <row r="217">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9821,19 +9821,19 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N218" t="n">
         <v>27123.764828283</v>
       </c>
       <c r="O218" t="n">
-        <v>1003579.298646471</v>
+        <v>867960.474505056</v>
       </c>
       <c r="P218" t="n">
         <v>44500</v>
       </c>
       <c r="Q218" t="n">
-        <v>1646500</v>
+        <v>1424000</v>
       </c>
     </row>
     <row r="219">
@@ -9853,28 +9853,28 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N219" t="n">
-        <v>4107.6818342152</v>
+        <v>4100.45</v>
       </c>
       <c r="O219" t="n">
-        <v>920120.7308642048</v>
+        <v>910299.8999999999</v>
       </c>
       <c r="P219" t="n">
         <v>26900</v>
       </c>
       <c r="Q219" t="n">
-        <v>6025600</v>
+        <v>5971800</v>
       </c>
     </row>
     <row r="220">
@@ -10249,10 +10249,10 @@
         <v>180</v>
       </c>
       <c r="N228" t="n">
-        <v>7969.9501706749</v>
+        <v>7969.9501710731</v>
       </c>
       <c r="O228" t="n">
-        <v>1434591.030721482</v>
+        <v>1434591.030793158</v>
       </c>
       <c r="P228" t="n">
         <v>12900</v>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10287,19 +10287,19 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N229" t="n">
         <v>8968.24</v>
       </c>
       <c r="O229" t="n">
-        <v>107618.88</v>
+        <v>17936.48</v>
       </c>
       <c r="P229" t="n">
         <v>18600</v>
       </c>
       <c r="Q229" t="n">
-        <v>223200</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="230">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -11339,19 +11339,19 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N252" t="n">
         <v>27307</v>
       </c>
       <c r="O252" t="n">
-        <v>163842</v>
+        <v>54614</v>
       </c>
       <c r="P252" t="n">
         <v>44900</v>
       </c>
       <c r="Q252" t="n">
-        <v>269400</v>
+        <v>89800</v>
       </c>
     </row>
     <row r="253">
@@ -11480,10 +11480,10 @@
         <v>3</v>
       </c>
       <c r="N255" t="n">
-        <v>23521.623</v>
+        <v>23521.622708333</v>
       </c>
       <c r="O255" t="n">
-        <v>70564.86900000001</v>
+        <v>70564.868124999</v>
       </c>
       <c r="P255" t="n">
         <v>39000</v>
@@ -11608,10 +11608,10 @@
         <v>952</v>
       </c>
       <c r="N258" t="n">
-        <v>1778.4728487518</v>
+        <v>1778.4728562081</v>
       </c>
       <c r="O258" t="n">
-        <v>1693106.152011714</v>
+        <v>1693106.159110111</v>
       </c>
       <c r="P258" t="n">
         <v>4900</v>
@@ -14063,10 +14063,10 @@
         <v>504</v>
       </c>
       <c r="N311" t="n">
-        <v>2328.118659892</v>
+        <v>2328.1186586141</v>
       </c>
       <c r="O311" t="n">
-        <v>1173371.804585568</v>
+        <v>1173371.803941506</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
@@ -14523,10 +14523,10 @@
         <v>24</v>
       </c>
       <c r="N321" t="n">
-        <v>6426.9445005045</v>
+        <v>6414</v>
       </c>
       <c r="O321" t="n">
-        <v>154246.668012108</v>
+        <v>153936</v>
       </c>
       <c r="P321" t="n">
         <v>10900</v>
@@ -14707,10 +14707,10 @@
         <v>84</v>
       </c>
       <c r="N325" t="n">
-        <v>3903.7394652406</v>
+        <v>3903.7395348837</v>
       </c>
       <c r="O325" t="n">
-        <v>327914.1150802104</v>
+        <v>327914.1209302308</v>
       </c>
       <c r="P325" t="n">
         <v>7500</v>
@@ -14741,7 +14741,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -14750,19 +14750,19 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N326" t="n">
         <v>33000</v>
       </c>
       <c r="O326" t="n">
-        <v>429000</v>
+        <v>231000</v>
       </c>
       <c r="P326" t="n">
         <v>52900</v>
       </c>
       <c r="Q326" t="n">
-        <v>687700</v>
+        <v>370300</v>
       </c>
     </row>
     <row r="327">
@@ -15121,10 +15121,10 @@
         <v>224</v>
       </c>
       <c r="N334" t="n">
-        <v>6648.7102177554</v>
+        <v>6645</v>
       </c>
       <c r="O334" t="n">
-        <v>1489311.08877721</v>
+        <v>1488480</v>
       </c>
       <c r="P334" t="n">
         <v>10900</v>
@@ -15201,7 +15201,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -15210,19 +15210,19 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N336" t="n">
         <v>27186</v>
       </c>
       <c r="O336" t="n">
-        <v>326232</v>
+        <v>190302</v>
       </c>
       <c r="P336" t="n">
         <v>43900</v>
       </c>
       <c r="Q336" t="n">
-        <v>526800</v>
+        <v>307300</v>
       </c>
     </row>
     <row r="337">
@@ -15259,10 +15259,10 @@
         <v>159</v>
       </c>
       <c r="N337" t="n">
-        <v>3904.464344942</v>
+        <v>3898</v>
       </c>
       <c r="O337" t="n">
-        <v>620809.830845778</v>
+        <v>619782</v>
       </c>
       <c r="P337" t="n">
         <v>6900</v>
@@ -16174,10 +16174,10 @@
         <v>839</v>
       </c>
       <c r="N357" t="n">
-        <v>1516.0387386003</v>
+        <v>1516.0387367881</v>
       </c>
       <c r="O357" t="n">
-        <v>1271956.501685652</v>
+        <v>1271956.500165216</v>
       </c>
       <c r="P357" t="n">
         <v>2300</v>
@@ -16581,10 +16581,10 @@
         <v>2063</v>
       </c>
       <c r="N366" t="n">
-        <v>692.15241910093</v>
+        <v>692.15242929914</v>
       </c>
       <c r="O366" t="n">
-        <v>1427910.440605219</v>
+        <v>1427910.461644126</v>
       </c>
       <c r="P366" t="n">
         <v>1200</v>
@@ -16716,7 +16716,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -16725,19 +16725,19 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="N369" t="n">
         <v>13518</v>
       </c>
       <c r="O369" t="n">
-        <v>7962102</v>
+        <v>7894512</v>
       </c>
       <c r="P369" t="n">
         <v>21900</v>
       </c>
       <c r="Q369" t="n">
-        <v>12899100</v>
+        <v>12789600</v>
       </c>
     </row>
     <row r="370">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="J370" t="n">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="K370" t="n">
         <v>0</v>
@@ -16774,19 +16774,19 @@
         <v>0</v>
       </c>
       <c r="M370" t="n">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="N370" t="n">
         <v>9736</v>
       </c>
       <c r="O370" t="n">
-        <v>6902824</v>
+        <v>6815200</v>
       </c>
       <c r="P370" t="n">
         <v>15900</v>
       </c>
       <c r="Q370" t="n">
-        <v>11273100</v>
+        <v>11130000</v>
       </c>
     </row>
     <row r="371">
@@ -16863,7 +16863,7 @@
         </is>
       </c>
       <c r="J372" t="n">
-        <v>1044</v>
+        <v>999</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
@@ -16872,19 +16872,19 @@
         <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>1044</v>
+        <v>999</v>
       </c>
       <c r="N372" t="n">
         <v>5215</v>
       </c>
       <c r="O372" t="n">
-        <v>5444460</v>
+        <v>5209785</v>
       </c>
       <c r="P372" t="n">
         <v>8900</v>
       </c>
       <c r="Q372" t="n">
-        <v>9291600</v>
+        <v>8891100</v>
       </c>
     </row>
     <row r="373">
@@ -17359,10 +17359,10 @@
         <v>780</v>
       </c>
       <c r="N382" t="n">
-        <v>1538.0108069164</v>
+        <v>1530.4499180664</v>
       </c>
       <c r="O382" t="n">
-        <v>1199648.429394792</v>
+        <v>1193750.936091792</v>
       </c>
       <c r="P382" t="n">
         <v>2600</v>
@@ -17779,10 +17779,10 @@
         <v>158</v>
       </c>
       <c r="N391" t="n">
-        <v>1690.8700094029</v>
+        <v>1690.8700094251</v>
       </c>
       <c r="O391" t="n">
-        <v>267157.4614856582</v>
+        <v>267157.4614891658</v>
       </c>
       <c r="P391" t="n">
         <v>3000</v>
@@ -18808,10 +18808,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8366754617</v>
+        <v>3110.8366199849</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.6733509234</v>
+        <v>6221.6732399698</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -19742,10 +19742,10 @@
         <v>381</v>
       </c>
       <c r="N433" t="n">
-        <v>1595.4991666667</v>
+        <v>1595.4982940252</v>
       </c>
       <c r="O433" t="n">
-        <v>607885.1825000127</v>
+        <v>607884.8500236012</v>
       </c>
       <c r="P433" t="n">
         <v>2500</v>
@@ -20309,7 +20309,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -20318,19 +20318,19 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N445" t="n">
         <v>3100.87</v>
       </c>
       <c r="O445" t="n">
-        <v>114732.19</v>
+        <v>83723.48999999999</v>
       </c>
       <c r="P445" t="n">
         <v>9900</v>
       </c>
       <c r="Q445" t="n">
-        <v>366300</v>
+        <v>267300</v>
       </c>
     </row>
     <row r="446">
@@ -21679,10 +21679,10 @@
         <v>152</v>
       </c>
       <c r="N473" t="n">
-        <v>7046.9398267273</v>
+        <v>7046.9398265771</v>
       </c>
       <c r="O473" t="n">
-        <v>1071134.85366255</v>
+        <v>1071134.853639719</v>
       </c>
       <c r="P473" t="n">
         <v>9900</v>
@@ -24015,7 +24015,7 @@
         </is>
       </c>
       <c r="J524" t="n">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -24024,19 +24024,19 @@
         <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="N524" t="n">
         <v>7480</v>
       </c>
       <c r="O524" t="n">
-        <v>2692800</v>
+        <v>2513280</v>
       </c>
       <c r="P524" t="n">
         <v>9500</v>
       </c>
       <c r="Q524" t="n">
-        <v>3420000</v>
+        <v>3192000</v>
       </c>
     </row>
     <row r="525">
@@ -24568,22 +24568,17 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>MG20930</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>MG20930</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>CARRO BUGGY RECARGABLE MG20930</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -24592,7 +24587,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -24601,35 +24596,35 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="N536" t="n">
-        <v>63353.92</v>
+        <v>1129.14</v>
       </c>
       <c r="O536" t="n">
-        <v>380123.52</v>
+        <v>91460.34000000001</v>
       </c>
       <c r="P536" t="n">
-        <v>128000</v>
+        <v>6900</v>
       </c>
       <c r="Q536" t="n">
-        <v>768000</v>
+        <v>558900</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG27668</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -24638,7 +24633,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24647,30 +24642,30 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="N537" t="n">
-        <v>1129.14</v>
+        <v>15239.8</v>
       </c>
       <c r="O537" t="n">
-        <v>91460.34000000001</v>
+        <v>243836.8</v>
       </c>
       <c r="P537" t="n">
-        <v>6900</v>
+        <v>15900</v>
       </c>
       <c r="Q537" t="n">
-        <v>558900</v>
+        <v>254400</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>MG27668</t>
+          <t>MG28914</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
+          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -24684,7 +24679,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -24693,35 +24688,35 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="N538" t="n">
-        <v>15239.8</v>
+        <v>5563</v>
       </c>
       <c r="O538" t="n">
-        <v>320035.8</v>
+        <v>5563</v>
       </c>
       <c r="P538" t="n">
-        <v>15900</v>
+        <v>11900</v>
       </c>
       <c r="Q538" t="n">
-        <v>333900</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>MG28914</t>
+          <t>MG30041</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
+          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -24742,32 +24737,37 @@
         <v>24</v>
       </c>
       <c r="N539" t="n">
-        <v>5563</v>
+        <v>9046.99</v>
       </c>
       <c r="O539" t="n">
-        <v>133512</v>
+        <v>217127.76</v>
       </c>
       <c r="P539" t="n">
-        <v>11900</v>
+        <v>22500</v>
       </c>
       <c r="Q539" t="n">
-        <v>285600</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>MG30041</t>
+          <t>MG30183</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>MG30183</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -24776,7 +24776,7 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
@@ -24785,40 +24785,35 @@
         <v>0</v>
       </c>
       <c r="M540" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="N540" t="n">
-        <v>9046.99</v>
+        <v>3982.6708</v>
       </c>
       <c r="O540" t="n">
-        <v>217127.76</v>
+        <v>370388.3844</v>
       </c>
       <c r="P540" t="n">
-        <v>22500</v>
+        <v>10900</v>
       </c>
       <c r="Q540" t="n">
-        <v>540000</v>
+        <v>1013700</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>MG30183</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>MG30183</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24827,7 +24822,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>93</v>
+        <v>399</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -24836,35 +24831,40 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>93</v>
+        <v>399</v>
       </c>
       <c r="N541" t="n">
-        <v>3982.6708</v>
+        <v>571.87</v>
       </c>
       <c r="O541" t="n">
-        <v>370388.3844</v>
+        <v>228176.13</v>
       </c>
       <c r="P541" t="n">
-        <v>10900</v>
+        <v>2500</v>
       </c>
       <c r="Q541" t="n">
-        <v>1013700</v>
+        <v>997500</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40269</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -24873,7 +24873,7 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>399</v>
+        <v>3</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
@@ -24882,35 +24882,35 @@
         <v>0</v>
       </c>
       <c r="M542" t="n">
-        <v>399</v>
+        <v>3</v>
       </c>
       <c r="N542" t="n">
-        <v>571.87</v>
+        <v>2432.1360526316</v>
       </c>
       <c r="O542" t="n">
-        <v>228176.13</v>
+        <v>7296.408157894799</v>
       </c>
       <c r="P542" t="n">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="Q542" t="n">
-        <v>997500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>MG40269</t>
+          <t>MG40324</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MG40269</t>
+          <t>MG40324</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>JUEGO DE PESCA MG40324</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -24933,40 +24933,35 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N543" t="n">
-        <v>2432.1358227848</v>
+        <v>2005.78</v>
       </c>
       <c r="O543" t="n">
-        <v>7296.4074683544</v>
+        <v>2005.78</v>
       </c>
       <c r="P543" t="n">
-        <v>4500</v>
+        <v>9500</v>
       </c>
       <c r="Q543" t="n">
-        <v>13500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>MG40324</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>MG40324</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>JUEGO DE PESCA MG40324</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -24975,7 +24970,7 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -24984,35 +24979,40 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="N544" t="n">
-        <v>2005.78</v>
+        <v>227.41615210843</v>
       </c>
       <c r="O544" t="n">
-        <v>2005.78</v>
+        <v>61629.77722138453</v>
       </c>
       <c r="P544" t="n">
-        <v>9500</v>
+        <v>1200</v>
       </c>
       <c r="Q544" t="n">
-        <v>9500</v>
+        <v>325200</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40642</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>MG40642</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>MORRAL TOCADOR PORTABLE MG40642</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -25021,7 +25021,7 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -25030,35 +25030,35 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="N545" t="n">
-        <v>227.41614285714</v>
+        <v>19081.85</v>
       </c>
       <c r="O545" t="n">
-        <v>61629.77471428494</v>
+        <v>286227.75</v>
       </c>
       <c r="P545" t="n">
-        <v>1200</v>
+        <v>36900</v>
       </c>
       <c r="Q545" t="n">
-        <v>325200</v>
+        <v>553500</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>MG40642</t>
+          <t>MG40888</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MG40642</t>
+          <t>MG40888</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>MORRAL TOCADOR PORTABLE MG40642</t>
+          <t>SET DE RESCATE EN BOLSA MG40888</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -25072,7 +25072,7 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -25081,40 +25081,35 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N546" t="n">
-        <v>19081.85</v>
+        <v>7540.09</v>
       </c>
       <c r="O546" t="n">
-        <v>286227.75</v>
+        <v>37700.45</v>
       </c>
       <c r="P546" t="n">
-        <v>36900</v>
+        <v>18500</v>
       </c>
       <c r="Q546" t="n">
-        <v>553500</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>MG40888</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>MG40888</t>
+          <t>MG41171</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>SET DE RESCATE EN BOLSA MG40888</t>
+          <t>LANZA AGUA COLORES GDE MG41171</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -25123,7 +25118,7 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
@@ -25132,44 +25127,34 @@
         <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="N547" t="n">
-        <v>7540.09</v>
+        <v>25110.1</v>
       </c>
       <c r="O547" t="n">
-        <v>37700.45</v>
+        <v>778413.1</v>
       </c>
       <c r="P547" t="n">
-        <v>18500</v>
+        <v>27900</v>
       </c>
       <c r="Q547" t="n">
-        <v>92500</v>
+        <v>864900</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>MG41171</t>
+          <t>MR044</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>LANZA AGUA COLORES GDE MG41171</t>
-        </is>
-      </c>
-      <c r="E548" t="inlineStr">
-        <is>
-          <t>LANZADORES</t>
-        </is>
-      </c>
-      <c r="I548" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
         </is>
       </c>
       <c r="J548" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -25178,34 +25163,44 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="N548" t="n">
-        <v>25110.1</v>
+        <v>20720</v>
       </c>
       <c r="O548" t="n">
-        <v>778413.1</v>
+        <v>124320</v>
       </c>
       <c r="P548" t="n">
-        <v>27900</v>
+        <v>25900</v>
       </c>
       <c r="Q548" t="n">
-        <v>864900</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>MR044</t>
+          <t>MR045</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
+          <t>MORRAL ANIMALES STD 0230-02-002</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J549" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
@@ -25214,44 +25209,34 @@
         <v>0</v>
       </c>
       <c r="M549" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N549" t="n">
-        <v>20720</v>
+        <v>22080.08</v>
       </c>
       <c r="O549" t="n">
-        <v>124320</v>
+        <v>287041.04</v>
       </c>
       <c r="P549" t="n">
-        <v>25900</v>
+        <v>29900</v>
       </c>
       <c r="Q549" t="n">
-        <v>155400</v>
+        <v>388700</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>MR045</t>
+          <t>MR081</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>MORRAL ANIMALES STD 0230-02-002</t>
-        </is>
-      </c>
-      <c r="E550" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I550" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>MORRAL GATICO STD MR081</t>
         </is>
       </c>
       <c r="J550" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
@@ -25260,34 +25245,44 @@
         <v>0</v>
       </c>
       <c r="M550" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N550" t="n">
-        <v>22080.08</v>
+        <v>22865</v>
       </c>
       <c r="O550" t="n">
-        <v>287041.04</v>
+        <v>91460</v>
       </c>
       <c r="P550" t="n">
-        <v>29900</v>
+        <v>26900</v>
       </c>
       <c r="Q550" t="n">
-        <v>388700</v>
+        <v>107600</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>MR081</t>
+          <t>PT14019</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>MORRAL GATICO STD MR081</t>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>DIDACTICOS</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J551" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -25296,44 +25291,34 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="N551" t="n">
-        <v>22865</v>
+        <v>1950.7</v>
       </c>
       <c r="O551" t="n">
-        <v>91460</v>
+        <v>64373.1</v>
       </c>
       <c r="P551" t="n">
-        <v>26900</v>
+        <v>7500</v>
       </c>
       <c r="Q551" t="n">
-        <v>107600</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>SLBT04</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
-        </is>
-      </c>
-      <c r="E552" t="inlineStr">
-        <is>
-          <t>DIDACTICOS</t>
-        </is>
-      </c>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>BOLSA DE REGALO  SLT2023</t>
         </is>
       </c>
       <c r="J552" t="n">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25342,34 +25327,44 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="N552" t="n">
-        <v>1950.7</v>
+        <v>480</v>
       </c>
       <c r="O552" t="n">
-        <v>64373.1</v>
+        <v>70080</v>
       </c>
       <c r="P552" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q552" t="n">
-        <v>247500</v>
+        <v>87600</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>SLBT04</t>
+          <t>SLT014</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>BOLSA DE REGALO  SLT2023</t>
+          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J553" t="n">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="K553" t="n">
         <v>0</v>
@@ -25378,30 +25373,30 @@
         <v>0</v>
       </c>
       <c r="M553" t="n">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="N553" t="n">
-        <v>480</v>
+        <v>12000</v>
       </c>
       <c r="O553" t="n">
-        <v>70080</v>
+        <v>864000</v>
       </c>
       <c r="P553" t="n">
-        <v>600</v>
+        <v>15000</v>
       </c>
       <c r="Q553" t="n">
-        <v>87600</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>SLT014</t>
+          <t>SLT035</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
+          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -25415,7 +25410,7 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
@@ -25424,30 +25419,30 @@
         <v>0</v>
       </c>
       <c r="M554" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N554" t="n">
-        <v>12000</v>
+        <v>6917.54</v>
       </c>
       <c r="O554" t="n">
-        <v>864000</v>
+        <v>380464.7</v>
       </c>
       <c r="P554" t="n">
-        <v>15000</v>
+        <v>11500</v>
       </c>
       <c r="Q554" t="n">
-        <v>1080000</v>
+        <v>632500</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>SLT035</t>
+          <t>SLT05</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
+          <t>ESPADA DOBLE SLT2074</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -25461,7 +25456,7 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -25470,35 +25465,35 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="N555" t="n">
-        <v>6917.54</v>
+        <v>4720</v>
       </c>
       <c r="O555" t="n">
-        <v>380464.7</v>
+        <v>1123360</v>
       </c>
       <c r="P555" t="n">
-        <v>11500</v>
+        <v>5900</v>
       </c>
       <c r="Q555" t="n">
-        <v>632500</v>
+        <v>1404200</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>SLT05</t>
+          <t>SLT2640</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>ESPADA DOBLE SLT2074</t>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -25507,7 +25502,7 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -25516,30 +25511,30 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="N556" t="n">
-        <v>4720</v>
+        <v>1059.1855263158</v>
       </c>
       <c r="O556" t="n">
-        <v>1123360</v>
+        <v>22242.8960526318</v>
       </c>
       <c r="P556" t="n">
-        <v>5900</v>
+        <v>9500</v>
       </c>
       <c r="Q556" t="n">
-        <v>1404200</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>SLT2640</t>
+          <t>SLT2642</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
+          <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -25553,7 +25548,7 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -25562,64 +25557,18 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="N557" t="n">
-        <v>1059.1855263158</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O557" t="n">
-        <v>22242.8960526318</v>
+        <v>18074.13602459019</v>
       </c>
       <c r="P557" t="n">
-        <v>9500</v>
+        <v>14500</v>
       </c>
       <c r="Q557" t="n">
-        <v>199500</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>SLT2642</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>BALON BASQUEBOL # 7 ST2642</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J558" t="n">
-        <v>53</v>
-      </c>
-      <c r="K558" t="n">
-        <v>0</v>
-      </c>
-      <c r="L558" t="n">
-        <v>0</v>
-      </c>
-      <c r="M558" t="n">
-        <v>53</v>
-      </c>
-      <c r="N558" t="n">
-        <v>341.02143442623</v>
-      </c>
-      <c r="O558" t="n">
-        <v>18074.13602459019</v>
-      </c>
-      <c r="P558" t="n">
-        <v>14500</v>
-      </c>
-      <c r="Q558" t="n">
         <v>768500</v>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -947,22 +947,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M14" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>1854.241047619</v>
+        <v>1854.2411004785</v>
       </c>
       <c r="O14" t="n">
-        <v>107545.980761902</v>
+        <v>3708.482200957</v>
       </c>
       <c r="P14" t="n">
         <v>3200</v>
       </c>
       <c r="Q14" t="n">
-        <v>185600</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="15">
@@ -5601,10 +5601,10 @@
         <v>282</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.462959583</v>
+        <v>12422.46296087</v>
       </c>
       <c r="O122" t="n">
-        <v>3503134.554602406</v>
+        <v>3503134.55496534</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-22</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>572</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464051196</v>
+        <v>3376.7464001115</v>
       </c>
       <c r="O7" t="n">
-        <v>1931498.943728411</v>
+        <v>1931498.940863778</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8551798561</v>
+        <v>6272.855198556</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.581438845</v>
+        <v>1794036.586787016</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -2074,10 +2074,10 @@
         <v>34</v>
       </c>
       <c r="N42" t="n">
-        <v>61666.874364162</v>
+        <v>61666.874376812</v>
       </c>
       <c r="O42" t="n">
-        <v>2096673.728381508</v>
+        <v>2096673.728811608</v>
       </c>
       <c r="P42" t="n">
         <v>98900</v>
@@ -2927,10 +2927,10 @@
         <v>434</v>
       </c>
       <c r="N62" t="n">
-        <v>4937.310172549</v>
+        <v>4937.3101733649</v>
       </c>
       <c r="O62" t="n">
-        <v>2142792.614886266</v>
+        <v>2142792.615240367</v>
       </c>
       <c r="P62" t="n">
         <v>7500</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0685808709</v>
+        <v>1098.0688500785</v>
       </c>
       <c r="O70" t="n">
-        <v>129572.0925427662</v>
+        <v>129572.124309263</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3458,19 +3458,19 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="N74" t="n">
         <v>18291</v>
       </c>
       <c r="O74" t="n">
-        <v>310947</v>
+        <v>182910</v>
       </c>
       <c r="P74" t="n">
         <v>22900</v>
       </c>
       <c r="Q74" t="n">
-        <v>389300</v>
+        <v>229000</v>
       </c>
     </row>
     <row r="75">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3504,19 +3504,19 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N75" t="n">
         <v>13593.35</v>
       </c>
       <c r="O75" t="n">
-        <v>2664296.6</v>
+        <v>2637109.9</v>
       </c>
       <c r="P75" t="n">
         <v>25500</v>
       </c>
       <c r="Q75" t="n">
-        <v>4998000</v>
+        <v>4947000</v>
       </c>
     </row>
     <row r="76">
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4065,19 +4065,19 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="N88" t="n">
         <v>10600</v>
       </c>
       <c r="O88" t="n">
-        <v>9222000</v>
+        <v>9010000</v>
       </c>
       <c r="P88" t="n">
         <v>17200</v>
       </c>
       <c r="Q88" t="n">
-        <v>14964000</v>
+        <v>14620000</v>
       </c>
     </row>
     <row r="89">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4206,19 +4206,19 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="N91" t="n">
         <v>3154</v>
       </c>
       <c r="O91" t="n">
-        <v>624492</v>
+        <v>529872</v>
       </c>
       <c r="P91" t="n">
         <v>5500</v>
       </c>
       <c r="Q91" t="n">
-        <v>1089000</v>
+        <v>924000</v>
       </c>
     </row>
     <row r="92">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4882,19 +4882,19 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300534402</v>
+        <v>4890.9300535117</v>
       </c>
       <c r="O106" t="n">
-        <v>1809644.119772874</v>
+        <v>1790080.399585282</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
       </c>
       <c r="Q106" t="n">
-        <v>3034000</v>
+        <v>3001200</v>
       </c>
     </row>
     <row r="107">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -5066,19 +5066,19 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="N110" t="n">
         <v>5667.94</v>
       </c>
       <c r="O110" t="n">
-        <v>3174046.4</v>
+        <v>3162710.52</v>
       </c>
       <c r="P110" t="n">
         <v>9500</v>
       </c>
       <c r="Q110" t="n">
-        <v>5320000</v>
+        <v>5301000</v>
       </c>
     </row>
     <row r="111">
@@ -5333,10 +5333,10 @@
         <v>84</v>
       </c>
       <c r="N116" t="n">
-        <v>3240.8500533333</v>
+        <v>3240.8500542005</v>
       </c>
       <c r="O116" t="n">
-        <v>272231.4044799972</v>
+        <v>272231.404552842</v>
       </c>
       <c r="P116" t="n">
         <v>5200</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5598,19 +5598,19 @@
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.46296087</v>
+        <v>12422.462986842</v>
       </c>
       <c r="O122" t="n">
-        <v>3503134.55496534</v>
+        <v>3254685.302552604</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
       </c>
       <c r="Q122" t="n">
-        <v>5611800</v>
+        <v>5213800</v>
       </c>
     </row>
     <row r="123">
@@ -5732,10 +5732,10 @@
         <v>2406</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2762270961</v>
+        <v>3472.2762824732</v>
       </c>
       <c r="O125" t="n">
-        <v>8354296.602393216</v>
+        <v>8354296.735630519</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600142959</v>
+        <v>3041.6600148258</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.667162246</v>
+        <v>1523871.667427726</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9246283479</v>
+        <v>1630.9246804626</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.6040144489</v>
+        <v>311506.6139683566</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1947087933</v>
+        <v>1550.1947406745</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.0095165588</v>
+        <v>55807.010664282</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -8797,10 +8797,10 @@
         <v>348</v>
       </c>
       <c r="N194" t="n">
-        <v>2029.8741689828</v>
+        <v>2029.8741829336</v>
       </c>
       <c r="O194" t="n">
-        <v>706396.2108060144</v>
+        <v>706396.2156608928</v>
       </c>
       <c r="P194" t="n">
         <v>3600</v>
@@ -8838,10 +8838,10 @@
         <v>148</v>
       </c>
       <c r="N195" t="n">
-        <v>22485.695448799</v>
+        <v>22485.695419847</v>
       </c>
       <c r="O195" t="n">
-        <v>3327882.926422252</v>
+        <v>3327882.922137356</v>
       </c>
       <c r="P195" t="n">
         <v>36500</v>
@@ -9263,10 +9263,10 @@
         <v>609</v>
       </c>
       <c r="N205" t="n">
-        <v>998.76126436782</v>
+        <v>998.76126783754</v>
       </c>
       <c r="O205" t="n">
-        <v>608245.6100000024</v>
+        <v>608245.6121130618</v>
       </c>
       <c r="P205" t="n">
         <v>1600</v>
@@ -9297,7 +9297,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -9306,19 +9306,19 @@
         <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="N206" t="n">
         <v>6207.9882238578</v>
       </c>
       <c r="O206" t="n">
-        <v>7449585.868629361</v>
+        <v>7325426.104152204</v>
       </c>
       <c r="P206" t="n">
         <v>9900</v>
       </c>
       <c r="Q206" t="n">
-        <v>11880000</v>
+        <v>11682000</v>
       </c>
     </row>
     <row r="207">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9821,19 +9821,19 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N218" t="n">
-        <v>27123.764828283</v>
+        <v>27123.764699793</v>
       </c>
       <c r="O218" t="n">
-        <v>867960.474505056</v>
+        <v>542475.29399586</v>
       </c>
       <c r="P218" t="n">
         <v>44500</v>
       </c>
       <c r="Q218" t="n">
-        <v>1424000</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="219">
@@ -10249,10 +10249,10 @@
         <v>180</v>
       </c>
       <c r="N228" t="n">
-        <v>7969.9501710731</v>
+        <v>7969.9501716069</v>
       </c>
       <c r="O228" t="n">
-        <v>1434591.030793158</v>
+        <v>1434591.030889242</v>
       </c>
       <c r="P228" t="n">
         <v>12900</v>
@@ -10521,10 +10521,10 @@
         <v>154</v>
       </c>
       <c r="N234" t="n">
-        <v>548.1470665322601</v>
+        <v>548.14706357215</v>
       </c>
       <c r="O234" t="n">
-        <v>84414.64824596806</v>
+        <v>84414.64779011111</v>
       </c>
       <c r="P234" t="n">
         <v>2000</v>
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11385,19 +11385,19 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N253" t="n">
         <v>15824</v>
       </c>
       <c r="O253" t="n">
-        <v>284832</v>
+        <v>253184</v>
       </c>
       <c r="P253" t="n">
         <v>26900</v>
       </c>
       <c r="Q253" t="n">
-        <v>484200</v>
+        <v>430400</v>
       </c>
     </row>
     <row r="254">
@@ -11608,10 +11608,10 @@
         <v>952</v>
       </c>
       <c r="N258" t="n">
-        <v>1778.4728562081</v>
+        <v>1778.4728585462</v>
       </c>
       <c r="O258" t="n">
-        <v>1693106.159110111</v>
+        <v>1693106.161335982</v>
       </c>
       <c r="P258" t="n">
         <v>4900</v>
@@ -14063,10 +14063,10 @@
         <v>504</v>
       </c>
       <c r="N311" t="n">
-        <v>2328.1186586141</v>
+        <v>2328.118653478</v>
       </c>
       <c r="O311" t="n">
-        <v>1173371.803941506</v>
+        <v>1173371.801352912</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
@@ -14477,10 +14477,10 @@
         <v>100</v>
       </c>
       <c r="N320" t="n">
-        <v>4907.822690678</v>
+        <v>4907.8226963907</v>
       </c>
       <c r="O320" t="n">
-        <v>490782.2690678</v>
+        <v>490782.26963907</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14566,19 +14566,19 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N322" t="n">
         <v>4240</v>
       </c>
       <c r="O322" t="n">
-        <v>517280</v>
+        <v>508800</v>
       </c>
       <c r="P322" t="n">
         <v>7300</v>
       </c>
       <c r="Q322" t="n">
-        <v>890600</v>
+        <v>876000</v>
       </c>
     </row>
     <row r="323">
@@ -14707,10 +14707,10 @@
         <v>84</v>
       </c>
       <c r="N325" t="n">
-        <v>3903.7395348837</v>
+        <v>3903.7398185118</v>
       </c>
       <c r="O325" t="n">
-        <v>327914.1209302308</v>
+        <v>327914.1447549912</v>
       </c>
       <c r="P325" t="n">
         <v>7500</v>
@@ -14741,7 +14741,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -14750,19 +14750,19 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N326" t="n">
         <v>33000</v>
       </c>
       <c r="O326" t="n">
-        <v>231000</v>
+        <v>99000</v>
       </c>
       <c r="P326" t="n">
         <v>52900</v>
       </c>
       <c r="Q326" t="n">
-        <v>370300</v>
+        <v>158700</v>
       </c>
     </row>
     <row r="327">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="J353" t="n">
-        <v>1724</v>
+        <v>1702</v>
       </c>
       <c r="K353" t="n">
         <v>0</v>
@@ -15987,19 +15987,19 @@
         <v>0</v>
       </c>
       <c r="M353" t="n">
-        <v>1724</v>
+        <v>1702</v>
       </c>
       <c r="N353" t="n">
         <v>1326</v>
       </c>
       <c r="O353" t="n">
-        <v>2286024</v>
+        <v>2256852</v>
       </c>
       <c r="P353" t="n">
         <v>2500</v>
       </c>
       <c r="Q353" t="n">
-        <v>4310000</v>
+        <v>4255000</v>
       </c>
     </row>
     <row r="354">
@@ -16174,10 +16174,10 @@
         <v>839</v>
       </c>
       <c r="N357" t="n">
-        <v>1516.0387367881</v>
+        <v>1516.0387356204</v>
       </c>
       <c r="O357" t="n">
-        <v>1271956.500165216</v>
+        <v>1271956.499185516</v>
       </c>
       <c r="P357" t="n">
         <v>2300</v>
@@ -16581,10 +16581,10 @@
         <v>2063</v>
       </c>
       <c r="N366" t="n">
-        <v>692.15242929914</v>
+        <v>692.15244995571</v>
       </c>
       <c r="O366" t="n">
-        <v>1427910.461644126</v>
+        <v>1427910.50425863</v>
       </c>
       <c r="P366" t="n">
         <v>1200</v>
@@ -17779,10 +17779,10 @@
         <v>158</v>
       </c>
       <c r="N391" t="n">
-        <v>1690.8700094251</v>
+        <v>1690.8700094518</v>
       </c>
       <c r="O391" t="n">
-        <v>267157.4614891658</v>
+        <v>267157.4614933844</v>
       </c>
       <c r="P391" t="n">
         <v>3000</v>
@@ -18063,10 +18063,10 @@
         <v>50</v>
       </c>
       <c r="N397" t="n">
-        <v>3907.5003636364</v>
+        <v>3907.5003809524</v>
       </c>
       <c r="O397" t="n">
-        <v>195375.01818182</v>
+        <v>195375.01904762</v>
       </c>
       <c r="P397" t="n">
         <v>3900</v>
@@ -18387,10 +18387,10 @@
         <v>45</v>
       </c>
       <c r="N404" t="n">
-        <v>4032.3967885117</v>
+        <v>4032.3967801047</v>
       </c>
       <c r="O404" t="n">
-        <v>181457.8554830265</v>
+        <v>181457.8551047115</v>
       </c>
       <c r="P404" t="n">
         <v>4200</v>
@@ -18808,10 +18808,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8366199849</v>
+        <v>3110.8363143631</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.6732399698</v>
+        <v>6221.6726287262</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18998,10 +18998,10 @@
         <v>127</v>
       </c>
       <c r="N417" t="n">
-        <v>3182.2511320755</v>
+        <v>3182.2511342155</v>
       </c>
       <c r="O417" t="n">
-        <v>404145.8937735885</v>
+        <v>404145.8940453685</v>
       </c>
       <c r="P417" t="n">
         <v>6900</v>
@@ -20309,7 +20309,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -20318,19 +20318,19 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="N445" t="n">
         <v>3100.87</v>
       </c>
       <c r="O445" t="n">
-        <v>83723.48999999999</v>
+        <v>21706.09</v>
       </c>
       <c r="P445" t="n">
         <v>9900</v>
       </c>
       <c r="Q445" t="n">
-        <v>267300</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="446">
@@ -22962,10 +22962,10 @@
         <v>60</v>
       </c>
       <c r="N500" t="n">
-        <v>1008.8125188917</v>
+        <v>1008.8113941019</v>
       </c>
       <c r="O500" t="n">
-        <v>60528.751133502</v>
+        <v>60528.683646114</v>
       </c>
       <c r="P500" t="n">
         <v>1500</v>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24642,19 +24642,19 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N537" t="n">
         <v>15239.8</v>
       </c>
       <c r="O537" t="n">
-        <v>243836.8</v>
+        <v>182877.6</v>
       </c>
       <c r="P537" t="n">
         <v>15900</v>
       </c>
       <c r="Q537" t="n">
-        <v>254400</v>
+        <v>190800</v>
       </c>
     </row>
     <row r="538">

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.855198556</v>
+        <v>6272.8552079566</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.586787016</v>
+        <v>1794036.589475587</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1310,10 +1310,10 @@
         <v>48</v>
       </c>
       <c r="N23" t="n">
-        <v>3716.3301967213</v>
+        <v>3716.3301970443</v>
       </c>
       <c r="O23" t="n">
-        <v>178383.8494426224</v>
+        <v>178383.8494581264</v>
       </c>
       <c r="P23" t="n">
         <v>9500</v>
@@ -5601,10 +5601,10 @@
         <v>262</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.462986842</v>
+        <v>12422.462990777</v>
       </c>
       <c r="O122" t="n">
-        <v>3254685.302552604</v>
+        <v>3254685.303583574</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600148258</v>
+        <v>3041.6600148478</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.667427726</v>
+        <v>1523871.667438748</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9246804626</v>
+        <v>1630.9246976176</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.6139683566</v>
+        <v>311506.6172449616</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -16174,10 +16174,10 @@
         <v>839</v>
       </c>
       <c r="N357" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O357" t="n">
-        <v>1271956.499185516</v>
+        <v>1271956.495248424</v>
       </c>
       <c r="P357" t="n">
         <v>2300</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8552079566</v>
+        <v>6272.8552268603</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.589475587</v>
+        <v>1794036.594882046</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -2536,10 +2536,10 @@
         <v>178</v>
       </c>
       <c r="N53" t="n">
-        <v>3340.6800842105</v>
+        <v>3340.6800849257</v>
       </c>
       <c r="O53" t="n">
-        <v>594641.054989469</v>
+        <v>594641.0551167746</v>
       </c>
       <c r="P53" t="n">
         <v>7100</v>
@@ -2840,10 +2840,10 @@
         <v>148</v>
       </c>
       <c r="N60" t="n">
-        <v>1950.2137350835</v>
+        <v>1950.2137275986</v>
       </c>
       <c r="O60" t="n">
-        <v>288631.632792358</v>
+        <v>288631.6316845928</v>
       </c>
       <c r="P60" t="n">
         <v>2900</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0688500785</v>
+        <v>1098.0691359493</v>
       </c>
       <c r="O70" t="n">
-        <v>129572.124309263</v>
+        <v>129572.1580420174</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4706,10 +4706,10 @@
         <v>179</v>
       </c>
       <c r="N102" t="n">
-        <v>3795.7100076292</v>
+        <v>3795.7100076321</v>
       </c>
       <c r="O102" t="n">
-        <v>679432.0913656268</v>
+        <v>679432.0913661459</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -4885,10 +4885,10 @@
         <v>366</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300535117</v>
+        <v>4890.9300537634</v>
       </c>
       <c r="O106" t="n">
-        <v>1790080.399585282</v>
+        <v>1790080.399677404</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4928,19 +4928,19 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="N107" t="n">
         <v>3472</v>
       </c>
       <c r="O107" t="n">
-        <v>711760</v>
+        <v>538160</v>
       </c>
       <c r="P107" t="n">
         <v>4800</v>
       </c>
       <c r="Q107" t="n">
-        <v>984000</v>
+        <v>744000</v>
       </c>
     </row>
     <row r="108">
@@ -5333,10 +5333,10 @@
         <v>84</v>
       </c>
       <c r="N116" t="n">
-        <v>3240.8500542005</v>
+        <v>3240.8500537634</v>
       </c>
       <c r="O116" t="n">
-        <v>272231.404552842</v>
+        <v>272231.4045161256</v>
       </c>
       <c r="P116" t="n">
         <v>5200</v>
@@ -5418,10 +5418,10 @@
         <v>135</v>
       </c>
       <c r="N118" t="n">
-        <v>5191.4800284495</v>
+        <v>5191.4800286123</v>
       </c>
       <c r="O118" t="n">
-        <v>700849.8038406826</v>
+        <v>700849.8038626605</v>
       </c>
       <c r="P118" t="n">
         <v>9100</v>
@@ -5601,10 +5601,10 @@
         <v>262</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.462990777</v>
+        <v>12422.462992091</v>
       </c>
       <c r="O122" t="n">
-        <v>3254685.303583574</v>
+        <v>3254685.303927842</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5732,10 +5732,10 @@
         <v>2406</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2762824732</v>
+        <v>3472.2762877567</v>
       </c>
       <c r="O125" t="n">
-        <v>8354296.735630519</v>
+        <v>8354296.74834262</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5912,10 +5912,10 @@
         <v>1101</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1712631292</v>
+        <v>4371.1712633877</v>
       </c>
       <c r="O129" t="n">
-        <v>4812659.560705249</v>
+        <v>4812659.560989858</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9246976176</v>
+        <v>1630.9246990529</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.6172449616</v>
+        <v>311506.6175191039</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1947406745</v>
+        <v>1550.1947552537</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.010664282</v>
+        <v>55807.0111891332</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -8838,10 +8838,10 @@
         <v>148</v>
       </c>
       <c r="N195" t="n">
-        <v>22485.695419847</v>
+        <v>22485.695402299</v>
       </c>
       <c r="O195" t="n">
-        <v>3327882.922137356</v>
+        <v>3327882.919540252</v>
       </c>
       <c r="P195" t="n">
         <v>36500</v>
@@ -9309,10 +9309,10 @@
         <v>1180</v>
       </c>
       <c r="N206" t="n">
-        <v>6207.9882238578</v>
+        <v>6207.9882231175</v>
       </c>
       <c r="O206" t="n">
-        <v>7325426.104152204</v>
+        <v>7325426.10327865</v>
       </c>
       <c r="P206" t="n">
         <v>9900</v>
@@ -9696,10 +9696,10 @@
         <v>707</v>
       </c>
       <c r="N215" t="n">
-        <v>4814.2679256837</v>
+        <v>4814.2679250376</v>
       </c>
       <c r="O215" t="n">
-        <v>3403687.423458376</v>
+        <v>3403687.423001584</v>
       </c>
       <c r="P215" t="n">
         <v>9900</v>
@@ -11608,10 +11608,10 @@
         <v>952</v>
       </c>
       <c r="N258" t="n">
-        <v>1778.4728585462</v>
+        <v>1778.4728622951</v>
       </c>
       <c r="O258" t="n">
-        <v>1693106.161335982</v>
+        <v>1693106.164904935</v>
       </c>
       <c r="P258" t="n">
         <v>4900</v>
@@ -13864,7 +13864,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>263</v>
+        <v>143</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13873,19 +13873,19 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>263</v>
+        <v>143</v>
       </c>
       <c r="N307" t="n">
-        <v>2252.2983673469</v>
+        <v>2252.3005544554</v>
       </c>
       <c r="O307" t="n">
-        <v>592354.4706122347</v>
+        <v>322078.9792871222</v>
       </c>
       <c r="P307" t="n">
         <v>3900</v>
       </c>
       <c r="Q307" t="n">
-        <v>1025700</v>
+        <v>557700</v>
       </c>
     </row>
     <row r="308">
@@ -14063,10 +14063,10 @@
         <v>504</v>
       </c>
       <c r="N311" t="n">
-        <v>2328.118653478</v>
+        <v>2328.1186430868</v>
       </c>
       <c r="O311" t="n">
-        <v>1173371.801352912</v>
+        <v>1173371.796115747</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
@@ -14477,10 +14477,10 @@
         <v>100</v>
       </c>
       <c r="N320" t="n">
-        <v>4907.8226963907</v>
+        <v>4907.8227078891</v>
       </c>
       <c r="O320" t="n">
-        <v>490782.26963907</v>
+        <v>490782.27078891</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -16024,7 +16024,7 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
@@ -16033,19 +16033,19 @@
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N354" t="n">
         <v>5640</v>
       </c>
       <c r="O354" t="n">
-        <v>78960</v>
+        <v>50760</v>
       </c>
       <c r="P354" t="n">
         <v>9900</v>
       </c>
       <c r="Q354" t="n">
-        <v>138600</v>
+        <v>89100</v>
       </c>
     </row>
     <row r="355">
@@ -16174,10 +16174,10 @@
         <v>839</v>
       </c>
       <c r="N357" t="n">
-        <v>1516.0387309278</v>
+        <v>1516.0387272539</v>
       </c>
       <c r="O357" t="n">
-        <v>1271956.495248424</v>
+        <v>1271956.492166022</v>
       </c>
       <c r="P357" t="n">
         <v>2300</v>
@@ -16581,10 +16581,10 @@
         <v>2063</v>
       </c>
       <c r="N366" t="n">
-        <v>692.15244995571</v>
+        <v>692.1524551748601</v>
       </c>
       <c r="O366" t="n">
-        <v>1427910.50425863</v>
+        <v>1427910.515025736</v>
       </c>
       <c r="P366" t="n">
         <v>1200</v>
@@ -17359,10 +17359,10 @@
         <v>780</v>
       </c>
       <c r="N382" t="n">
-        <v>1530.4499180664</v>
+        <v>1530.4499179655</v>
       </c>
       <c r="O382" t="n">
-        <v>1193750.936091792</v>
+        <v>1193750.93601309</v>
       </c>
       <c r="P382" t="n">
         <v>2600</v>
@@ -17534,7 +17534,7 @@
         </is>
       </c>
       <c r="J386" t="n">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="K386" t="n">
         <v>0</v>
@@ -17543,19 +17543,19 @@
         <v>0</v>
       </c>
       <c r="M386" t="n">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="N386" t="n">
         <v>1426.39</v>
       </c>
       <c r="O386" t="n">
-        <v>999899.39</v>
+        <v>991341.05</v>
       </c>
       <c r="P386" t="n">
         <v>2500</v>
       </c>
       <c r="Q386" t="n">
-        <v>1752500</v>
+        <v>1737500</v>
       </c>
     </row>
     <row r="387">
@@ -17779,10 +17779,10 @@
         <v>158</v>
       </c>
       <c r="N391" t="n">
-        <v>1690.8700094518</v>
+        <v>1690.8700095238</v>
       </c>
       <c r="O391" t="n">
-        <v>267157.4614933844</v>
+        <v>267157.4615047604</v>
       </c>
       <c r="P391" t="n">
         <v>3000</v>
@@ -18063,10 +18063,10 @@
         <v>50</v>
       </c>
       <c r="N397" t="n">
-        <v>3907.5003809524</v>
+        <v>3907.5003864734</v>
       </c>
       <c r="O397" t="n">
-        <v>195375.01904762</v>
+        <v>195375.01932367</v>
       </c>
       <c r="P397" t="n">
         <v>3900</v>
@@ -18808,10 +18808,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8363143631</v>
+        <v>3110.8359666534</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.6726287262</v>
+        <v>6221.6719333068</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -19182,10 +19182,10 @@
         <v>4</v>
       </c>
       <c r="N421" t="n">
-        <v>2501.3844041451</v>
+        <v>2501.3843455497</v>
       </c>
       <c r="O421" t="n">
-        <v>10005.5376165804</v>
+        <v>10005.5373821988</v>
       </c>
       <c r="P421" t="n">
         <v>4100</v>
@@ -22772,7 +22772,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -22781,19 +22781,19 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="N496" t="n">
         <v>1297.52</v>
       </c>
       <c r="O496" t="n">
-        <v>373685.76</v>
+        <v>308809.76</v>
       </c>
       <c r="P496" t="n">
         <v>1800</v>
       </c>
       <c r="Q496" t="n">
-        <v>518400</v>
+        <v>428400</v>
       </c>
     </row>
     <row r="497">
@@ -23035,7 +23035,7 @@
         </is>
       </c>
       <c r="J502" t="n">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="K502" t="n">
         <v>0</v>
@@ -23044,19 +23044,19 @@
         <v>0</v>
       </c>
       <c r="M502" t="n">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="N502" t="n">
         <v>3181.9</v>
       </c>
       <c r="O502" t="n">
-        <v>2360969.8</v>
+        <v>2329150.8</v>
       </c>
       <c r="P502" t="n">
         <v>5100</v>
       </c>
       <c r="Q502" t="n">
-        <v>3784200</v>
+        <v>3733200</v>
       </c>
     </row>
     <row r="503">
@@ -23265,10 +23265,10 @@
         <v>11</v>
       </c>
       <c r="N507" t="n">
-        <v>22951.704689564</v>
+        <v>22951.70468254</v>
       </c>
       <c r="O507" t="n">
-        <v>252468.751585204</v>
+        <v>252468.75150794</v>
       </c>
       <c r="P507" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0691359493</v>
+        <v>1098.0698699716</v>
       </c>
       <c r="O70" t="n">
-        <v>129572.1580420174</v>
+        <v>129572.2446566488</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4706,10 +4706,10 @@
         <v>179</v>
       </c>
       <c r="N102" t="n">
-        <v>3795.7100076321</v>
+        <v>3795.710007638</v>
       </c>
       <c r="O102" t="n">
-        <v>679432.0913661459</v>
+        <v>679432.091367202</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -4885,10 +4885,10 @@
         <v>366</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300537634</v>
+        <v>4890.9300539811</v>
       </c>
       <c r="O106" t="n">
-        <v>1790080.399677404</v>
+        <v>1790080.399757083</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
@@ -5732,10 +5732,10 @@
         <v>2406</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2762877567</v>
+        <v>3472.2762983503</v>
       </c>
       <c r="O125" t="n">
-        <v>8354296.74834262</v>
+        <v>8354296.773830822</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5912,10 +5912,10 @@
         <v>1101</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1712633877</v>
+        <v>4371.171263905</v>
       </c>
       <c r="O129" t="n">
-        <v>4812659.560989858</v>
+        <v>4812659.561559405</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9246990529</v>
+        <v>1630.9247048027</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.6175191039</v>
+        <v>311506.6186173157</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -9309,10 +9309,10 @@
         <v>1180</v>
       </c>
       <c r="N206" t="n">
-        <v>6207.9882231175</v>
+        <v>6213.167301168</v>
       </c>
       <c r="O206" t="n">
-        <v>7325426.10327865</v>
+        <v>7331537.415378241</v>
       </c>
       <c r="P206" t="n">
         <v>9900</v>
@@ -9737,10 +9737,10 @@
         <v>908</v>
       </c>
       <c r="N216" t="n">
-        <v>3591.13</v>
+        <v>3594.9639466192</v>
       </c>
       <c r="O216" t="n">
-        <v>3260746.04</v>
+        <v>3264227.263530234</v>
       </c>
       <c r="P216" t="n">
         <v>6300</v>
@@ -10521,10 +10521,10 @@
         <v>154</v>
       </c>
       <c r="N234" t="n">
-        <v>548.14706357215</v>
+        <v>548.14704568528</v>
       </c>
       <c r="O234" t="n">
-        <v>84414.64779011111</v>
+        <v>84414.64503553312</v>
       </c>
       <c r="P234" t="n">
         <v>2000</v>
@@ -13600,10 +13600,10 @@
         <v>348</v>
       </c>
       <c r="N301" t="n">
-        <v>8858.16</v>
+        <v>8873.1568848758</v>
       </c>
       <c r="O301" t="n">
-        <v>3082639.68</v>
+        <v>3087858.595936778</v>
       </c>
       <c r="P301" t="n">
         <v>15500</v>
@@ -14937,10 +14937,10 @@
         <v>438</v>
       </c>
       <c r="N330" t="n">
-        <v>6849.2</v>
+        <v>6862.329456869</v>
       </c>
       <c r="O330" t="n">
-        <v>2999949.6</v>
+        <v>3005700.302108622</v>
       </c>
       <c r="P330" t="n">
         <v>11500</v>
@@ -16174,10 +16174,10 @@
         <v>839</v>
       </c>
       <c r="N357" t="n">
-        <v>1516.0387272539</v>
+        <v>1516.0387269907</v>
       </c>
       <c r="O357" t="n">
-        <v>1271956.492166022</v>
+        <v>1271956.491945197</v>
       </c>
       <c r="P357" t="n">
         <v>2300</v>
@@ -18808,10 +18808,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8359666534</v>
+        <v>3110.8359331476</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.6719333068</v>
+        <v>6221.6718662952</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -20177,10 +20177,10 @@
         <v>23</v>
       </c>
       <c r="N442" t="n">
-        <v>2832.1953125</v>
+        <v>2832.1953968254</v>
       </c>
       <c r="O442" t="n">
-        <v>65140.4921875</v>
+        <v>65140.4941269842</v>
       </c>
       <c r="P442" t="n">
         <v>12900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1112,10 +1112,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>12357.960428571</v>
+        <v>12357.960431655</v>
       </c>
       <c r="O18" t="n">
-        <v>444886.575428556</v>
+        <v>444886.57553958</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -1388,10 +1388,10 @@
         <v>384</v>
       </c>
       <c r="N25" t="n">
-        <v>2785.6243902439</v>
+        <v>2681</v>
       </c>
       <c r="O25" t="n">
-        <v>1069679.765853658</v>
+        <v>1029504</v>
       </c>
       <c r="P25" t="n">
         <v>3500</v>
@@ -2295,10 +2295,10 @@
         <v>64</v>
       </c>
       <c r="N47" t="n">
-        <v>2584.1380683507</v>
+        <v>2572.67</v>
       </c>
       <c r="O47" t="n">
-        <v>165384.8363744448</v>
+        <v>164650.88</v>
       </c>
       <c r="P47" t="n">
         <v>4700</v>
@@ -2927,10 +2927,10 @@
         <v>434</v>
       </c>
       <c r="N62" t="n">
-        <v>4937.3101733649</v>
+        <v>4937.3101737757</v>
       </c>
       <c r="O62" t="n">
-        <v>2142792.615240367</v>
+        <v>2142792.615418653</v>
       </c>
       <c r="P62" t="n">
         <v>7500</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1108.8838530981</v>
+        <v>1098.0703134021</v>
       </c>
       <c r="O70" t="n">
-        <v>130848.2946655758</v>
+        <v>129572.2969814478</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4209,10 +4209,10 @@
         <v>168</v>
       </c>
       <c r="N91" t="n">
-        <v>3154</v>
+        <v>3359.6956521739</v>
       </c>
       <c r="O91" t="n">
-        <v>529872</v>
+        <v>564428.8695652152</v>
       </c>
       <c r="P91" t="n">
         <v>5500</v>
@@ -4394,10 +4394,10 @@
         <v>484</v>
       </c>
       <c r="N95" t="n">
-        <v>1482.2572445348</v>
+        <v>1480</v>
       </c>
       <c r="O95" t="n">
-        <v>717412.5063548433</v>
+        <v>716320</v>
       </c>
       <c r="P95" t="n">
         <v>2600</v>
@@ -4885,10 +4885,10 @@
         <v>366</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300540176</v>
+        <v>4890.9300540541</v>
       </c>
       <c r="O106" t="n">
-        <v>1790080.399770442</v>
+        <v>1790080.399783801</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
@@ -5333,10 +5333,10 @@
         <v>84</v>
       </c>
       <c r="N116" t="n">
-        <v>3354.2325655977</v>
+        <v>3240.850058309</v>
       </c>
       <c r="O116" t="n">
-        <v>281755.5355102068</v>
+        <v>272231.404897956</v>
       </c>
       <c r="P116" t="n">
         <v>5200</v>
@@ -5377,10 +5377,10 @@
         <v>2706</v>
       </c>
       <c r="N117" t="n">
-        <v>2093.3158067369</v>
+        <v>2090.85</v>
       </c>
       <c r="O117" t="n">
-        <v>5664512.573030051</v>
+        <v>5657840.1</v>
       </c>
       <c r="P117" t="n">
         <v>2900</v>
@@ -5732,10 +5732,10 @@
         <v>2406</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.276319645</v>
+        <v>3472.276322317</v>
       </c>
       <c r="O125" t="n">
-        <v>8354296.82506587</v>
+        <v>8354296.831494702</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -6629,10 +6629,10 @@
         <v>51</v>
       </c>
       <c r="N145" t="n">
-        <v>9677.770167910399</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O145" t="n">
-        <v>493566.2785634304</v>
+        <v>480129.81</v>
       </c>
       <c r="P145" t="n">
         <v>16900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9247235872</v>
+        <v>1630.9247279434</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.6222051552</v>
+        <v>311506.6230371894</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -9309,10 +9309,10 @@
         <v>1160</v>
       </c>
       <c r="N206" t="n">
-        <v>6207.988218663</v>
+        <v>6207.9882181666</v>
       </c>
       <c r="O206" t="n">
-        <v>7201266.33364908</v>
+        <v>7201266.333073256</v>
       </c>
       <c r="P206" t="n">
         <v>9900</v>
@@ -9696,10 +9696,10 @@
         <v>697</v>
       </c>
       <c r="N215" t="n">
-        <v>4814.2679247144</v>
+        <v>4814.2679243911</v>
       </c>
       <c r="O215" t="n">
-        <v>3355544.743525937</v>
+        <v>3355544.743300597</v>
       </c>
       <c r="P215" t="n">
         <v>9900</v>
@@ -10426,10 +10426,10 @@
         <v>1425</v>
       </c>
       <c r="N232" t="n">
-        <v>1200.9029345372</v>
+        <v>1200</v>
       </c>
       <c r="O232" t="n">
-        <v>1711286.68171551</v>
+        <v>1710000</v>
       </c>
       <c r="P232" t="n">
         <v>1500</v>
@@ -11838,10 +11838,10 @@
         <v>246</v>
       </c>
       <c r="N263" t="n">
-        <v>5188.8571428571</v>
+        <v>5148</v>
       </c>
       <c r="O263" t="n">
-        <v>1276458.857142847</v>
+        <v>1266408</v>
       </c>
       <c r="P263" t="n">
         <v>8600</v>
@@ -13324,10 +13324,10 @@
         <v>5</v>
       </c>
       <c r="N295" t="n">
-        <v>3957.6262600321</v>
+        <v>3938.66</v>
       </c>
       <c r="O295" t="n">
-        <v>19788.1313001605</v>
+        <v>19693.3</v>
       </c>
       <c r="P295" t="n">
         <v>4500</v>
@@ -14845,10 +14845,10 @@
         <v>120</v>
       </c>
       <c r="N328" t="n">
-        <v>2636.2357798165</v>
+        <v>2629</v>
       </c>
       <c r="O328" t="n">
-        <v>316348.29357798</v>
+        <v>315480</v>
       </c>
       <c r="P328" t="n">
         <v>4500</v>
@@ -15075,10 +15075,10 @@
         <v>224</v>
       </c>
       <c r="N333" t="n">
-        <v>6650.5777839955</v>
+        <v>6645</v>
       </c>
       <c r="O333" t="n">
-        <v>1489729.423614992</v>
+        <v>1488480</v>
       </c>
       <c r="P333" t="n">
         <v>10900</v>
@@ -15622,10 +15622,10 @@
         <v>48</v>
       </c>
       <c r="N345" t="n">
-        <v>18170.288401254</v>
+        <v>18001</v>
       </c>
       <c r="O345" t="n">
-        <v>872173.8432601921</v>
+        <v>864048</v>
       </c>
       <c r="P345" t="n">
         <v>28900</v>
@@ -16082,10 +16082,10 @@
         <v>839</v>
       </c>
       <c r="N355" t="n">
-        <v>1516.0387131507</v>
+        <v>1516.0387126124</v>
       </c>
       <c r="O355" t="n">
-        <v>1271956.480333437</v>
+        <v>1271956.479881804</v>
       </c>
       <c r="P355" t="n">
         <v>2300</v>
@@ -16398,22 +16398,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M362" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="N362" t="n">
         <v>2944</v>
       </c>
       <c r="O362" t="n">
-        <v>497536</v>
+        <v>450432</v>
       </c>
       <c r="P362" t="n">
         <v>4900</v>
       </c>
       <c r="Q362" t="n">
-        <v>828100</v>
+        <v>749700</v>
       </c>
     </row>
     <row r="363">
@@ -16489,10 +16489,10 @@
         <v>2063</v>
       </c>
       <c r="N364" t="n">
-        <v>692.15249234096</v>
+        <v>692.15249774246</v>
       </c>
       <c r="O364" t="n">
-        <v>1427910.5916994</v>
+        <v>1427910.602842695</v>
       </c>
       <c r="P364" t="n">
         <v>1200</v>
@@ -16538,10 +16538,10 @@
         <v>1</v>
       </c>
       <c r="N365" t="n">
-        <v>19051.333333333</v>
+        <v>18491</v>
       </c>
       <c r="O365" t="n">
-        <v>19051.333333333</v>
+        <v>18491</v>
       </c>
       <c r="P365" t="n">
         <v>13500</v>
@@ -16832,10 +16832,10 @@
         <v>64</v>
       </c>
       <c r="N371" t="n">
-        <v>5510.92</v>
+        <v>6178.9103030303</v>
       </c>
       <c r="O371" t="n">
-        <v>352698.88</v>
+        <v>395450.2593939392</v>
       </c>
       <c r="P371" t="n">
         <v>4900</v>
@@ -18251,10 +18251,10 @@
         <v>9</v>
       </c>
       <c r="N401" t="n">
-        <v>1333.9879518072</v>
+        <v>1326</v>
       </c>
       <c r="O401" t="n">
-        <v>12005.8915662648</v>
+        <v>11934</v>
       </c>
       <c r="P401" t="n">
         <v>2900</v>
@@ -19650,10 +19650,10 @@
         <v>381</v>
       </c>
       <c r="N431" t="n">
-        <v>1595.4982940252</v>
+        <v>1595.4982440945</v>
       </c>
       <c r="O431" t="n">
-        <v>607884.8500236012</v>
+        <v>607884.8310000045</v>
       </c>
       <c r="P431" t="n">
         <v>2500</v>
@@ -23929,22 +23929,22 @@
         <v>0</v>
       </c>
       <c r="L522" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M522" t="n">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="N522" t="n">
         <v>7480</v>
       </c>
       <c r="O522" t="n">
-        <v>2513280</v>
+        <v>2423520</v>
       </c>
       <c r="P522" t="n">
         <v>9500</v>
       </c>
       <c r="Q522" t="n">
-        <v>3192000</v>
+        <v>3078000</v>
       </c>
     </row>
     <row r="523">
@@ -25468,10 +25468,10 @@
         <v>53</v>
       </c>
       <c r="N555" t="n">
-        <v>345.26651452282</v>
+        <v>341.02145228216</v>
       </c>
       <c r="O555" t="n">
-        <v>18299.12526970946</v>
+        <v>18074.13697095448</v>
       </c>
       <c r="P555" t="n">
         <v>14500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -589,22 +589,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="N5" t="n">
         <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>6615000</v>
+        <v>6291000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
       </c>
       <c r="Q5" t="n">
-        <v>4900000</v>
+        <v>4660000</v>
       </c>
     </row>
     <row r="6">
@@ -628,22 +628,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N6" t="n">
         <v>27000</v>
       </c>
       <c r="O6" t="n">
-        <v>729000</v>
+        <v>702000</v>
       </c>
       <c r="P6" t="n">
         <v>30000</v>
       </c>
       <c r="Q6" t="n">
-        <v>810000</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="7">
@@ -5063,22 +5063,22 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M110" t="n">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="N110" t="n">
         <v>5667.94</v>
       </c>
       <c r="O110" t="n">
-        <v>3162710.52</v>
+        <v>3083359.36</v>
       </c>
       <c r="P110" t="n">
         <v>9500</v>
       </c>
       <c r="Q110" t="n">
-        <v>5301000</v>
+        <v>5168000</v>
       </c>
     </row>
     <row r="111">
@@ -5500,22 +5500,22 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M120" t="n">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="N120" t="n">
         <v>2665.4</v>
       </c>
       <c r="O120" t="n">
-        <v>1708521.4</v>
+        <v>1700525.2</v>
       </c>
       <c r="P120" t="n">
         <v>20900</v>
       </c>
       <c r="Q120" t="n">
-        <v>13396900</v>
+        <v>13334200</v>
       </c>
     </row>
     <row r="121">
@@ -5726,22 +5726,22 @@
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M125" t="n">
-        <v>2406</v>
+        <v>2388</v>
       </c>
       <c r="N125" t="n">
         <v>3472.2763500602</v>
       </c>
       <c r="O125" t="n">
-        <v>8354296.898244841</v>
+        <v>8291795.923943758</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
       </c>
       <c r="Q125" t="n">
-        <v>14195400</v>
+        <v>14089200</v>
       </c>
     </row>
     <row r="126">
@@ -9032,22 +9032,22 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M200" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N200" t="n">
         <v>14060.64</v>
       </c>
       <c r="O200" t="n">
-        <v>253091.52</v>
+        <v>140606.4</v>
       </c>
       <c r="P200" t="n">
         <v>22900</v>
       </c>
       <c r="Q200" t="n">
-        <v>412200</v>
+        <v>229000</v>
       </c>
     </row>
     <row r="201">
@@ -9252,22 +9252,22 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M205" t="n">
-        <v>1160</v>
+        <v>1140</v>
       </c>
       <c r="N205" t="n">
         <v>6207.9882021366</v>
       </c>
       <c r="O205" t="n">
-        <v>7201266.314478456</v>
+        <v>7077106.550435725</v>
       </c>
       <c r="P205" t="n">
         <v>9900</v>
       </c>
       <c r="Q205" t="n">
-        <v>11484000</v>
+        <v>11286000</v>
       </c>
     </row>
     <row r="206">
@@ -9680,22 +9680,22 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M215" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="N215" t="n">
         <v>3591.13</v>
       </c>
       <c r="O215" t="n">
-        <v>3260746.04</v>
+        <v>3242790.39</v>
       </c>
       <c r="P215" t="n">
         <v>6300</v>
       </c>
       <c r="Q215" t="n">
-        <v>5720400</v>
+        <v>5688900</v>
       </c>
     </row>
     <row r="216">
@@ -11295,22 +11295,22 @@
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M251" t="n">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="N251" t="n">
         <v>3646</v>
       </c>
       <c r="O251" t="n">
-        <v>648988</v>
+        <v>466688</v>
       </c>
       <c r="P251" t="n">
         <v>6900</v>
       </c>
       <c r="Q251" t="n">
-        <v>1228200</v>
+        <v>883200</v>
       </c>
     </row>
     <row r="252">
@@ -14200,22 +14200,22 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M314" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="N314" t="n">
         <v>13922</v>
       </c>
       <c r="O314" t="n">
-        <v>1322590</v>
+        <v>1225136</v>
       </c>
       <c r="P314" t="n">
         <v>22900</v>
       </c>
       <c r="Q314" t="n">
-        <v>2175500</v>
+        <v>2015200</v>
       </c>
     </row>
     <row r="315">
@@ -14292,22 +14292,22 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M316" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N316" t="n">
         <v>25076</v>
       </c>
       <c r="O316" t="n">
-        <v>300912</v>
+        <v>175532</v>
       </c>
       <c r="P316" t="n">
         <v>40900</v>
       </c>
       <c r="Q316" t="n">
-        <v>490800</v>
+        <v>286300</v>
       </c>
     </row>
     <row r="317">
@@ -14982,22 +14982,22 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M331" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="N331" t="n">
         <v>13098</v>
       </c>
       <c r="O331" t="n">
-        <v>1427682</v>
+        <v>1349094</v>
       </c>
       <c r="P331" t="n">
         <v>21200</v>
       </c>
       <c r="Q331" t="n">
-        <v>2310800</v>
+        <v>2183600</v>
       </c>
     </row>
     <row r="332">
@@ -15028,22 +15028,22 @@
         <v>0</v>
       </c>
       <c r="L332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M332" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N332" t="n">
         <v>27186</v>
       </c>
       <c r="O332" t="n">
-        <v>190302</v>
+        <v>163116</v>
       </c>
       <c r="P332" t="n">
         <v>43900</v>
       </c>
       <c r="Q332" t="n">
-        <v>307300</v>
+        <v>263400</v>
       </c>
     </row>
     <row r="333">
@@ -16448,22 +16448,22 @@
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M363" t="n">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="N363" t="n">
         <v>11690</v>
       </c>
       <c r="O363" t="n">
-        <v>8264830</v>
+        <v>8171310</v>
       </c>
       <c r="P363" t="n">
         <v>18900</v>
       </c>
       <c r="Q363" t="n">
-        <v>13362300</v>
+        <v>13211100</v>
       </c>
     </row>
     <row r="364">
@@ -16546,22 +16546,22 @@
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M365" t="n">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="N365" t="n">
         <v>9736</v>
       </c>
       <c r="O365" t="n">
-        <v>6815200</v>
+        <v>6766520</v>
       </c>
       <c r="P365" t="n">
         <v>15900</v>
       </c>
       <c r="Q365" t="n">
-        <v>11130000</v>
+        <v>11050500</v>
       </c>
     </row>
     <row r="366">
@@ -16595,22 +16595,22 @@
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M366" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="N366" t="n">
         <v>44470</v>
       </c>
       <c r="O366" t="n">
-        <v>1823270</v>
+        <v>1600920</v>
       </c>
       <c r="P366" t="n">
         <v>71900</v>
       </c>
       <c r="Q366" t="n">
-        <v>2947900</v>
+        <v>2588400</v>
       </c>
     </row>
     <row r="367">
@@ -16644,22 +16644,22 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M367" t="n">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="N367" t="n">
         <v>5215</v>
       </c>
       <c r="O367" t="n">
-        <v>5016830</v>
+        <v>4975110</v>
       </c>
       <c r="P367" t="n">
         <v>8900</v>
       </c>
       <c r="Q367" t="n">
-        <v>8561800</v>
+        <v>8490600</v>
       </c>
     </row>
     <row r="368">
@@ -20721,22 +20721,22 @@
         <v>0</v>
       </c>
       <c r="L453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M453" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N453" t="n">
         <v>27577.72</v>
       </c>
       <c r="O453" t="n">
-        <v>110310.88</v>
+        <v>82733.16</v>
       </c>
       <c r="P453" t="n">
         <v>120900</v>
       </c>
       <c r="Q453" t="n">
-        <v>483600</v>
+        <v>362700</v>
       </c>
     </row>
     <row r="454">
@@ -24414,22 +24414,22 @@
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M532" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N532" t="n">
         <v>15239.8</v>
       </c>
       <c r="O532" t="n">
-        <v>182877.6</v>
+        <v>137158.2</v>
       </c>
       <c r="P532" t="n">
         <v>15900</v>
       </c>
       <c r="Q532" t="n">
-        <v>190800</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="533">

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>233</v>
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>26</v>
@@ -5057,13 +5057,13 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
         <v>544</v>
@@ -5494,13 +5494,13 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
         <v>638</v>
@@ -5720,13 +5720,13 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>2406</v>
+        <v>2388</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
         <v>2388</v>
@@ -9026,13 +9026,13 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
         <v>10</v>
@@ -9246,13 +9246,13 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>1160</v>
+        <v>1140</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
         <v>1140</v>
@@ -9674,13 +9674,13 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
         <v>903</v>
@@ -11289,13 +11289,13 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
         <v>128</v>
@@ -14194,13 +14194,13 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
         <v>88</v>
@@ -14286,13 +14286,13 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
         <v>7</v>
@@ -14976,13 +14976,13 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M331" t="n">
         <v>103</v>
@@ -15022,13 +15022,13 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
       </c>
       <c r="L332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M332" t="n">
         <v>6</v>
@@ -16442,13 +16442,13 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M363" t="n">
         <v>699</v>
@@ -16540,13 +16540,13 @@
         </is>
       </c>
       <c r="J365" t="n">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M365" t="n">
         <v>695</v>
@@ -16589,13 +16589,13 @@
         </is>
       </c>
       <c r="J366" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K366" t="n">
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M366" t="n">
         <v>36</v>
@@ -16638,13 +16638,13 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
         <v>954</v>
@@ -20715,13 +20715,13 @@
         </is>
       </c>
       <c r="J453" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K453" t="n">
         <v>0</v>
       </c>
       <c r="L453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M453" t="n">
         <v>3</v>
@@ -24408,13 +24408,13 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M532" t="n">
         <v>9</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -556,10 +556,10 @@
         <v>37</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27065.693430657</v>
       </c>
       <c r="O4" t="n">
-        <v>999000</v>
+        <v>1001430.656934309</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -595,10 +595,10 @@
         <v>233</v>
       </c>
       <c r="N5" t="n">
-        <v>27000</v>
+        <v>27109.756097561</v>
       </c>
       <c r="O5" t="n">
-        <v>6291000</v>
+        <v>6316573.170731713</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
@@ -1151,10 +1151,10 @@
         <v>440</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8370711297</v>
+        <v>3926.837066527</v>
       </c>
       <c r="O19" t="n">
-        <v>1727808.311297068</v>
+        <v>1727808.30927188</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -1310,10 +1310,10 @@
         <v>48</v>
       </c>
       <c r="N23" t="n">
-        <v>3716.3301970443</v>
+        <v>3716.3301973684</v>
       </c>
       <c r="O23" t="n">
-        <v>178383.8494581264</v>
+        <v>178383.8494736832</v>
       </c>
       <c r="P23" t="n">
         <v>9500</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.072297891</v>
+        <v>1098.0725121628</v>
       </c>
       <c r="O70" t="n">
-        <v>129572.531151138</v>
+        <v>129572.5564352104</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4068,10 +4068,10 @@
         <v>844</v>
       </c>
       <c r="N88" t="n">
-        <v>10600</v>
+        <v>10614.851138354</v>
       </c>
       <c r="O88" t="n">
-        <v>8946400</v>
+        <v>8958934.360770777</v>
       </c>
       <c r="P88" t="n">
         <v>17200</v>
@@ -4885,10 +4885,10 @@
         <v>366</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300552868</v>
+        <v>4890.930055517</v>
       </c>
       <c r="O106" t="n">
-        <v>1790080.400234969</v>
+        <v>1790080.400319222</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
@@ -5601,10 +5601,10 @@
         <v>252</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.463007951</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O122" t="n">
-        <v>3130460.678003652</v>
+        <v>3130460.679345048</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5732,10 +5732,10 @@
         <v>2388</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2763500602</v>
+        <v>3472.2763717066</v>
       </c>
       <c r="O125" t="n">
-        <v>8291795.923943758</v>
+        <v>8291795.975635361</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600149925</v>
+        <v>3041.660015015</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.667511242</v>
+        <v>1523871.667522515</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5912,10 +5912,10 @@
         <v>1101</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1729689003</v>
+        <v>4371.1729703288</v>
       </c>
       <c r="O129" t="n">
-        <v>4812661.43875923</v>
+        <v>4812661.440332009</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9249342316</v>
+        <v>1630.925009772</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.6624382356</v>
+        <v>311506.676866452</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1949322169</v>
+        <v>1550.1949414115</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.0175598084</v>
+        <v>55807.017890814</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -8746,10 +8746,10 @@
         <v>348</v>
       </c>
       <c r="N193" t="n">
-        <v>2029.8742253521</v>
+        <v>2029.8742541123</v>
       </c>
       <c r="O193" t="n">
-        <v>706396.2304225308</v>
+        <v>706396.2404310803</v>
       </c>
       <c r="P193" t="n">
         <v>3600</v>
@@ -8951,10 +8951,10 @@
         <v>170</v>
       </c>
       <c r="N198" t="n">
-        <v>2680.7396931747</v>
+        <v>2680.7396929825</v>
       </c>
       <c r="O198" t="n">
-        <v>455725.747839699</v>
+        <v>455725.747807025</v>
       </c>
       <c r="P198" t="n">
         <v>4900</v>
@@ -9125,10 +9125,10 @@
         <v>79</v>
       </c>
       <c r="N202" t="n">
-        <v>30611</v>
+        <v>30745.062773723</v>
       </c>
       <c r="O202" t="n">
-        <v>2418269</v>
+        <v>2428859.959124117</v>
       </c>
       <c r="P202" t="n">
         <v>38900</v>
@@ -9258,10 +9258,10 @@
         <v>1140</v>
       </c>
       <c r="N205" t="n">
-        <v>6207.9882021366</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O205" t="n">
-        <v>7077106.550435725</v>
+        <v>7077106.549571034</v>
       </c>
       <c r="P205" t="n">
         <v>9900</v>
@@ -9599,10 +9599,10 @@
         <v>290</v>
       </c>
       <c r="N213" t="n">
-        <v>1106</v>
+        <v>1111.1642023346</v>
       </c>
       <c r="O213" t="n">
-        <v>320740</v>
+        <v>322237.618677034</v>
       </c>
       <c r="P213" t="n">
         <v>2100</v>
@@ -9645,10 +9645,10 @@
         <v>697</v>
       </c>
       <c r="N214" t="n">
-        <v>4814.2633769677</v>
+        <v>4814.2633736737</v>
       </c>
       <c r="O214" t="n">
-        <v>3355541.573746487</v>
+        <v>3355541.571450569</v>
       </c>
       <c r="P214" t="n">
         <v>9900</v>
@@ -9773,10 +9773,10 @@
         <v>20</v>
       </c>
       <c r="N217" t="n">
-        <v>27123.764688797</v>
+        <v>27123.764610526</v>
       </c>
       <c r="O217" t="n">
-        <v>542475.29377594</v>
+        <v>542475.29221052</v>
       </c>
       <c r="P217" t="n">
         <v>44500</v>
@@ -10029,10 +10029,10 @@
         <v>97</v>
       </c>
       <c r="N223" t="n">
-        <v>2568.8354081633</v>
+        <v>2568.8353767123</v>
       </c>
       <c r="O223" t="n">
-        <v>249177.0345918401</v>
+        <v>249177.0315410931</v>
       </c>
       <c r="P223" t="n">
         <v>4500</v>
@@ -10829,10 +10829,10 @@
         <v>88</v>
       </c>
       <c r="N241" t="n">
-        <v>7700</v>
+        <v>7738.024691358</v>
       </c>
       <c r="O241" t="n">
-        <v>677600</v>
+        <v>680946.1728395041</v>
       </c>
       <c r="P241" t="n">
         <v>13900</v>
@@ -11347,10 +11347,10 @@
         <v>3</v>
       </c>
       <c r="N252" t="n">
-        <v>23521.622708333</v>
+        <v>23521.621666667</v>
       </c>
       <c r="O252" t="n">
-        <v>70564.868124999</v>
+        <v>70564.86500000101</v>
       </c>
       <c r="P252" t="n">
         <v>39000</v>
@@ -11475,10 +11475,10 @@
         <v>883</v>
       </c>
       <c r="N255" t="n">
-        <v>1778.4728840436</v>
+        <v>1778.4728878597</v>
       </c>
       <c r="O255" t="n">
-        <v>1570391.556610499</v>
+        <v>1570391.559980115</v>
       </c>
       <c r="P255" t="n">
         <v>4900</v>
@@ -11613,10 +11613,10 @@
         <v>62</v>
       </c>
       <c r="N258" t="n">
-        <v>16058</v>
+        <v>16177.301634473</v>
       </c>
       <c r="O258" t="n">
-        <v>995596</v>
+        <v>1002992.701337326</v>
       </c>
       <c r="P258" t="n">
         <v>25900</v>
@@ -12303,10 +12303,10 @@
         <v>15</v>
       </c>
       <c r="N273" t="n">
-        <v>3259.2102666667</v>
+        <v>3259.2102702703</v>
       </c>
       <c r="O273" t="n">
-        <v>48888.1540000005</v>
+        <v>48888.1540540545</v>
       </c>
       <c r="P273" t="n">
         <v>5300</v>
@@ -13743,10 +13743,10 @@
         <v>143</v>
       </c>
       <c r="N304" t="n">
-        <v>2252.3008997955</v>
+        <v>2252.3011740042</v>
       </c>
       <c r="O304" t="n">
-        <v>322079.0286707565</v>
+        <v>322079.0678826006</v>
       </c>
       <c r="P304" t="n">
         <v>3900</v>
@@ -14022,10 +14022,10 @@
         <v>153</v>
       </c>
       <c r="N310" t="n">
-        <v>3519</v>
+        <v>4129.9375</v>
       </c>
       <c r="O310" t="n">
-        <v>538407</v>
+        <v>631880.4375</v>
       </c>
       <c r="P310" t="n">
         <v>5900</v>
@@ -14344,10 +14344,10 @@
         <v>100</v>
       </c>
       <c r="N317" t="n">
-        <v>4907.8227973568</v>
+        <v>4907.8228159645</v>
       </c>
       <c r="O317" t="n">
-        <v>490782.27973568</v>
+        <v>490782.28159645</v>
       </c>
       <c r="P317" t="n">
         <v>8200</v>
@@ -15126,10 +15126,10 @@
         <v>19</v>
       </c>
       <c r="N334" t="n">
-        <v>19008</v>
+        <v>19059.165545087</v>
       </c>
       <c r="O334" t="n">
-        <v>361152</v>
+        <v>362124.145356653</v>
       </c>
       <c r="P334" t="n">
         <v>30900</v>
@@ -15172,10 +15172,10 @@
         <v>82</v>
       </c>
       <c r="N335" t="n">
-        <v>17992</v>
+        <v>18038.854166667</v>
       </c>
       <c r="O335" t="n">
-        <v>1475344</v>
+        <v>1479186.041666694</v>
       </c>
       <c r="P335" t="n">
         <v>28900</v>
@@ -16356,10 +16356,10 @@
         <v>2063</v>
       </c>
       <c r="N361" t="n">
-        <v>692.15251958462</v>
+        <v>692.1525362185999</v>
       </c>
       <c r="O361" t="n">
-        <v>1427910.647903071</v>
+        <v>1427910.682218972</v>
       </c>
       <c r="P361" t="n">
         <v>1200</v>
@@ -17554,10 +17554,10 @@
         <v>158</v>
       </c>
       <c r="N386" t="n">
-        <v>1690.8700095969</v>
+        <v>1690.8700097561</v>
       </c>
       <c r="O386" t="n">
-        <v>267157.4615163102</v>
+        <v>267157.4615414638</v>
       </c>
       <c r="P386" t="n">
         <v>3000</v>
@@ -18447,10 +18447,10 @@
         <v>132</v>
       </c>
       <c r="N405" t="n">
-        <v>3259.1346835443</v>
+        <v>3259.1347844828</v>
       </c>
       <c r="O405" t="n">
-        <v>430205.7782278476</v>
+        <v>430205.7915517296</v>
       </c>
       <c r="P405" t="n">
         <v>3600</v>
@@ -18583,10 +18583,10 @@
         <v>2</v>
       </c>
       <c r="N408" t="n">
-        <v>3110.8352523988</v>
+        <v>3110.8351781971</v>
       </c>
       <c r="O408" t="n">
-        <v>6221.6705047976</v>
+        <v>6221.6703563942</v>
       </c>
       <c r="P408" t="n">
         <v>4500</v>
@@ -18957,10 +18957,10 @@
         <v>4</v>
       </c>
       <c r="N416" t="n">
-        <v>2501.384</v>
+        <v>2501.3837931034</v>
       </c>
       <c r="O416" t="n">
-        <v>10005.536</v>
+        <v>10005.5351724136</v>
       </c>
       <c r="P416" t="n">
         <v>4100</v>
@@ -19952,10 +19952,10 @@
         <v>23</v>
       </c>
       <c r="N437" t="n">
-        <v>2832.195862069</v>
+        <v>2986.6792727273</v>
       </c>
       <c r="O437" t="n">
-        <v>65140.50482758701</v>
+        <v>68693.6232727279</v>
       </c>
       <c r="P437" t="n">
         <v>12900</v>
@@ -20338,10 +20338,10 @@
         <v>3</v>
       </c>
       <c r="N445" t="n">
-        <v>12448.354</v>
+        <v>12448.355263158</v>
       </c>
       <c r="O445" t="n">
-        <v>37345.062</v>
+        <v>37345.065789474</v>
       </c>
       <c r="P445" t="n">
         <v>22900</v>
@@ -22422,10 +22422,10 @@
         <v>288</v>
       </c>
       <c r="N488" t="n">
-        <v>430.60997520149</v>
+        <v>430.6099751861</v>
       </c>
       <c r="O488" t="n">
-        <v>124015.6728580291</v>
+        <v>124015.6728535968</v>
       </c>
       <c r="P488" t="n">
         <v>2200</v>
@@ -23040,10 +23040,10 @@
         <v>11</v>
       </c>
       <c r="N502" t="n">
-        <v>22951.704647137</v>
+        <v>22951.704432133</v>
       </c>
       <c r="O502" t="n">
-        <v>252468.751118507</v>
+        <v>252468.748753463</v>
       </c>
       <c r="P502" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>37</v>
       </c>
       <c r="N4" t="n">
-        <v>27065.693430657</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>1001430.656934309</v>
+        <v>999000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -673,10 +673,10 @@
         <v>572</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7463799384</v>
+        <v>3376.7463585118</v>
       </c>
       <c r="O7" t="n">
-        <v>1931498.929324765</v>
+        <v>1931498.917068749</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1151,10 +1151,10 @@
         <v>440</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.837066527</v>
+        <v>3926.837057278</v>
       </c>
       <c r="O19" t="n">
-        <v>1727808.30927188</v>
+        <v>1727808.30520232</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -2074,10 +2074,10 @@
         <v>34</v>
       </c>
       <c r="N42" t="n">
-        <v>61666.874389535</v>
+        <v>61666.874467456</v>
       </c>
       <c r="O42" t="n">
-        <v>2096673.72924419</v>
+        <v>2096673.731893504</v>
       </c>
       <c r="P42" t="n">
         <v>98900</v>
@@ -2927,10 +2927,10 @@
         <v>415</v>
       </c>
       <c r="N62" t="n">
-        <v>4937.310173913</v>
+        <v>4937.3101888412</v>
       </c>
       <c r="O62" t="n">
-        <v>2048983.722173895</v>
+        <v>2048983.728369098</v>
       </c>
       <c r="P62" t="n">
         <v>7500</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0725121628</v>
+        <v>1098.0729937163</v>
       </c>
       <c r="O70" t="n">
-        <v>129572.5564352104</v>
+        <v>129572.6132585234</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -4068,10 +4068,10 @@
         <v>844</v>
       </c>
       <c r="N88" t="n">
-        <v>10614.851138354</v>
+        <v>10600</v>
       </c>
       <c r="O88" t="n">
-        <v>8958934.360770777</v>
+        <v>8946400</v>
       </c>
       <c r="P88" t="n">
         <v>17200</v>
@@ -4885,10 +4885,10 @@
         <v>366</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.930055517</v>
+        <v>4890.9300565371</v>
       </c>
       <c r="O106" t="n">
-        <v>1790080.400319222</v>
+        <v>1790080.400692579</v>
       </c>
       <c r="P106" t="n">
         <v>8200</v>
@@ -5601,10 +5601,10 @@
         <v>252</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.463013274</v>
+        <v>12422.46300928</v>
       </c>
       <c r="O122" t="n">
-        <v>3130460.679345048</v>
+        <v>3130460.67833856</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5732,10 +5732,10 @@
         <v>2388</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2763717066</v>
+        <v>3472.2763744227</v>
       </c>
       <c r="O125" t="n">
-        <v>8291795.975635361</v>
+        <v>8291795.982121408</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.660015015</v>
+        <v>3041.6600151515</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.667522515</v>
+        <v>1523871.667590901</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5912,10 +5912,10 @@
         <v>1101</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1729703288</v>
+        <v>4371.1729731899</v>
       </c>
       <c r="O129" t="n">
-        <v>4812661.440332009</v>
+        <v>4812661.44348208</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.925009772</v>
+        <v>1630.9251181364</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.676866452</v>
+        <v>311506.6975640524</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1949414115</v>
+        <v>1550.1950026961</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.017890814</v>
+        <v>55807.0200970596</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7456,10 +7456,10 @@
         <v>48</v>
       </c>
       <c r="N163" t="n">
-        <v>1579.3809042553</v>
+        <v>1579.380802139</v>
       </c>
       <c r="O163" t="n">
-        <v>75810.2834042544</v>
+        <v>75810.27850267201</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -8377,10 +8377,10 @@
         <v>46</v>
       </c>
       <c r="N184" t="n">
-        <v>5162.2537195122</v>
+        <v>5162.2534810127</v>
       </c>
       <c r="O184" t="n">
-        <v>237463.6710975612</v>
+        <v>237463.6601265842</v>
       </c>
       <c r="P184" t="n">
         <v>8200</v>
@@ -8787,10 +8787,10 @@
         <v>142</v>
       </c>
       <c r="N194" t="n">
-        <v>22485.695396419</v>
+        <v>22485.695378691</v>
       </c>
       <c r="O194" t="n">
-        <v>3192968.746291498</v>
+        <v>3192968.743774122</v>
       </c>
       <c r="P194" t="n">
         <v>36500</v>
@@ -9258,10 +9258,10 @@
         <v>1140</v>
       </c>
       <c r="N205" t="n">
-        <v>6207.9882013781</v>
+        <v>6207.9882003658</v>
       </c>
       <c r="O205" t="n">
-        <v>7077106.549571034</v>
+        <v>7077106.548417012</v>
       </c>
       <c r="P205" t="n">
         <v>9900</v>
@@ -9599,10 +9599,10 @@
         <v>290</v>
       </c>
       <c r="N213" t="n">
-        <v>1111.1642023346</v>
+        <v>1106</v>
       </c>
       <c r="O213" t="n">
-        <v>322237.618677034</v>
+        <v>320740</v>
       </c>
       <c r="P213" t="n">
         <v>2100</v>
@@ -9645,10 +9645,10 @@
         <v>697</v>
       </c>
       <c r="N214" t="n">
-        <v>4814.2633736737</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O214" t="n">
-        <v>3355541.571450569</v>
+        <v>3355541.553000979</v>
       </c>
       <c r="P214" t="n">
         <v>9900</v>
@@ -9692,10 +9692,10 @@
         <v>3242790.39</v>
       </c>
       <c r="P215" t="n">
-        <v>6300</v>
+        <v>6900</v>
       </c>
       <c r="Q215" t="n">
-        <v>5688900</v>
+        <v>6230700</v>
       </c>
     </row>
     <row r="216">
@@ -10829,10 +10829,10 @@
         <v>88</v>
       </c>
       <c r="N241" t="n">
-        <v>7738.024691358</v>
+        <v>7700</v>
       </c>
       <c r="O241" t="n">
-        <v>680946.1728395041</v>
+        <v>677600</v>
       </c>
       <c r="P241" t="n">
         <v>13900</v>
@@ -11347,10 +11347,10 @@
         <v>3</v>
       </c>
       <c r="N252" t="n">
-        <v>23521.621666667</v>
+        <v>23521.621025641</v>
       </c>
       <c r="O252" t="n">
-        <v>70564.86500000101</v>
+        <v>70564.86307692301</v>
       </c>
       <c r="P252" t="n">
         <v>39000</v>
@@ -11475,10 +11475,10 @@
         <v>883</v>
       </c>
       <c r="N255" t="n">
-        <v>1778.4728878597</v>
+        <v>1778.4728955224</v>
       </c>
       <c r="O255" t="n">
-        <v>1570391.559980115</v>
+        <v>1570391.566746279</v>
       </c>
       <c r="P255" t="n">
         <v>4900</v>
@@ -11613,10 +11613,10 @@
         <v>62</v>
       </c>
       <c r="N258" t="n">
-        <v>16177.301634473</v>
+        <v>16058</v>
       </c>
       <c r="O258" t="n">
-        <v>1002992.701337326</v>
+        <v>995596</v>
       </c>
       <c r="P258" t="n">
         <v>25900</v>
@@ -12303,10 +12303,10 @@
         <v>15</v>
       </c>
       <c r="N273" t="n">
-        <v>3259.2102702703</v>
+        <v>3259.2102666667</v>
       </c>
       <c r="O273" t="n">
-        <v>48888.1540540545</v>
+        <v>48888.1540000005</v>
       </c>
       <c r="P273" t="n">
         <v>5300</v>
@@ -13743,10 +13743,10 @@
         <v>143</v>
       </c>
       <c r="N304" t="n">
-        <v>2252.3011740042</v>
+        <v>2252.3013646055</v>
       </c>
       <c r="O304" t="n">
-        <v>322079.0678826006</v>
+        <v>322079.0951385865</v>
       </c>
       <c r="P304" t="n">
         <v>3900</v>
@@ -14022,10 +14022,10 @@
         <v>153</v>
       </c>
       <c r="N310" t="n">
-        <v>4129.9375</v>
+        <v>3519</v>
       </c>
       <c r="O310" t="n">
-        <v>631880.4375</v>
+        <v>538407</v>
       </c>
       <c r="P310" t="n">
         <v>5900</v>
@@ -14344,10 +14344,10 @@
         <v>100</v>
       </c>
       <c r="N317" t="n">
-        <v>4907.8228159645</v>
+        <v>4907.8228222222</v>
       </c>
       <c r="O317" t="n">
-        <v>490782.28159645</v>
+        <v>490782.28222222</v>
       </c>
       <c r="P317" t="n">
         <v>8200</v>
@@ -14574,10 +14574,10 @@
         <v>84</v>
       </c>
       <c r="N322" t="n">
-        <v>3903.7399452055</v>
+        <v>3903.7403351955</v>
       </c>
       <c r="O322" t="n">
-        <v>327914.155397262</v>
+        <v>327914.188156422</v>
       </c>
       <c r="P322" t="n">
         <v>7500</v>
@@ -15949,10 +15949,10 @@
         <v>839</v>
       </c>
       <c r="N352" t="n">
-        <v>1516.0387067969</v>
+        <v>1516.0386973545</v>
       </c>
       <c r="O352" t="n">
-        <v>1271956.475002599</v>
+        <v>1271956.467080425</v>
       </c>
       <c r="P352" t="n">
         <v>2300</v>
@@ -16356,10 +16356,10 @@
         <v>2063</v>
       </c>
       <c r="N361" t="n">
-        <v>692.1525362185999</v>
+        <v>692.1525418121701</v>
       </c>
       <c r="O361" t="n">
-        <v>1427910.682218972</v>
+        <v>1427910.693758507</v>
       </c>
       <c r="P361" t="n">
         <v>1200</v>
@@ -17554,10 +17554,10 @@
         <v>158</v>
       </c>
       <c r="N386" t="n">
-        <v>1690.8700097561</v>
+        <v>1690.8700097895</v>
       </c>
       <c r="O386" t="n">
-        <v>267157.4615414638</v>
+        <v>267157.461546741</v>
       </c>
       <c r="P386" t="n">
         <v>3000</v>
@@ -18583,10 +18583,10 @@
         <v>2</v>
       </c>
       <c r="N408" t="n">
-        <v>3110.8351781971</v>
+        <v>3110.8351657574</v>
       </c>
       <c r="O408" t="n">
-        <v>6221.6703563942</v>
+        <v>6221.6703315148</v>
       </c>
       <c r="P408" t="n">
         <v>4500</v>
@@ -23040,10 +23040,10 @@
         <v>11</v>
       </c>
       <c r="N502" t="n">
-        <v>22951.704432133</v>
+        <v>22951.704393305</v>
       </c>
       <c r="O502" t="n">
-        <v>252468.748753463</v>
+        <v>252468.748326355</v>
       </c>
       <c r="P502" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -595,10 +595,10 @@
         <v>233</v>
       </c>
       <c r="N5" t="n">
-        <v>27109.756097561</v>
+        <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>6316573.170731713</v>
+        <v>6291000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
@@ -3281,10 +3281,10 @@
         <v>118</v>
       </c>
       <c r="N70" t="n">
-        <v>1098.0729937163</v>
+        <v>1098.0730382022</v>
       </c>
       <c r="O70" t="n">
-        <v>129572.6132585234</v>
+        <v>129572.6185078596</v>
       </c>
       <c r="P70" t="n">
         <v>1500</v>
@@ -5732,10 +5732,10 @@
         <v>2388</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2763744227</v>
+        <v>3472.276379862</v>
       </c>
       <c r="O125" t="n">
-        <v>8291795.982121408</v>
+        <v>8291795.995110456</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1950026961</v>
+        <v>1550.1949625568</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.0200970596</v>
+        <v>55807.0186520448</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -8746,10 +8746,10 @@
         <v>348</v>
       </c>
       <c r="N193" t="n">
-        <v>2029.8742541123</v>
+        <v>2029.8742613636</v>
       </c>
       <c r="O193" t="n">
-        <v>706396.2404310803</v>
+        <v>706396.2429545328</v>
       </c>
       <c r="P193" t="n">
         <v>3600</v>
@@ -9125,10 +9125,10 @@
         <v>79</v>
       </c>
       <c r="N202" t="n">
-        <v>30745.062773723</v>
+        <v>30611</v>
       </c>
       <c r="O202" t="n">
-        <v>2428859.959124117</v>
+        <v>2418269</v>
       </c>
       <c r="P202" t="n">
         <v>38900</v>
@@ -9258,10 +9258,10 @@
         <v>1140</v>
       </c>
       <c r="N205" t="n">
-        <v>6207.9882003658</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O205" t="n">
-        <v>7077106.548417012</v>
+        <v>7077106.549571034</v>
       </c>
       <c r="P205" t="n">
         <v>9900</v>
@@ -9645,10 +9645,10 @@
         <v>697</v>
       </c>
       <c r="N214" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.2633516301</v>
       </c>
       <c r="O214" t="n">
-        <v>3355541.553000979</v>
+        <v>3355541.55608618</v>
       </c>
       <c r="P214" t="n">
         <v>9900</v>
@@ -9773,10 +9773,10 @@
         <v>20</v>
       </c>
       <c r="N217" t="n">
-        <v>27123.764610526</v>
+        <v>27123.764587738</v>
       </c>
       <c r="O217" t="n">
-        <v>542475.29221052</v>
+        <v>542475.29175476</v>
       </c>
       <c r="P217" t="n">
         <v>44500</v>
@@ -10973,10 +10973,10 @@
         <v>125</v>
       </c>
       <c r="N244" t="n">
-        <v>9188.98</v>
+        <v>9456.2957818182</v>
       </c>
       <c r="O244" t="n">
-        <v>1148622.5</v>
+        <v>1182036.972727275</v>
       </c>
       <c r="P244" t="n">
         <v>12900</v>
@@ -11347,10 +11347,10 @@
         <v>3</v>
       </c>
       <c r="N252" t="n">
-        <v>23521.621025641</v>
+        <v>23521.620277778</v>
       </c>
       <c r="O252" t="n">
-        <v>70564.86307692301</v>
+        <v>70564.86083333401</v>
       </c>
       <c r="P252" t="n">
         <v>39000</v>
@@ -15126,10 +15126,10 @@
         <v>19</v>
       </c>
       <c r="N334" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="O334" t="n">
-        <v>362124.145356653</v>
+        <v>361152</v>
       </c>
       <c r="P334" t="n">
         <v>30900</v>
@@ -15172,10 +15172,10 @@
         <v>82</v>
       </c>
       <c r="N335" t="n">
-        <v>18038.854166667</v>
+        <v>17992</v>
       </c>
       <c r="O335" t="n">
-        <v>1479186.041666694</v>
+        <v>1475344</v>
       </c>
       <c r="P335" t="n">
         <v>28900</v>
@@ -15949,10 +15949,10 @@
         <v>839</v>
       </c>
       <c r="N352" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386990066</v>
       </c>
       <c r="O352" t="n">
-        <v>1271956.467080425</v>
+        <v>1271956.468466537</v>
       </c>
       <c r="P352" t="n">
         <v>2300</v>
@@ -16356,10 +16356,10 @@
         <v>2063</v>
       </c>
       <c r="N361" t="n">
-        <v>692.1525418121701</v>
+        <v>692.15254743047</v>
       </c>
       <c r="O361" t="n">
-        <v>1427910.693758507</v>
+        <v>1427910.70534906</v>
       </c>
       <c r="P361" t="n">
         <v>1200</v>
@@ -16990,10 +16990,10 @@
         <v>1051</v>
       </c>
       <c r="N374" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O374" t="n">
-        <v>9401594.379999999</v>
+        <v>9405832.514205847</v>
       </c>
       <c r="P374" t="n">
         <v>14900</v>
@@ -19952,10 +19952,10 @@
         <v>23</v>
       </c>
       <c r="N437" t="n">
-        <v>2986.6792727273</v>
+        <v>2832.1961818182</v>
       </c>
       <c r="O437" t="n">
-        <v>68693.6232727279</v>
+        <v>65140.51218181859</v>
       </c>
       <c r="P437" t="n">
         <v>12900</v>
@@ -23040,10 +23040,10 @@
         <v>11</v>
       </c>
       <c r="N502" t="n">
-        <v>22951.704393305</v>
+        <v>22951.704377622</v>
       </c>
       <c r="O502" t="n">
-        <v>252468.748326355</v>
+        <v>252468.748153842</v>
       </c>
       <c r="P502" t="n">
         <v>37900</v>
@@ -24660,10 +24660,10 @@
         <v>3</v>
       </c>
       <c r="N537" t="n">
-        <v>2432.1360526316</v>
+        <v>2432.1363013699</v>
       </c>
       <c r="O537" t="n">
-        <v>7296.408157894799</v>
+        <v>7296.4089041097</v>
       </c>
       <c r="P537" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1310,10 +1310,10 @@
         <v>48</v>
       </c>
       <c r="N23" t="n">
-        <v>3716.3301973684</v>
+        <v>3716.3301980198</v>
       </c>
       <c r="O23" t="n">
-        <v>178383.8494736832</v>
+        <v>178383.8495049504</v>
       </c>
       <c r="P23" t="n">
         <v>9500</v>
@@ -1588,10 +1588,10 @@
         <v>89</v>
       </c>
       <c r="N30" t="n">
-        <v>3910.6279262673</v>
+        <v>3910.6278971963</v>
       </c>
       <c r="O30" t="n">
-        <v>348045.8854377897</v>
+        <v>348045.8828504707</v>
       </c>
       <c r="P30" t="n">
         <v>9100</v>
@@ -4706,10 +4706,10 @@
         <v>179</v>
       </c>
       <c r="N102" t="n">
-        <v>3795.7100076453</v>
+        <v>3795.7100076628</v>
       </c>
       <c r="O102" t="n">
-        <v>679432.0913685086</v>
+        <v>679432.0913716411</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -4891,10 +4891,10 @@
         <v>1790080.400692579</v>
       </c>
       <c r="P106" t="n">
-        <v>8200</v>
+        <v>8900</v>
       </c>
       <c r="Q106" t="n">
-        <v>3001200</v>
+        <v>3257400</v>
       </c>
     </row>
     <row r="107">
@@ -5418,10 +5418,10 @@
         <v>135</v>
       </c>
       <c r="N118" t="n">
-        <v>5191.4800286123</v>
+        <v>5191.4800286533</v>
       </c>
       <c r="O118" t="n">
-        <v>700849.8038626605</v>
+        <v>700849.8038681955</v>
       </c>
       <c r="P118" t="n">
         <v>9100</v>
@@ -5732,10 +5732,10 @@
         <v>2388</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.276379862</v>
+        <v>3472.276393501</v>
       </c>
       <c r="O125" t="n">
-        <v>8291795.995110456</v>
+        <v>8291796.027680388</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5825,10 +5825,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600151515</v>
+        <v>3041.660015186</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.667590901</v>
+        <v>1523871.667608186</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9251181364</v>
+        <v>1630.9251335113</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.6975640524</v>
+        <v>311506.7005006583</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -8295,10 +8295,10 @@
         <v>670</v>
       </c>
       <c r="N182" t="n">
-        <v>4196.8725467746</v>
+        <v>4196.8725524769</v>
       </c>
       <c r="O182" t="n">
-        <v>2811904.606338982</v>
+        <v>2811904.610159523</v>
       </c>
       <c r="P182" t="n">
         <v>5900</v>
@@ -8787,10 +8787,10 @@
         <v>142</v>
       </c>
       <c r="N194" t="n">
-        <v>22485.695378691</v>
+        <v>22485.69534282</v>
       </c>
       <c r="O194" t="n">
-        <v>3192968.743774122</v>
+        <v>3192968.73868044</v>
       </c>
       <c r="P194" t="n">
         <v>36500</v>
@@ -8951,10 +8951,10 @@
         <v>170</v>
       </c>
       <c r="N198" t="n">
-        <v>2680.7396929825</v>
+        <v>2680.7396925972</v>
       </c>
       <c r="O198" t="n">
-        <v>455725.747807025</v>
+        <v>455725.747741524</v>
       </c>
       <c r="P198" t="n">
         <v>4900</v>
@@ -9258,10 +9258,10 @@
         <v>1140</v>
       </c>
       <c r="N205" t="n">
-        <v>6207.9882013781</v>
+        <v>6207.9881978301</v>
       </c>
       <c r="O205" t="n">
-        <v>7077106.549571034</v>
+        <v>7077106.545526314</v>
       </c>
       <c r="P205" t="n">
         <v>9900</v>
@@ -9645,16 +9645,16 @@
         <v>697</v>
       </c>
       <c r="N214" t="n">
-        <v>4814.2633516301</v>
+        <v>4814.2633494176</v>
       </c>
       <c r="O214" t="n">
-        <v>3355541.55608618</v>
+        <v>3355541.554544067</v>
       </c>
       <c r="P214" t="n">
-        <v>9900</v>
+        <v>7900</v>
       </c>
       <c r="Q214" t="n">
-        <v>6900300</v>
+        <v>5506300</v>
       </c>
     </row>
     <row r="215">
@@ -10973,10 +10973,10 @@
         <v>125</v>
       </c>
       <c r="N244" t="n">
-        <v>9456.2957818182</v>
+        <v>9188.98</v>
       </c>
       <c r="O244" t="n">
-        <v>1182036.972727275</v>
+        <v>1148622.5</v>
       </c>
       <c r="P244" t="n">
         <v>12900</v>
@@ -11347,10 +11347,10 @@
         <v>3</v>
       </c>
       <c r="N252" t="n">
-        <v>23521.620277778</v>
+        <v>23521.618709677</v>
       </c>
       <c r="O252" t="n">
-        <v>70564.86083333401</v>
+        <v>70564.856129031</v>
       </c>
       <c r="P252" t="n">
         <v>39000</v>
@@ -14344,10 +14344,10 @@
         <v>100</v>
       </c>
       <c r="N317" t="n">
-        <v>4907.8228222222</v>
+        <v>4907.8228863636</v>
       </c>
       <c r="O317" t="n">
-        <v>490782.28222222</v>
+        <v>490782.28863636</v>
       </c>
       <c r="P317" t="n">
         <v>8200</v>
@@ -14574,10 +14574,10 @@
         <v>84</v>
       </c>
       <c r="N322" t="n">
-        <v>3903.7403351955</v>
+        <v>3903.7404686036</v>
       </c>
       <c r="O322" t="n">
-        <v>327914.188156422</v>
+        <v>327914.1993627024</v>
       </c>
       <c r="P322" t="n">
         <v>7500</v>
@@ -15949,10 +15949,10 @@
         <v>839</v>
       </c>
       <c r="N352" t="n">
-        <v>1516.0386990066</v>
+        <v>1516.0386973545</v>
       </c>
       <c r="O352" t="n">
-        <v>1271956.468466537</v>
+        <v>1271956.467080425</v>
       </c>
       <c r="P352" t="n">
         <v>2300</v>
@@ -16356,10 +16356,10 @@
         <v>2063</v>
       </c>
       <c r="N361" t="n">
-        <v>692.15254743047</v>
+        <v>692.15255307366</v>
       </c>
       <c r="O361" t="n">
-        <v>1427910.70534906</v>
+        <v>1427910.716990961</v>
       </c>
       <c r="P361" t="n">
         <v>1200</v>
@@ -16990,10 +16990,10 @@
         <v>1051</v>
       </c>
       <c r="N374" t="n">
-        <v>8949.4124778362</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O374" t="n">
-        <v>9405832.514205847</v>
+        <v>9401594.379999999</v>
       </c>
       <c r="P374" t="n">
         <v>14900</v>
@@ -17554,10 +17554,10 @@
         <v>158</v>
       </c>
       <c r="N386" t="n">
-        <v>1690.8700097895</v>
+        <v>1690.8700098184</v>
       </c>
       <c r="O386" t="n">
-        <v>267157.461546741</v>
+        <v>267157.4615513072</v>
       </c>
       <c r="P386" t="n">
         <v>3000</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -3507,10 +3507,10 @@
         <v>173</v>
       </c>
       <c r="N75" t="n">
-        <v>13593.35</v>
+        <v>13694.165945612</v>
       </c>
       <c r="O75" t="n">
-        <v>2351649.55</v>
+        <v>2369090.708590876</v>
       </c>
       <c r="P75" t="n">
         <v>25500</v>
@@ -4885,10 +4885,10 @@
         <v>366</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300565371</v>
+        <v>4890.9300570207</v>
       </c>
       <c r="O106" t="n">
-        <v>1790080.400692579</v>
+        <v>1790080.400869576</v>
       </c>
       <c r="P106" t="n">
         <v>8900</v>
@@ -5601,10 +5601,10 @@
         <v>252</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.46300928</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O122" t="n">
-        <v>3130460.67833856</v>
+        <v>3130460.679345048</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5732,10 +5732,10 @@
         <v>2388</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.276393501</v>
+        <v>3472.2764071985</v>
       </c>
       <c r="O125" t="n">
-        <v>8291796.027680388</v>
+        <v>8291796.060390018</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5912,10 +5912,10 @@
         <v>1101</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O129" t="n">
-        <v>4812661.44348208</v>
+        <v>4812661.444007697</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9251335113</v>
+        <v>1633.1055147059</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.7005006583</v>
+        <v>311923.1533088269</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1949625568</v>
+        <v>1550.1949638844</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.0186520448</v>
+        <v>55807.0186998384</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -8069,10 +8069,10 @@
         <v>42</v>
       </c>
       <c r="N177" t="n">
-        <v>18071.26</v>
+        <v>18238.586481481</v>
       </c>
       <c r="O177" t="n">
-        <v>758992.9199999999</v>
+        <v>766020.632222202</v>
       </c>
       <c r="P177" t="n">
         <v>23900</v>
@@ -9645,10 +9645,10 @@
         <v>697</v>
       </c>
       <c r="N214" t="n">
-        <v>4814.2633494176</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O214" t="n">
-        <v>3355541.554544067</v>
+        <v>3355541.553000979</v>
       </c>
       <c r="P214" t="n">
         <v>7900</v>
@@ -9773,10 +9773,10 @@
         <v>20</v>
       </c>
       <c r="N217" t="n">
-        <v>27123.764587738</v>
+        <v>27123.764576271</v>
       </c>
       <c r="O217" t="n">
-        <v>542475.29175476</v>
+        <v>542475.29152542</v>
       </c>
       <c r="P217" t="n">
         <v>44500</v>
@@ -10973,10 +10973,10 @@
         <v>125</v>
       </c>
       <c r="N244" t="n">
-        <v>9188.98</v>
+        <v>9254.3819928826</v>
       </c>
       <c r="O244" t="n">
-        <v>1148622.5</v>
+        <v>1156797.749110325</v>
       </c>
       <c r="P244" t="n">
         <v>12900</v>
@@ -11659,10 +11659,10 @@
         <v>24</v>
       </c>
       <c r="N259" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O259" t="n">
-        <v>612816</v>
+        <v>613864.7438676481</v>
       </c>
       <c r="P259" t="n">
         <v>40900</v>
@@ -12303,10 +12303,10 @@
         <v>15</v>
       </c>
       <c r="N273" t="n">
-        <v>3259.2102666667</v>
+        <v>3259.2102702703</v>
       </c>
       <c r="O273" t="n">
-        <v>48888.1540000005</v>
+        <v>48888.1540540545</v>
       </c>
       <c r="P273" t="n">
         <v>5300</v>
@@ -12633,10 +12633,10 @@
         <v>17</v>
       </c>
       <c r="N280" t="n">
-        <v>2260</v>
+        <v>2280.7339449541</v>
       </c>
       <c r="O280" t="n">
-        <v>38420</v>
+        <v>38772.4770642197</v>
       </c>
       <c r="P280" t="n">
         <v>3800</v>
@@ -14068,10 +14068,10 @@
         <v>47</v>
       </c>
       <c r="N311" t="n">
-        <v>9003</v>
+        <v>9018.1565656566</v>
       </c>
       <c r="O311" t="n">
-        <v>423141</v>
+        <v>423853.3585858602</v>
       </c>
       <c r="P311" t="n">
         <v>14900</v>
@@ -15172,10 +15172,10 @@
         <v>82</v>
       </c>
       <c r="N335" t="n">
-        <v>17992</v>
+        <v>18015.518954248</v>
       </c>
       <c r="O335" t="n">
-        <v>1475344</v>
+        <v>1477272.554248336</v>
       </c>
       <c r="P335" t="n">
         <v>28900</v>
@@ -15949,10 +15949,10 @@
         <v>839</v>
       </c>
       <c r="N352" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O352" t="n">
-        <v>1271956.467080425</v>
+        <v>1271956.466964728</v>
       </c>
       <c r="P352" t="n">
         <v>2300</v>
@@ -16503,10 +16503,10 @@
         <v>584</v>
       </c>
       <c r="N364" t="n">
-        <v>13518</v>
+        <v>13521.774923206</v>
       </c>
       <c r="O364" t="n">
-        <v>7894512</v>
+        <v>7896716.555152304</v>
       </c>
       <c r="P364" t="n">
         <v>21900</v>
@@ -23040,10 +23040,10 @@
         <v>11</v>
       </c>
       <c r="N502" t="n">
-        <v>22951.704377622</v>
+        <v>22951.704345992</v>
       </c>
       <c r="O502" t="n">
-        <v>252468.748153842</v>
+        <v>252468.747805912</v>
       </c>
       <c r="P502" t="n">
         <v>37900</v>
@@ -23894,10 +23894,10 @@
         <v>106</v>
       </c>
       <c r="N521" t="n">
-        <v>4576</v>
+        <v>4591.2533333333</v>
       </c>
       <c r="O521" t="n">
-        <v>485056</v>
+        <v>486672.8533333298</v>
       </c>
       <c r="P521" t="n">
         <v>5900</v>
@@ -23940,10 +23940,10 @@
         <v>242</v>
       </c>
       <c r="N522" t="n">
-        <v>5280</v>
+        <v>5285.1815505397</v>
       </c>
       <c r="O522" t="n">
-        <v>1277760</v>
+        <v>1279013.935230607</v>
       </c>
       <c r="P522" t="n">
         <v>6900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1310,10 +1310,10 @@
         <v>48</v>
       </c>
       <c r="N23" t="n">
-        <v>3716.3301980198</v>
+        <v>3716.3301983471</v>
       </c>
       <c r="O23" t="n">
-        <v>178383.8495049504</v>
+        <v>178383.8495206608</v>
       </c>
       <c r="P23" t="n">
         <v>9500</v>
@@ -1427,10 +1427,10 @@
         <v>30</v>
       </c>
       <c r="N26" t="n">
-        <v>27000</v>
+        <v>27051.823416507</v>
       </c>
       <c r="O26" t="n">
-        <v>810000</v>
+        <v>811554.70249521</v>
       </c>
       <c r="P26" t="n">
         <v>30000</v>
@@ -1466,10 +1466,10 @@
         <v>62</v>
       </c>
       <c r="N27" t="n">
-        <v>14857.623287671</v>
+        <v>14857.623302752</v>
       </c>
       <c r="O27" t="n">
-        <v>921172.643835602</v>
+        <v>921172.644770624</v>
       </c>
       <c r="P27" t="n">
         <v>34900</v>
@@ -2927,10 +2927,10 @@
         <v>415</v>
       </c>
       <c r="N62" t="n">
-        <v>4937.3101888412</v>
+        <v>4937.3101890034</v>
       </c>
       <c r="O62" t="n">
-        <v>2048983.728369098</v>
+        <v>2048983.728436411</v>
       </c>
       <c r="P62" t="n">
         <v>7500</v>
@@ -3507,10 +3507,10 @@
         <v>173</v>
       </c>
       <c r="N75" t="n">
-        <v>13694.165945612</v>
+        <v>13593.35</v>
       </c>
       <c r="O75" t="n">
-        <v>2369090.708590876</v>
+        <v>2351649.55</v>
       </c>
       <c r="P75" t="n">
         <v>25500</v>
@@ -4706,10 +4706,10 @@
         <v>179</v>
       </c>
       <c r="N102" t="n">
-        <v>3795.7100076628</v>
+        <v>3795.7100076717</v>
       </c>
       <c r="O102" t="n">
-        <v>679432.0913716411</v>
+        <v>679432.0913732343</v>
       </c>
       <c r="P102" t="n">
         <v>6200</v>
@@ -4885,10 +4885,10 @@
         <v>366</v>
       </c>
       <c r="N106" t="n">
-        <v>4890.9300570207</v>
+        <v>4890.9300571837</v>
       </c>
       <c r="O106" t="n">
-        <v>1790080.400869576</v>
+        <v>1790080.400929234</v>
       </c>
       <c r="P106" t="n">
         <v>8900</v>
@@ -5333,10 +5333,10 @@
         <v>60</v>
       </c>
       <c r="N116" t="n">
-        <v>3240.8500597015</v>
+        <v>3240.8500619195</v>
       </c>
       <c r="O116" t="n">
-        <v>194451.00358209</v>
+        <v>194451.00371517</v>
       </c>
       <c r="P116" t="n">
         <v>5200</v>
@@ -5601,10 +5601,10 @@
         <v>252</v>
       </c>
       <c r="N122" t="n">
-        <v>12422.463013274</v>
+        <v>12422.46301728</v>
       </c>
       <c r="O122" t="n">
-        <v>3130460.679345048</v>
+        <v>3130460.68035456</v>
       </c>
       <c r="P122" t="n">
         <v>19900</v>
@@ -5732,10 +5732,10 @@
         <v>2388</v>
       </c>
       <c r="N125" t="n">
-        <v>3472.2764071985</v>
+        <v>3472.2764292368</v>
       </c>
       <c r="O125" t="n">
-        <v>8291796.060390018</v>
+        <v>8291796.113017479</v>
       </c>
       <c r="P125" t="n">
         <v>5900</v>
@@ -5912,10 +5912,10 @@
         <v>1101</v>
       </c>
       <c r="N129" t="n">
-        <v>4371.1729736673</v>
+        <v>4371.1729765349</v>
       </c>
       <c r="O129" t="n">
-        <v>4812661.444007697</v>
+        <v>4812661.447164925</v>
       </c>
       <c r="P129" t="n">
         <v>8900</v>
@@ -7364,10 +7364,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1633.1055147059</v>
+        <v>1630.9252455662</v>
       </c>
       <c r="O161" t="n">
-        <v>311923.1533088269</v>
+        <v>311506.7219031442</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7410,10 +7410,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1949638844</v>
+        <v>1550.1949858928</v>
       </c>
       <c r="O162" t="n">
-        <v>55807.0186998384</v>
+        <v>55807.0194921408</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7805,10 +7805,10 @@
         <v>31</v>
       </c>
       <c r="N171" t="n">
-        <v>10034.5</v>
+        <v>10166.532894737</v>
       </c>
       <c r="O171" t="n">
-        <v>311069.5</v>
+        <v>315162.519736847</v>
       </c>
       <c r="P171" t="n">
         <v>12900</v>
@@ -8418,10 +8418,10 @@
         <v>91</v>
       </c>
       <c r="N185" t="n">
-        <v>7537.4724786325</v>
+        <v>7537.4727619048</v>
       </c>
       <c r="O185" t="n">
-        <v>685909.9955555574</v>
+        <v>685910.0213333368</v>
       </c>
       <c r="P185" t="n">
         <v>8900</v>
@@ -8746,10 +8746,10 @@
         <v>348</v>
       </c>
       <c r="N193" t="n">
-        <v>2029.8742613636</v>
+        <v>2029.8742906178</v>
       </c>
       <c r="O193" t="n">
-        <v>706396.2429545328</v>
+        <v>706396.2531349944</v>
       </c>
       <c r="P193" t="n">
         <v>3600</v>
@@ -9258,10 +9258,10 @@
         <v>1140</v>
       </c>
       <c r="N205" t="n">
-        <v>6207.9881978301</v>
+        <v>6207.9881950325</v>
       </c>
       <c r="O205" t="n">
-        <v>7077106.545526314</v>
+        <v>7077106.54233705</v>
       </c>
       <c r="P205" t="n">
         <v>9900</v>
@@ -9645,10 +9645,10 @@
         <v>697</v>
       </c>
       <c r="N214" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.263336112</v>
       </c>
       <c r="O214" t="n">
-        <v>3355541.553000979</v>
+        <v>3355541.545270064</v>
       </c>
       <c r="P214" t="n">
         <v>7900</v>
@@ -11301,10 +11301,10 @@
         <v>128</v>
       </c>
       <c r="N251" t="n">
-        <v>3646</v>
+        <v>3656.7445972495</v>
       </c>
       <c r="O251" t="n">
-        <v>466688</v>
+        <v>468063.308447936</v>
       </c>
       <c r="P251" t="n">
         <v>6900</v>
@@ -11347,10 +11347,10 @@
         <v>3</v>
       </c>
       <c r="N252" t="n">
-        <v>23521.618709677</v>
+        <v>23521.6175</v>
       </c>
       <c r="O252" t="n">
-        <v>70564.856129031</v>
+        <v>70564.85250000001</v>
       </c>
       <c r="P252" t="n">
         <v>39000</v>
@@ -11429,10 +11429,10 @@
         <v>620</v>
       </c>
       <c r="N254" t="n">
-        <v>3486</v>
+        <v>3488.1801125704</v>
       </c>
       <c r="O254" t="n">
-        <v>2161320</v>
+        <v>2162671.669793648</v>
       </c>
       <c r="P254" t="n">
         <v>6900</v>
@@ -11475,10 +11475,10 @@
         <v>883</v>
       </c>
       <c r="N255" t="n">
-        <v>1778.4728955224</v>
+        <v>1779.3581483325</v>
       </c>
       <c r="O255" t="n">
-        <v>1570391.566746279</v>
+        <v>1571173.244977597</v>
       </c>
       <c r="P255" t="n">
         <v>4900</v>
@@ -11659,10 +11659,10 @@
         <v>24</v>
       </c>
       <c r="N259" t="n">
-        <v>25577.697661152</v>
+        <v>25534</v>
       </c>
       <c r="O259" t="n">
-        <v>613864.7438676481</v>
+        <v>612816</v>
       </c>
       <c r="P259" t="n">
         <v>40900</v>
@@ -13743,10 +13743,10 @@
         <v>143</v>
       </c>
       <c r="N304" t="n">
-        <v>2252.3013646055</v>
+        <v>2252.3013888889</v>
       </c>
       <c r="O304" t="n">
-        <v>322079.0951385865</v>
+        <v>322079.0986111127</v>
       </c>
       <c r="P304" t="n">
         <v>3900</v>
@@ -13930,10 +13930,10 @@
         <v>504</v>
       </c>
       <c r="N308" t="n">
-        <v>2328.1186316472</v>
+        <v>2328.1186298701</v>
       </c>
       <c r="O308" t="n">
-        <v>1173371.790350189</v>
+        <v>1173371.78945453</v>
       </c>
       <c r="P308" t="n">
         <v>4500</v>
@@ -13976,10 +13976,10 @@
         <v>81</v>
       </c>
       <c r="N309" t="n">
-        <v>21676</v>
+        <v>21700.382452193</v>
       </c>
       <c r="O309" t="n">
-        <v>1755756</v>
+        <v>1757730.978627633</v>
       </c>
       <c r="P309" t="n">
         <v>34900</v>
@@ -14068,10 +14068,10 @@
         <v>47</v>
       </c>
       <c r="N311" t="n">
-        <v>9018.1565656566</v>
+        <v>9003</v>
       </c>
       <c r="O311" t="n">
-        <v>423853.3585858602</v>
+        <v>423141</v>
       </c>
       <c r="P311" t="n">
         <v>14900</v>
@@ -14344,10 +14344,10 @@
         <v>100</v>
       </c>
       <c r="N317" t="n">
-        <v>4907.8228863636</v>
+        <v>4907.8230382775</v>
       </c>
       <c r="O317" t="n">
-        <v>490782.28863636</v>
+        <v>490782.30382775</v>
       </c>
       <c r="P317" t="n">
         <v>8200</v>
@@ -15949,10 +15949,10 @@
         <v>839</v>
       </c>
       <c r="N352" t="n">
-        <v>1516.0386972166</v>
+        <v>1516.0386977679</v>
       </c>
       <c r="O352" t="n">
-        <v>1271956.466964728</v>
+        <v>1271956.467427268</v>
       </c>
       <c r="P352" t="n">
         <v>2300</v>
@@ -16503,10 +16503,10 @@
         <v>584</v>
       </c>
       <c r="N364" t="n">
-        <v>13521.774923206</v>
+        <v>13518</v>
       </c>
       <c r="O364" t="n">
-        <v>7896716.555152304</v>
+        <v>7894512</v>
       </c>
       <c r="P364" t="n">
         <v>21900</v>
@@ -17554,10 +17554,10 @@
         <v>158</v>
       </c>
       <c r="N386" t="n">
-        <v>1690.8700098184</v>
+        <v>1690.8700098765</v>
       </c>
       <c r="O386" t="n">
-        <v>267157.4615513072</v>
+        <v>267157.461560487</v>
       </c>
       <c r="P386" t="n">
         <v>3000</v>
@@ -17701,10 +17701,10 @@
         <v>47</v>
       </c>
       <c r="N389" t="n">
-        <v>2270.3215151515</v>
+        <v>2270.3217241379</v>
       </c>
       <c r="O389" t="n">
-        <v>106705.1112121205</v>
+        <v>106705.1210344813</v>
       </c>
       <c r="P389" t="n">
         <v>3900</v>
@@ -17745,10 +17745,10 @@
         <v>1602</v>
       </c>
       <c r="N390" t="n">
-        <v>481.48790068997</v>
+        <v>481.48790045249</v>
       </c>
       <c r="O390" t="n">
-        <v>771343.616905332</v>
+        <v>771343.616524889</v>
       </c>
       <c r="P390" t="n">
         <v>650</v>
@@ -18162,10 +18162,10 @@
         <v>45</v>
       </c>
       <c r="N399" t="n">
-        <v>4032.3967801047</v>
+        <v>4032.3967716535</v>
       </c>
       <c r="O399" t="n">
-        <v>181457.8551047115</v>
+        <v>181457.8547244075</v>
       </c>
       <c r="P399" t="n">
         <v>4200</v>
@@ -18957,10 +18957,10 @@
         <v>4</v>
       </c>
       <c r="N416" t="n">
-        <v>2501.3837931034</v>
+        <v>2501.3837572254</v>
       </c>
       <c r="O416" t="n">
-        <v>10005.5351724136</v>
+        <v>10005.5350289016</v>
       </c>
       <c r="P416" t="n">
         <v>4100</v>
@@ -19952,10 +19952,10 @@
         <v>23</v>
       </c>
       <c r="N437" t="n">
-        <v>2832.1961818182</v>
+        <v>2832.1965384615</v>
       </c>
       <c r="O437" t="n">
-        <v>65140.51218181859</v>
+        <v>65140.5203846145</v>
       </c>
       <c r="P437" t="n">
         <v>12900</v>
@@ -20194,10 +20194,10 @@
         <v>21</v>
       </c>
       <c r="N442" t="n">
-        <v>16670.89</v>
+        <v>17351.334489796</v>
       </c>
       <c r="O442" t="n">
-        <v>350088.69</v>
+        <v>364378.024285716</v>
       </c>
       <c r="P442" t="n">
         <v>25500</v>
@@ -21650,10 +21650,10 @@
         <v>4</v>
       </c>
       <c r="N472" t="n">
-        <v>8931.4411111111</v>
+        <v>8931.4411764706</v>
       </c>
       <c r="O472" t="n">
-        <v>35725.7644444444</v>
+        <v>35725.7647058824</v>
       </c>
       <c r="P472" t="n">
         <v>19900</v>
@@ -21748,10 +21748,10 @@
         <v>15</v>
       </c>
       <c r="N474" t="n">
-        <v>16146.498181818</v>
+        <v>16146.498</v>
       </c>
       <c r="O474" t="n">
-        <v>242197.47272727</v>
+        <v>242197.47</v>
       </c>
       <c r="P474" t="n">
         <v>26900</v>
@@ -22737,10 +22737,10 @@
         <v>60</v>
       </c>
       <c r="N495" t="n">
-        <v>1008.8110899183</v>
+        <v>1008.8107756233</v>
       </c>
       <c r="O495" t="n">
-        <v>60528.665395098</v>
+        <v>60528.646537398</v>
       </c>
       <c r="P495" t="n">
         <v>1500</v>
@@ -23040,10 +23040,10 @@
         <v>11</v>
       </c>
       <c r="N502" t="n">
-        <v>22951.704345992</v>
+        <v>22951.704248927</v>
       </c>
       <c r="O502" t="n">
-        <v>252468.747805912</v>
+        <v>252468.746738197</v>
       </c>
       <c r="P502" t="n">
         <v>37900</v>
@@ -23894,10 +23894,10 @@
         <v>106</v>
       </c>
       <c r="N521" t="n">
-        <v>4591.2533333333</v>
+        <v>4576</v>
       </c>
       <c r="O521" t="n">
-        <v>486672.8533333298</v>
+        <v>485056</v>
       </c>
       <c r="P521" t="n">
         <v>5900</v>
